--- a/500万资产配置组合2026.xlsx
+++ b/500万资产配置组合2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17680" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="9060" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="投资纪要" sheetId="1" state="visible" r:id="rId1"/>
@@ -1528,7 +1528,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E55"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
     <col width="30" customWidth="1" style="1" min="2" max="2"/>
@@ -2292,26 +2292,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <dimension ref="A1:R14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.731481481481479" defaultRowHeight="14.4"/>
   <cols>
-    <col width="7.54545454545455" customWidth="1" style="1" min="1" max="1"/>
-    <col width="21.6363636363636" customWidth="1" style="1" min="2" max="2"/>
-    <col hidden="1" width="16.2727272727273" customWidth="1" style="1" min="3" max="3"/>
-    <col width="16.2727272727273" customWidth="1" style="1" min="4" max="4"/>
-    <col width="9" customWidth="1" style="1" min="5" max="6"/>
-    <col width="9.54545454545454" customWidth="1" style="1" min="7" max="7"/>
-    <col width="10.6363636363636" customWidth="1" style="50" min="8" max="8"/>
-    <col width="10.6363636363636" customWidth="1" style="51" min="9" max="9"/>
-    <col width="16.2727272727273" customWidth="1" style="52" min="10" max="10"/>
-    <col width="11.0909090909091" customWidth="1" style="53" min="11" max="11"/>
-    <col width="15.1818181818182" customWidth="1" style="1" min="12" max="12"/>
-    <col width="10.6363636363636" customWidth="1" style="53" min="13" max="13"/>
-    <col width="15.1818181818182" customWidth="1" style="54" min="14" max="14"/>
+    <col width="7.5462962962963" customWidth="1" style="1" min="1" max="1"/>
+    <col width="21.6388888888889" customWidth="1" style="1" min="2" max="2"/>
+    <col hidden="1" width="16.2685185185185" customWidth="1" style="1" min="3" max="3"/>
+    <col width="16.2685185185185" customWidth="1" style="1" min="4" max="4"/>
+    <col width="12" customWidth="1" style="1" min="5" max="5"/>
+    <col width="11.7777777777778" customWidth="1" style="1" min="6" max="6"/>
+    <col width="9.66666666666667" customWidth="1" style="1" min="7" max="7"/>
+    <col width="10.6388888888889" customWidth="1" style="50" min="8" max="8"/>
+    <col width="10.6388888888889" customWidth="1" style="51" min="9" max="9"/>
+    <col width="16.4444444444444" customWidth="1" style="52" min="10" max="10"/>
+    <col width="14.2222222222222" customWidth="1" style="53" min="11" max="11"/>
+    <col width="15.1851851851852" customWidth="1" style="1" min="12" max="12"/>
+    <col width="10.6388888888889" customWidth="1" style="53" min="13" max="13"/>
+    <col width="15.1851851851852" customWidth="1" style="54" min="14" max="14"/>
     <col width="14" customWidth="1" style="1" min="15" max="15"/>
-    <col width="9.54545454545454" customWidth="1" style="1" min="17" max="17"/>
-    <col width="12.8181818181818" customWidth="1" style="1" min="18" max="18"/>
-    <col width="12.8181818181818" customWidth="1" style="1" min="19" max="19"/>
+    <col width="9.546296296296299" customWidth="1" style="1" min="16" max="16"/>
+    <col width="12.8148148148148" customWidth="1" style="1" min="17" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="1">
@@ -2411,10 +2411,10 @@
         <v>0.15</v>
       </c>
       <c r="F2" s="61" t="n">
-        <v>0.1084</v>
+        <v>0.1703</v>
       </c>
       <c r="G2" s="61" t="n">
-        <v>-0.0416</v>
+        <v>0.0203</v>
       </c>
       <c r="H2" s="62" t="n">
         <v>4.914</v>
@@ -2427,29 +2427,20 @@
         <v/>
       </c>
       <c r="K2" s="65" t="n">
-        <v>4.936</v>
+        <v>4.965</v>
       </c>
       <c r="L2" s="66" t="n">
-        <v>2420</v>
+        <v>5610</v>
       </c>
       <c r="M2" s="58" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>📊权重预警偏离-4.2%</t>
-        </is>
-      </c>
+        <v>0.0104</v>
+      </c>
+      <c r="N2" s="4" t="n"/>
       <c r="O2" s="67">
         <f>D2-J2</f>
         <v/>
       </c>
-      <c r="P2" s="0" t="inlineStr">
-        <is>
-          <t>[DATA-LAG] 数据滞后(05-28)</t>
-        </is>
-      </c>
-      <c r="S2" s="0" t="n">
+      <c r="R2" s="0" t="n">
         <v>42600</v>
       </c>
     </row>
@@ -2473,10 +2464,10 @@
         <v>0.1</v>
       </c>
       <c r="F3" s="61" t="n">
-        <v>0.0336</v>
+        <v>0.0527</v>
       </c>
       <c r="G3" s="61" t="n">
-        <v>-0.0664</v>
+        <v>-0.0473</v>
       </c>
       <c r="H3" s="62" t="n">
         <v>8.696</v>
@@ -2489,29 +2480,24 @@
         <v/>
       </c>
       <c r="K3" s="65" t="n">
-        <v>8.406000000000001</v>
+        <v>8.455</v>
       </c>
       <c r="L3" s="66" t="n">
-        <v>-5800</v>
+        <v>-4820</v>
       </c>
       <c r="M3" s="58" t="n">
-        <v>-0.0333</v>
+        <v>-0.0277</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>📊权重预警偏离-6.6%</t>
+          <t>📊权重预警偏离-4.7%</t>
         </is>
       </c>
       <c r="O3" s="67">
         <f>D3-J3</f>
         <v/>
       </c>
-      <c r="P3" s="0" t="inlineStr">
-        <is>
-          <t>[DATA-LAG] 数据滞后(05-28)</t>
-        </is>
-      </c>
-      <c r="S3" s="0" t="n">
+      <c r="R3" s="0" t="n">
         <v>38700</v>
       </c>
     </row>
@@ -2535,10 +2521,10 @@
         <v>0.05</v>
       </c>
       <c r="F4" s="61" t="n">
-        <v>0.0208</v>
+        <v>0.0332</v>
       </c>
       <c r="G4" s="61" t="n">
-        <v>-0.0292</v>
+        <v>-0.0168</v>
       </c>
       <c r="H4" s="62" t="n">
         <v>1.838</v>
@@ -2551,29 +2537,20 @@
         <v/>
       </c>
       <c r="K4" s="65" t="n">
-        <v>1.734</v>
+        <v>1.772</v>
       </c>
       <c r="L4" s="66" t="n">
-        <v>-6240</v>
+        <v>-3960</v>
       </c>
       <c r="M4" s="58" t="n">
-        <v>-0.0566</v>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>⚡预警：浮亏-5.7% &gt;= -5%，暂停新增买入</t>
-        </is>
-      </c>
+        <v>-0.0359</v>
+      </c>
+      <c r="N4" s="4" t="n"/>
       <c r="O4" s="67">
         <f>D4-J4</f>
         <v/>
       </c>
-      <c r="P4" s="0" t="inlineStr">
-        <is>
-          <t>[DATA-LAG] 数据滞后(05-28)</t>
-        </is>
-      </c>
-      <c r="S4" s="0" t="n">
+      <c r="R4" s="0" t="n">
         <v>77900</v>
       </c>
     </row>
@@ -2597,10 +2574,10 @@
         <v>0.05</v>
       </c>
       <c r="F5" s="70" t="n">
-        <v>0.0512</v>
+        <v>0.0814</v>
       </c>
       <c r="G5" s="70" t="n">
-        <v>0.0012</v>
+        <v>0.0314</v>
       </c>
       <c r="H5" s="71" t="n">
         <v>3.968</v>
@@ -2613,21 +2590,20 @@
         <v/>
       </c>
       <c r="K5" s="65" t="n">
-        <v>4.071</v>
+        <v>4.145</v>
       </c>
       <c r="L5" s="74" t="n">
-        <v>6489</v>
+        <v>11151</v>
       </c>
       <c r="M5" s="75" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="N5" s="41" t="inlineStr"/>
+        <v>0.0446</v>
+      </c>
+      <c r="N5" s="41" t="inlineStr">
+        <is>
+          <t>📊权重预警偏离+3.1%</t>
+        </is>
+      </c>
       <c r="O5" s="67" t="n"/>
-      <c r="P5" s="0" t="inlineStr">
-        <is>
-          <t>[DATA-LAG] 数据滞后(05-28)</t>
-        </is>
-      </c>
     </row>
     <row r="6" customFormat="1" s="10">
       <c r="A6" s="31" t="n">
@@ -2649,10 +2625,10 @@
         <v>0.05</v>
       </c>
       <c r="F6" s="70" t="n">
-        <v>0.0515</v>
+        <v>0.0798</v>
       </c>
       <c r="G6" s="70" t="n">
-        <v>0.0015</v>
+        <v>0.0298</v>
       </c>
       <c r="H6" s="71" t="n">
         <v>1.15</v>
@@ -2665,21 +2641,16 @@
         <v/>
       </c>
       <c r="K6" s="65" t="n">
-        <v>1.182</v>
+        <v>1.173</v>
       </c>
       <c r="L6" s="74" t="n">
-        <v>6976</v>
+        <v>5014</v>
       </c>
       <c r="M6" s="75" t="n">
-        <v>0.0278</v>
-      </c>
-      <c r="N6" s="41" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="N6" s="41" t="n"/>
       <c r="O6" s="67" t="n"/>
-      <c r="P6" s="0" t="inlineStr">
-        <is>
-          <t>[DATA-LAG] 数据滞后(05-28)</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="22" t="n">
@@ -2713,22 +2684,25 @@
         <v/>
       </c>
       <c r="K7" s="62" t="n">
-        <v>14.121</v>
+        <v>14.083</v>
       </c>
       <c r="L7" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="58">
-        <f>(K7-H7)/H7</f>
-        <v/>
-      </c>
-      <c r="N7" s="4" t="inlineStr"/>
+      <c r="M7" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>🔴再平衡紧急线：偏离-10.0% &gt;= ±10%</t>
+        </is>
+      </c>
       <c r="O7" s="67">
         <f>D7-J7</f>
         <v/>
       </c>
     </row>
-    <row r="8" customFormat="1" s="10">
+    <row r="8" ht="28.8" customFormat="1" customHeight="1" s="10">
       <c r="A8" s="31" t="n">
         <v>511260</v>
       </c>
@@ -2748,10 +2722,10 @@
         <v>0.1</v>
       </c>
       <c r="F8" s="70" t="n">
-        <v>0.1006</v>
+        <v>0.157</v>
       </c>
       <c r="G8" s="70" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.057</v>
       </c>
       <c r="H8" s="71" t="n">
         <v>135.645</v>
@@ -2764,21 +2738,20 @@
         <v/>
       </c>
       <c r="K8" s="65" t="n">
-        <v>136.14</v>
+        <v>136.078</v>
       </c>
       <c r="L8" s="74" t="n">
-        <v>1831.5</v>
+        <v>1602.1</v>
       </c>
       <c r="M8" s="75" t="n">
-        <v>0.0036</v>
-      </c>
-      <c r="N8" s="41" t="inlineStr"/>
+        <v>0.0032</v>
+      </c>
+      <c r="N8" s="41" t="inlineStr">
+        <is>
+          <t>📊权重预警偏离+5.7%</t>
+        </is>
+      </c>
       <c r="O8" s="67" t="n"/>
-      <c r="P8" s="0" t="inlineStr">
-        <is>
-          <t>[DATA-LAG] 数据滞后(05-28)</t>
-        </is>
-      </c>
     </row>
     <row r="9" customFormat="1" s="10">
       <c r="A9" s="31" t="n">
@@ -2800,10 +2773,10 @@
         <v>0.1</v>
       </c>
       <c r="F9" s="70" t="n">
-        <v>0.0989</v>
+        <v>0.1544</v>
       </c>
       <c r="G9" s="70" t="n">
-        <v>-0.0011</v>
+        <v>0.0544</v>
       </c>
       <c r="H9" s="71" t="n">
         <v>141.2121</v>
@@ -2816,21 +2789,20 @@
         <v/>
       </c>
       <c r="K9" s="65" t="n">
-        <v>141.48</v>
+        <v>141.464</v>
       </c>
       <c r="L9" s="74" t="n">
-        <v>937.65</v>
+        <v>881.65</v>
       </c>
       <c r="M9" s="75" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="N9" s="41" t="inlineStr"/>
+        <v>0.0018</v>
+      </c>
+      <c r="N9" s="41" t="inlineStr">
+        <is>
+          <t>📊权重预警偏离+5.4%</t>
+        </is>
+      </c>
       <c r="O9" s="67" t="n"/>
-      <c r="P9" s="0" t="inlineStr">
-        <is>
-          <t>[DATA-LAG] 数据滞后(05-28)</t>
-        </is>
-      </c>
     </row>
     <row r="10" customFormat="1" s="10">
       <c r="A10" s="31" t="n">
@@ -2852,10 +2824,10 @@
         <v>0.05</v>
       </c>
       <c r="F10" s="70" t="n">
-        <v>0.0499</v>
+        <v>0.0779</v>
       </c>
       <c r="G10" s="70" t="n">
-        <v>-0.0001</v>
+        <v>0.0279</v>
       </c>
       <c r="H10" s="71" t="n">
         <v>113.462</v>
@@ -2868,21 +2840,16 @@
         <v/>
       </c>
       <c r="K10" s="65" t="n">
-        <v>113.526</v>
+        <v>113.528</v>
       </c>
       <c r="L10" s="74" t="n">
-        <v>140.8</v>
+        <v>145.2</v>
       </c>
       <c r="M10" s="75" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="N10" s="41" t="inlineStr"/>
+      <c r="N10" s="41" t="n"/>
       <c r="O10" s="67" t="n"/>
-      <c r="P10" s="0" t="inlineStr">
-        <is>
-          <t>[DATA-LAG] 数据滞后(05-28)</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="22" t="n">
@@ -2904,10 +2871,10 @@
         <v>0.15</v>
       </c>
       <c r="F11" s="61" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.1152</v>
       </c>
       <c r="G11" s="61" t="n">
-        <v>-0.0752</v>
+        <v>-0.0348</v>
       </c>
       <c r="H11" s="62" t="n">
         <v>9.396599999999999</v>
@@ -2920,27 +2887,22 @@
         <v/>
       </c>
       <c r="K11" s="65" t="n">
-        <v>9.41</v>
+        <v>9.281000000000001</v>
       </c>
       <c r="L11" s="66" t="n">
-        <v>533.3200000000001</v>
+        <v>-4600.88</v>
       </c>
       <c r="M11" s="58" t="n">
-        <v>0.0014</v>
+        <v>-0.0123</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>⚠️权重触发线偏离-7.5%</t>
+          <t>📊权重预警偏离-3.5%</t>
         </is>
       </c>
       <c r="O11" s="67">
         <f>D11-J11</f>
         <v/>
-      </c>
-      <c r="P11" s="0" t="inlineStr">
-        <is>
-          <t>[DATA-LAG] 数据滞后(05-28)</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -2975,16 +2937,19 @@
         <v/>
       </c>
       <c r="K12" s="62" t="n">
-        <v>100.488</v>
+        <v>100.501</v>
       </c>
       <c r="L12" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="58">
-        <f>(K12-H12)/H12</f>
-        <v/>
-      </c>
-      <c r="N12" s="4" t="inlineStr"/>
+      <c r="M12" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>📊权重预警偏离-5.0%</t>
+        </is>
+      </c>
       <c r="O12" s="67">
         <f>D12-J12</f>
         <v/>
@@ -3010,10 +2975,10 @@
         <v>0.05</v>
       </c>
       <c r="F13" s="61" t="n">
-        <v>0.0499</v>
+        <v>0.078</v>
       </c>
       <c r="G13" s="61" t="n">
-        <v>-0.0001</v>
+        <v>0.028</v>
       </c>
       <c r="H13" s="62" t="n">
         <v>99.997</v>
@@ -3026,21 +2991,16 @@
         <v/>
       </c>
       <c r="K13" s="65" t="n">
-        <v>99.999</v>
+        <v>100</v>
       </c>
       <c r="L13" s="66" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="M13" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="4" t="inlineStr"/>
+      <c r="N13" s="4" t="n"/>
       <c r="O13" s="67" t="n"/>
-      <c r="P13" s="0" t="inlineStr">
-        <is>
-          <t>[DATA-LAG] 数据滞后(05-28)</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr"/>
@@ -3083,12 +3043,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col width="20.8181818181818" customWidth="1" style="76" min="1" max="1"/>
-    <col width="7.54545454545455" customWidth="1" style="1" min="2" max="2"/>
-    <col width="12.9090909090909" customWidth="1" style="1" min="3" max="3"/>
-    <col width="10.6363636363636" customWidth="1" style="1" min="4" max="4"/>
+    <col width="20.8148148148148" customWidth="1" style="76" min="1" max="1"/>
+    <col width="7.5462962962963" customWidth="1" style="1" min="2" max="2"/>
+    <col width="12.9074074074074" customWidth="1" style="1" min="3" max="3"/>
+    <col width="10.6388888888889" customWidth="1" style="1" min="4" max="4"/>
     <col width="14" customWidth="1" style="1" min="5" max="6"/>
   </cols>
   <sheetData>
@@ -3556,21 +3516,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q115"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:Q127"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col width="11.8181818181818" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.54545454545454" customWidth="1" style="1" min="2" max="2"/>
-    <col width="10.6363636363636" customWidth="1" style="1" min="3" max="3"/>
-    <col width="9.54545454545454" customWidth="1" style="1" min="4" max="4"/>
-    <col width="8.54545454545454" customWidth="1" style="1" min="5" max="5"/>
-    <col width="9.54545454545454" customWidth="1" style="1" min="6" max="7"/>
-    <col width="7.54545454545455" customWidth="1" style="1" min="8" max="8"/>
-    <col width="9.54545454545454" customWidth="1" style="1" min="9" max="10"/>
-    <col width="8.54545454545454" customWidth="1" style="1" min="11" max="11"/>
-    <col width="9.54545454545454" customWidth="1" style="1" min="12" max="13"/>
-    <col width="7.54545454545455" customWidth="1" style="1" min="14" max="14"/>
-    <col width="9.54545454545454" customWidth="1" style="1" min="15" max="15"/>
+    <col width="11.8148148148148" customWidth="1" style="1" min="1" max="1"/>
+    <col width="9.546296296296299" customWidth="1" style="1" min="2" max="2"/>
+    <col width="10.6388888888889" customWidth="1" style="1" min="3" max="3"/>
+    <col width="9.546296296296299" customWidth="1" style="1" min="4" max="4"/>
+    <col width="8.546296296296299" customWidth="1" style="1" min="5" max="5"/>
+    <col width="9.546296296296299" customWidth="1" style="1" min="6" max="7"/>
+    <col width="7.5462962962963" customWidth="1" style="1" min="8" max="8"/>
+    <col width="9.546296296296299" customWidth="1" style="1" min="9" max="10"/>
+    <col width="8.546296296296299" customWidth="1" style="1" min="11" max="11"/>
+    <col width="9.546296296296299" customWidth="1" style="1" min="12" max="13"/>
+    <col width="7.5462962962963" customWidth="1" style="1" min="14" max="14"/>
+    <col width="9.546296296296299" customWidth="1" style="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10077,366 +10037,738 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="0" t="inlineStr">
         <is>
           <t>20260602</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="0" t="inlineStr">
         <is>
           <t>沪深300ETF</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="0" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="H104" t="n">
+      <c r="H104" s="0" t="n">
         <v>4.936</v>
       </c>
-      <c r="I104" t="n">
+      <c r="I104" s="0" t="n">
         <v>2420</v>
       </c>
-      <c r="J104" t="n">
+      <c r="J104" s="0" t="n">
         <v>0.0045</v>
       </c>
-      <c r="N104" t="inlineStr">
+      <c r="N104" s="0" t="inlineStr">
         <is>
           <t>📊权重预警偏离-4.2%</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="0" t="inlineStr">
         <is>
           <t>20260602</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="0" t="inlineStr">
         <is>
           <t>中证500ETF</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="0" t="inlineStr">
         <is>
           <t>510500</t>
         </is>
       </c>
-      <c r="H105" t="n">
+      <c r="H105" s="0" t="n">
         <v>8.406000000000001</v>
       </c>
-      <c r="I105" t="n">
+      <c r="I105" s="0" t="n">
         <v>-5800</v>
       </c>
-      <c r="J105" t="n">
+      <c r="J105" s="0" t="n">
         <v>-0.0333</v>
       </c>
-      <c r="N105" t="inlineStr">
+      <c r="N105" s="0" t="inlineStr">
         <is>
           <t>📊权重预警偏离-6.6%</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="0" t="inlineStr">
         <is>
           <t>20260602</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="0" t="inlineStr">
         <is>
           <t>科创50ETF</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="0" t="inlineStr">
         <is>
           <t>588050</t>
         </is>
       </c>
-      <c r="H106" t="n">
+      <c r="H106" s="0" t="n">
         <v>1.734</v>
       </c>
-      <c r="I106" t="n">
+      <c r="I106" s="0" t="n">
         <v>-6240</v>
       </c>
-      <c r="J106" t="n">
+      <c r="J106" s="0" t="n">
         <v>-0.0566</v>
       </c>
-      <c r="N106" t="inlineStr">
+      <c r="N106" s="0" t="inlineStr">
         <is>
           <t>⚡预警：浮亏-5.7% &gt;= -5%，暂停新增买入</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="0" t="inlineStr">
         <is>
           <t>20260602</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="0" t="inlineStr">
         <is>
           <t>创业板ETF</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="0" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="H107" t="n">
+      <c r="H107" s="0" t="n">
         <v>4.071</v>
       </c>
-      <c r="I107" t="n">
+      <c r="I107" s="0" t="n">
         <v>6489</v>
       </c>
-      <c r="J107" t="n">
+      <c r="J107" s="0" t="n">
         <v>0.026</v>
       </c>
-      <c r="N107" t="inlineStr">
+      <c r="N107" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="0" t="inlineStr">
         <is>
           <t>20260602</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="0" t="inlineStr">
         <is>
           <t>红利低波ETF</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="0" t="inlineStr">
         <is>
           <t>512890</t>
         </is>
       </c>
-      <c r="H108" t="n">
+      <c r="H108" s="0" t="n">
         <v>1.182</v>
       </c>
-      <c r="I108" t="n">
+      <c r="I108" s="0" t="n">
         <v>6976</v>
       </c>
-      <c r="J108" t="n">
+      <c r="J108" s="0" t="n">
         <v>0.0278</v>
       </c>
-      <c r="N108" t="inlineStr">
+      <c r="N108" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="0" t="inlineStr">
         <is>
           <t>20260602</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="0" t="inlineStr">
         <is>
           <t>可转债ETF</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="0" t="inlineStr">
         <is>
           <t>511380</t>
         </is>
       </c>
-      <c r="H109" t="n">
+      <c r="H109" s="0" t="n">
         <v>14.121</v>
       </c>
-      <c r="I109" t="n">
+      <c r="I109" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="N109" t="inlineStr">
+      <c r="N109" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="0" t="inlineStr">
         <is>
           <t>20260602</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="0" t="inlineStr">
         <is>
           <t>10年国债ETF</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="0" t="inlineStr">
         <is>
           <t>511260</t>
         </is>
       </c>
-      <c r="H110" t="n">
+      <c r="H110" s="0" t="n">
         <v>136.14</v>
       </c>
-      <c r="I110" t="n">
+      <c r="I110" s="0" t="n">
         <v>1831.5</v>
       </c>
-      <c r="J110" t="n">
+      <c r="J110" s="0" t="n">
         <v>0.0036</v>
       </c>
-      <c r="N110" t="inlineStr">
+      <c r="N110" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="0" t="inlineStr">
         <is>
           <t>20260602</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="0" t="inlineStr">
         <is>
           <t>5年国债ETF</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" s="0" t="inlineStr">
         <is>
           <t>511010</t>
         </is>
       </c>
-      <c r="H111" t="n">
+      <c r="H111" s="0" t="n">
         <v>141.48</v>
       </c>
-      <c r="I111" t="n">
+      <c r="I111" s="0" t="n">
         <v>937.65</v>
       </c>
-      <c r="J111" t="n">
+      <c r="J111" s="0" t="n">
         <v>0.0019</v>
       </c>
-      <c r="N111" t="inlineStr">
+      <c r="N111" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="0" t="inlineStr">
         <is>
           <t>20260602</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="0" t="inlineStr">
         <is>
           <t>短融ETF</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="0" t="inlineStr">
         <is>
           <t>511360</t>
         </is>
       </c>
-      <c r="H112" t="n">
+      <c r="H112" s="0" t="n">
         <v>113.526</v>
       </c>
-      <c r="I112" t="n">
+      <c r="I112" s="0" t="n">
         <v>140.8</v>
       </c>
-      <c r="J112" t="n">
+      <c r="J112" s="0" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="N112" t="inlineStr">
+      <c r="N112" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="0" t="inlineStr">
         <is>
           <t>20260602</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="0" t="inlineStr">
         <is>
           <t>黄金ETF</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="0" t="inlineStr">
         <is>
           <t>518880</t>
         </is>
       </c>
-      <c r="H113" t="n">
+      <c r="H113" s="0" t="n">
         <v>9.41</v>
       </c>
-      <c r="I113" t="n">
+      <c r="I113" s="0" t="n">
         <v>533.3200000000001</v>
       </c>
-      <c r="J113" t="n">
+      <c r="J113" s="0" t="n">
         <v>0.0014</v>
       </c>
-      <c r="N113" t="inlineStr">
+      <c r="N113" s="0" t="inlineStr">
         <is>
           <t>⚠️权重触发线偏离-7.5%</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="0" t="inlineStr">
         <is>
           <t>20260602</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="0" t="inlineStr">
         <is>
           <t>银华日利ETF</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="0" t="inlineStr">
         <is>
           <t>511880</t>
         </is>
       </c>
-      <c r="H114" t="n">
+      <c r="H114" s="0" t="n">
         <v>100.488</v>
       </c>
-      <c r="I114" t="n">
+      <c r="I114" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="N114" t="inlineStr">
+      <c r="N114" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="0" t="inlineStr">
         <is>
           <t>20260602</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="0" t="inlineStr">
         <is>
           <t>华宝添益ETF</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="0" t="inlineStr">
         <is>
           <t>511990</t>
         </is>
       </c>
-      <c r="H115" t="n">
+      <c r="H115" s="0" t="n">
         <v>99.999</v>
       </c>
-      <c r="I115" t="n">
+      <c r="I115" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J115" t="n">
+      <c r="J115" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="N115" t="inlineStr">
+      <c r="N115" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t>沪深300ETF</t>
+        </is>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="H116" s="0" t="n">
+        <v>4.965</v>
+      </c>
+      <c r="I116" s="0" t="n">
+        <v>5610</v>
+      </c>
+      <c r="J116" s="0" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="N116" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B117" s="0" t="inlineStr">
+        <is>
+          <t>中证500ETF</t>
+        </is>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t>510500</t>
+        </is>
+      </c>
+      <c r="H117" s="0" t="n">
+        <v>8.455</v>
+      </c>
+      <c r="I117" s="0" t="n">
+        <v>-4820</v>
+      </c>
+      <c r="J117" s="0" t="n">
+        <v>-0.0277</v>
+      </c>
+      <c r="N117" s="0" t="inlineStr">
+        <is>
+          <t>📊权重预警偏离-4.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B118" s="0" t="inlineStr">
+        <is>
+          <t>科创50ETF</t>
+        </is>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t>588050</t>
+        </is>
+      </c>
+      <c r="H118" s="0" t="n">
+        <v>1.772</v>
+      </c>
+      <c r="I118" s="0" t="n">
+        <v>-3960</v>
+      </c>
+      <c r="J118" s="0" t="n">
+        <v>-0.0359</v>
+      </c>
+      <c r="N118" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B119" s="0" t="inlineStr">
+        <is>
+          <t>创业板ETF</t>
+        </is>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="H119" s="0" t="n">
+        <v>4.145</v>
+      </c>
+      <c r="I119" s="0" t="n">
+        <v>11151</v>
+      </c>
+      <c r="J119" s="0" t="n">
+        <v>0.0446</v>
+      </c>
+      <c r="N119" s="0" t="inlineStr">
+        <is>
+          <t>📊权重预警偏离+3.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B120" s="0" t="inlineStr">
+        <is>
+          <t>红利低波ETF</t>
+        </is>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t>512890</t>
+        </is>
+      </c>
+      <c r="H120" s="0" t="n">
+        <v>1.173</v>
+      </c>
+      <c r="I120" s="0" t="n">
+        <v>5014</v>
+      </c>
+      <c r="J120" s="0" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N120" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B121" s="0" t="inlineStr">
+        <is>
+          <t>可转债ETF</t>
+        </is>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t>511380</t>
+        </is>
+      </c>
+      <c r="H121" s="0" t="n">
+        <v>14.083</v>
+      </c>
+      <c r="I121" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" s="0" t="inlineStr">
+        <is>
+          <t>🔴再平衡紧急线：偏离-10.0% &gt;= ±10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B122" s="0" t="inlineStr">
+        <is>
+          <t>10年国债ETF</t>
+        </is>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>511260</t>
+        </is>
+      </c>
+      <c r="H122" s="0" t="n">
+        <v>136.078</v>
+      </c>
+      <c r="I122" s="0" t="n">
+        <v>1602.1</v>
+      </c>
+      <c r="J122" s="0" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="N122" s="0" t="inlineStr">
+        <is>
+          <t>📊权重预警偏离+5.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B123" s="0" t="inlineStr">
+        <is>
+          <t>5年国债ETF</t>
+        </is>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t>511010</t>
+        </is>
+      </c>
+      <c r="H123" s="0" t="n">
+        <v>141.464</v>
+      </c>
+      <c r="I123" s="0" t="n">
+        <v>881.65</v>
+      </c>
+      <c r="J123" s="0" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="N123" s="0" t="inlineStr">
+        <is>
+          <t>📊权重预警偏离+5.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B124" s="0" t="inlineStr">
+        <is>
+          <t>短融ETF</t>
+        </is>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t>511360</t>
+        </is>
+      </c>
+      <c r="H124" s="0" t="n">
+        <v>113.528</v>
+      </c>
+      <c r="I124" s="0" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="J124" s="0" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="N124" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B125" s="0" t="inlineStr">
+        <is>
+          <t>黄金ETF</t>
+        </is>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t>518880</t>
+        </is>
+      </c>
+      <c r="H125" s="0" t="n">
+        <v>9.281000000000001</v>
+      </c>
+      <c r="I125" s="0" t="n">
+        <v>-4600.88</v>
+      </c>
+      <c r="J125" s="0" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="N125" s="0" t="inlineStr">
+        <is>
+          <t>📊权重预警偏离-3.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B126" s="0" t="inlineStr">
+        <is>
+          <t>银华日利ETF</t>
+        </is>
+      </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t>511880</t>
+        </is>
+      </c>
+      <c r="H126" s="0" t="n">
+        <v>100.501</v>
+      </c>
+      <c r="I126" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" s="0" t="inlineStr">
+        <is>
+          <t>📊权重预警偏离-5.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B127" s="0" t="inlineStr">
+        <is>
+          <t>华宝添益ETF</t>
+        </is>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t>511990</t>
+        </is>
+      </c>
+      <c r="H127" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="I127" s="0" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J127" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/500万资产配置组合2026.xlsx
+++ b/500万资产配置组合2026.xlsx
@@ -2411,10 +2411,10 @@
         <v>0.15</v>
       </c>
       <c r="F2" s="61" t="n">
-        <v>0.1703</v>
+        <v>0.1778</v>
       </c>
       <c r="G2" s="61" t="n">
-        <v>0.0203</v>
+        <v>0.0278</v>
       </c>
       <c r="H2" s="62" t="n">
         <v>4.914</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="K2" s="65" t="n">
-        <v>4.965</v>
+        <v>4.926</v>
       </c>
       <c r="L2" s="66" t="n">
-        <v>5610</v>
+        <v>1320</v>
       </c>
       <c r="M2" s="58" t="n">
-        <v>0.0104</v>
+        <v>0.0024</v>
       </c>
       <c r="N2" s="4" t="n"/>
       <c r="O2" s="67">
@@ -2464,10 +2464,10 @@
         <v>0.1</v>
       </c>
       <c r="F3" s="61" t="n">
-        <v>0.0527</v>
+        <v>0.0554</v>
       </c>
       <c r="G3" s="61" t="n">
-        <v>-0.0473</v>
+        <v>-0.0446</v>
       </c>
       <c r="H3" s="62" t="n">
         <v>8.696</v>
@@ -2480,17 +2480,17 @@
         <v/>
       </c>
       <c r="K3" s="65" t="n">
-        <v>8.455</v>
+        <v>8.448</v>
       </c>
       <c r="L3" s="66" t="n">
-        <v>-4820</v>
+        <v>-4960</v>
       </c>
       <c r="M3" s="58" t="n">
-        <v>-0.0277</v>
+        <v>-0.0285</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>📊权重预警偏离-4.7%</t>
+          <t>权重预警偏离-4.5%</t>
         </is>
       </c>
       <c r="O3" s="67">
@@ -2521,10 +2521,10 @@
         <v>0.05</v>
       </c>
       <c r="F4" s="61" t="n">
-        <v>0.0332</v>
+        <v>0.0351</v>
       </c>
       <c r="G4" s="61" t="n">
-        <v>-0.0168</v>
+        <v>-0.0149</v>
       </c>
       <c r="H4" s="62" t="n">
         <v>1.838</v>
@@ -2537,13 +2537,13 @@
         <v/>
       </c>
       <c r="K4" s="65" t="n">
-        <v>1.772</v>
+        <v>1.783</v>
       </c>
       <c r="L4" s="66" t="n">
-        <v>-3960</v>
+        <v>-3300</v>
       </c>
       <c r="M4" s="58" t="n">
-        <v>-0.0359</v>
+        <v>-0.0299</v>
       </c>
       <c r="N4" s="4" t="n"/>
       <c r="O4" s="67">
@@ -2574,10 +2574,10 @@
         <v>0.05</v>
       </c>
       <c r="F5" s="70" t="n">
-        <v>0.0814</v>
+        <v>0.0847</v>
       </c>
       <c r="G5" s="70" t="n">
-        <v>0.0314</v>
+        <v>0.0347</v>
       </c>
       <c r="H5" s="71" t="n">
         <v>3.968</v>
@@ -2590,17 +2590,17 @@
         <v/>
       </c>
       <c r="K5" s="65" t="n">
-        <v>4.145</v>
+        <v>4.1</v>
       </c>
       <c r="L5" s="74" t="n">
-        <v>11151</v>
+        <v>8316</v>
       </c>
       <c r="M5" s="75" t="n">
-        <v>0.0446</v>
+        <v>0.0333</v>
       </c>
       <c r="N5" s="41" t="inlineStr">
         <is>
-          <t>📊权重预警偏离+3.1%</t>
+          <t>权重预警偏离+3.5%</t>
         </is>
       </c>
       <c r="O5" s="67" t="n"/>
@@ -2625,10 +2625,10 @@
         <v>0.05</v>
       </c>
       <c r="F6" s="70" t="n">
-        <v>0.0798</v>
+        <v>0.0828</v>
       </c>
       <c r="G6" s="70" t="n">
-        <v>0.0298</v>
+        <v>0.0328</v>
       </c>
       <c r="H6" s="71" t="n">
         <v>1.15</v>
@@ -2641,15 +2641,19 @@
         <v/>
       </c>
       <c r="K6" s="65" t="n">
-        <v>1.173</v>
+        <v>1.158</v>
       </c>
       <c r="L6" s="74" t="n">
-        <v>5014</v>
+        <v>1744</v>
       </c>
       <c r="M6" s="75" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N6" s="41" t="n"/>
+        <v>0.007</v>
+      </c>
+      <c r="N6" s="41" t="inlineStr">
+        <is>
+          <t>权重预警偏离+3.3%</t>
+        </is>
+      </c>
       <c r="O6" s="67" t="n"/>
     </row>
     <row r="7">
@@ -2672,29 +2676,33 @@
         <v>0.1</v>
       </c>
       <c r="F7" s="61" t="n">
-        <v>0</v>
+        <v>0.0331</v>
       </c>
       <c r="G7" s="61" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="H7" s="62" t="n"/>
-      <c r="I7" s="63" t="n"/>
+        <v>-0.0669</v>
+      </c>
+      <c r="H7" s="62" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="I7" s="63" t="n">
+        <v>7200</v>
+      </c>
       <c r="J7" s="64">
         <f>H7*I7</f>
         <v/>
       </c>
       <c r="K7" s="62" t="n">
-        <v>14.083</v>
+        <v>13.999</v>
       </c>
       <c r="L7" s="66" t="n">
-        <v>0</v>
+        <v>352.8</v>
       </c>
       <c r="M7" s="58" t="n">
-        <v>0</v>
+        <v>0.0035</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>🔴再平衡紧急线：偏离-10.0% &gt;= ±10%</t>
+          <t>权重预警偏离-6.7%</t>
         </is>
       </c>
       <c r="O7" s="67">
@@ -2722,10 +2730,10 @@
         <v>0.1</v>
       </c>
       <c r="F8" s="70" t="n">
-        <v>0.157</v>
+        <v>0.1653</v>
       </c>
       <c r="G8" s="70" t="n">
-        <v>0.057</v>
+        <v>0.0653</v>
       </c>
       <c r="H8" s="71" t="n">
         <v>135.645</v>
@@ -2738,17 +2746,17 @@
         <v/>
       </c>
       <c r="K8" s="65" t="n">
-        <v>136.078</v>
+        <v>136.133</v>
       </c>
       <c r="L8" s="74" t="n">
-        <v>1602.1</v>
+        <v>1805.6</v>
       </c>
       <c r="M8" s="75" t="n">
-        <v>0.0032</v>
+        <v>0.0036</v>
       </c>
       <c r="N8" s="41" t="inlineStr">
         <is>
-          <t>📊权重预警偏离+5.7%</t>
+          <t>权重预警偏离+6.5%</t>
         </is>
       </c>
       <c r="O8" s="67" t="n"/>
@@ -2773,10 +2781,10 @@
         <v>0.1</v>
       </c>
       <c r="F9" s="70" t="n">
-        <v>0.1544</v>
+        <v>0.1625</v>
       </c>
       <c r="G9" s="70" t="n">
-        <v>0.0544</v>
+        <v>0.0625</v>
       </c>
       <c r="H9" s="71" t="n">
         <v>141.2121</v>
@@ -2789,17 +2797,17 @@
         <v/>
       </c>
       <c r="K9" s="65" t="n">
-        <v>141.464</v>
+        <v>141.504</v>
       </c>
       <c r="L9" s="74" t="n">
-        <v>881.65</v>
+        <v>1021.65</v>
       </c>
       <c r="M9" s="75" t="n">
-        <v>0.0018</v>
+        <v>0.0021</v>
       </c>
       <c r="N9" s="41" t="inlineStr">
         <is>
-          <t>📊权重预警偏离+5.4%</t>
+          <t>权重预警偏离+6.2%</t>
         </is>
       </c>
       <c r="O9" s="67" t="n"/>
@@ -2824,10 +2832,10 @@
         <v>0.05</v>
       </c>
       <c r="F10" s="70" t="n">
-        <v>0.0779</v>
+        <v>0.082</v>
       </c>
       <c r="G10" s="70" t="n">
-        <v>0.0279</v>
+        <v>0.032</v>
       </c>
       <c r="H10" s="71" t="n">
         <v>113.462</v>
@@ -2840,15 +2848,19 @@
         <v/>
       </c>
       <c r="K10" s="65" t="n">
-        <v>113.528</v>
+        <v>113.535</v>
       </c>
       <c r="L10" s="74" t="n">
-        <v>145.2</v>
+        <v>160.6</v>
       </c>
       <c r="M10" s="75" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="N10" s="41" t="n"/>
+      <c r="N10" s="41" t="inlineStr">
+        <is>
+          <t>权重预警偏离+3.2%</t>
+        </is>
+      </c>
       <c r="O10" s="67" t="n"/>
     </row>
     <row r="11">
@@ -2871,10 +2883,10 @@
         <v>0.15</v>
       </c>
       <c r="F11" s="61" t="n">
-        <v>0.1152</v>
+        <v>0.1213</v>
       </c>
       <c r="G11" s="61" t="n">
-        <v>-0.0348</v>
+        <v>-0.0287</v>
       </c>
       <c r="H11" s="62" t="n">
         <v>9.396599999999999</v>
@@ -2887,19 +2899,15 @@
         <v/>
       </c>
       <c r="K11" s="65" t="n">
-        <v>9.281000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="L11" s="66" t="n">
-        <v>-4600.88</v>
+        <v>-4242.68</v>
       </c>
       <c r="M11" s="58" t="n">
-        <v>-0.0123</v>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>📊权重预警偏离-3.5%</t>
-        </is>
-      </c>
+        <v>-0.0113</v>
+      </c>
+      <c r="N11" s="4" t="n"/>
       <c r="O11" s="67">
         <f>D11-J11</f>
         <v/>
@@ -2937,7 +2945,7 @@
         <v/>
       </c>
       <c r="K12" s="62" t="n">
-        <v>100.501</v>
+        <v>100.512</v>
       </c>
       <c r="L12" s="66" t="n">
         <v>0</v>
@@ -2947,7 +2955,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>📊权重预警偏离-5.0%</t>
+          <t>权重预警偏离-5.0%</t>
         </is>
       </c>
       <c r="O12" s="67">
@@ -2975,31 +2983,31 @@
         <v>0.05</v>
       </c>
       <c r="F13" s="61" t="n">
-        <v>0.078</v>
+        <v>0</v>
       </c>
       <c r="G13" s="61" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="H13" s="62" t="n">
-        <v>99.997</v>
-      </c>
-      <c r="I13" s="63" t="n">
-        <v>2500</v>
-      </c>
+        <v>-0.05</v>
+      </c>
+      <c r="H13" s="62" t="n"/>
+      <c r="I13" s="63" t="n"/>
       <c r="J13" s="64">
         <f>H13*I13</f>
         <v/>
       </c>
       <c r="K13" s="65" t="n">
-        <v>100</v>
+        <v>100.001</v>
       </c>
       <c r="L13" s="66" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M13" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="4" t="n"/>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>权重预警偏离-5.0%</t>
+        </is>
+      </c>
       <c r="O13" s="67" t="n"/>
     </row>
     <row r="14">
@@ -3042,7 +3050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="20.8148148148148" customWidth="1" style="76" min="1" max="1"/>
@@ -3502,6 +3510,60 @@
       </c>
       <c r="F17" s="64" t="n">
         <v>249992.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>511380</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>可转债ETF</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>7200</v>
+      </c>
+      <c r="F18" s="0">
+        <f>D18*E18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>511990</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>华宝添益ETF</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>100.005</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="F19">
+        <f>D19*E19</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3516,7 +3578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q127"/>
+  <dimension ref="A1:Q139"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.8148148148148" customWidth="1" style="1" min="1" max="1"/>
@@ -10774,6 +10836,378 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="0" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B128" s="0" t="inlineStr">
+        <is>
+          <t>沪深300ETF</t>
+        </is>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="H128" s="0" t="n">
+        <v>4.926</v>
+      </c>
+      <c r="I128" s="0" t="n">
+        <v>1320</v>
+      </c>
+      <c r="J128" s="0" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="N128" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B129" s="0" t="inlineStr">
+        <is>
+          <t>中证500ETF</t>
+        </is>
+      </c>
+      <c r="C129" s="0" t="inlineStr">
+        <is>
+          <t>510500</t>
+        </is>
+      </c>
+      <c r="H129" s="0" t="n">
+        <v>8.448</v>
+      </c>
+      <c r="I129" s="0" t="n">
+        <v>-4960</v>
+      </c>
+      <c r="J129" s="0" t="n">
+        <v>-0.0285</v>
+      </c>
+      <c r="N129" s="0" t="inlineStr">
+        <is>
+          <t>权重预警偏离-4.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B130" s="0" t="inlineStr">
+        <is>
+          <t>科创50ETF</t>
+        </is>
+      </c>
+      <c r="C130" s="0" t="inlineStr">
+        <is>
+          <t>588050</t>
+        </is>
+      </c>
+      <c r="H130" s="0" t="n">
+        <v>1.783</v>
+      </c>
+      <c r="I130" s="0" t="n">
+        <v>-3300</v>
+      </c>
+      <c r="J130" s="0" t="n">
+        <v>-0.0299</v>
+      </c>
+      <c r="N130" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B131" s="0" t="inlineStr">
+        <is>
+          <t>创业板ETF</t>
+        </is>
+      </c>
+      <c r="C131" s="0" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="H131" s="0" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I131" s="0" t="n">
+        <v>8316</v>
+      </c>
+      <c r="J131" s="0" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="N131" s="0" t="inlineStr">
+        <is>
+          <t>权重预警偏离+3.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B132" s="0" t="inlineStr">
+        <is>
+          <t>红利低波ETF</t>
+        </is>
+      </c>
+      <c r="C132" s="0" t="inlineStr">
+        <is>
+          <t>512890</t>
+        </is>
+      </c>
+      <c r="H132" s="0" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="I132" s="0" t="n">
+        <v>1744</v>
+      </c>
+      <c r="J132" s="0" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="N132" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B133" s="0" t="inlineStr">
+        <is>
+          <t>可转债ETF</t>
+        </is>
+      </c>
+      <c r="C133" s="0" t="inlineStr">
+        <is>
+          <t>511380</t>
+        </is>
+      </c>
+      <c r="H133" s="0" t="n">
+        <v>13.999</v>
+      </c>
+      <c r="I133" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" s="0" t="inlineStr">
+        <is>
+          <t>再平衡紧急:偏离&gt;=+-10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B134" s="0" t="inlineStr">
+        <is>
+          <t>10年国债ETF</t>
+        </is>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t>511260</t>
+        </is>
+      </c>
+      <c r="H134" s="0" t="n">
+        <v>136.133</v>
+      </c>
+      <c r="I134" s="0" t="n">
+        <v>1805.6</v>
+      </c>
+      <c r="J134" s="0" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="N134" s="0" t="inlineStr">
+        <is>
+          <t>权重预警偏离+5.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B135" s="0" t="inlineStr">
+        <is>
+          <t>5年国债ETF</t>
+        </is>
+      </c>
+      <c r="C135" s="0" t="inlineStr">
+        <is>
+          <t>511010</t>
+        </is>
+      </c>
+      <c r="H135" s="0" t="n">
+        <v>141.504</v>
+      </c>
+      <c r="I135" s="0" t="n">
+        <v>1021.65</v>
+      </c>
+      <c r="J135" s="0" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="N135" s="0" t="inlineStr">
+        <is>
+          <t>权重预警偏离+5.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B136" s="0" t="inlineStr">
+        <is>
+          <t>短融ETF</t>
+        </is>
+      </c>
+      <c r="C136" s="0" t="inlineStr">
+        <is>
+          <t>511360</t>
+        </is>
+      </c>
+      <c r="H136" s="0" t="n">
+        <v>113.535</v>
+      </c>
+      <c r="I136" s="0" t="n">
+        <v>160.6</v>
+      </c>
+      <c r="J136" s="0" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="N136" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B137" s="0" t="inlineStr">
+        <is>
+          <t>黄金ETF</t>
+        </is>
+      </c>
+      <c r="C137" s="0" t="inlineStr">
+        <is>
+          <t>518880</t>
+        </is>
+      </c>
+      <c r="H137" s="0" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="I137" s="0" t="n">
+        <v>-4242.68</v>
+      </c>
+      <c r="J137" s="0" t="n">
+        <v>-0.0113</v>
+      </c>
+      <c r="N137" s="0" t="inlineStr">
+        <is>
+          <t>权重预警偏离-3.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B138" s="0" t="inlineStr">
+        <is>
+          <t>银华日利ETF</t>
+        </is>
+      </c>
+      <c r="C138" s="0" t="inlineStr">
+        <is>
+          <t>511880</t>
+        </is>
+      </c>
+      <c r="H138" s="0" t="n">
+        <v>100.512</v>
+      </c>
+      <c r="I138" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" s="0" t="inlineStr">
+        <is>
+          <t>权重预警偏离-5.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B139" s="0" t="inlineStr">
+        <is>
+          <t>华宝添益ETF</t>
+        </is>
+      </c>
+      <c r="C139" s="0" t="inlineStr">
+        <is>
+          <t>511990</t>
+        </is>
+      </c>
+      <c r="H139" s="0" t="n">
+        <v>100.001</v>
+      </c>
+      <c r="I139" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J139" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/500万资产配置组合2026.xlsx
+++ b/500万资产配置组合2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="9060" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="9060" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="投资纪要" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日报" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'流水'!$A$1:$F$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'流水'!$A$1:$F$20</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??.00_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -29,6 +29,7 @@
     <numFmt numFmtId="169" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??.0_ ;_ @_ "/>
     <numFmt numFmtId="170" formatCode="0.0000%"/>
     <numFmt numFmtId="171" formatCode="0.000%"/>
+    <numFmt numFmtId="172" formatCode="0.0000"/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -721,7 +722,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -935,6 +936,15 @@
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2416,11 +2426,11 @@
       <c r="G2" s="61" t="n">
         <v>0.0278</v>
       </c>
-      <c r="H2" s="62" t="n">
-        <v>4.9042</v>
+      <c r="H2" s="82" t="n">
+        <v>4.885</v>
       </c>
       <c r="I2" s="63" t="n">
-        <v>130000</v>
+        <v>153800</v>
       </c>
       <c r="J2" s="64">
         <f>H2*I2</f>
@@ -2888,11 +2898,11 @@
       <c r="G11" s="61" t="n">
         <v>-0.0287</v>
       </c>
-      <c r="H11" s="62" t="n">
-        <v>9.396599999999999</v>
+      <c r="H11" s="82" t="n">
+        <v>9.3302</v>
       </c>
       <c r="I11" s="63" t="n">
-        <v>39800</v>
+        <v>47800</v>
       </c>
       <c r="J11" s="64">
         <f>H11*I11</f>
@@ -3053,7 +3063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="20.8148148148148" customWidth="1" style="76" min="1" max="1"/>
@@ -3570,32 +3580,86 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="77" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="5" t="n">
         <v>510300</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>华泰柏瑞沪深300ETF</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="78" t="n">
         <v>4.85</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="63" t="n">
         <v>20000</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="64">
         <f>D20*E20</f>
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="80" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B21" s="81" t="inlineStr">
+        <is>
+          <t>518880</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>华安黄金ETF</t>
+        </is>
+      </c>
+      <c r="D21" s="50" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" s="52" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F21" s="53">
+        <f>D21*E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="80" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B22" s="81" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>国泰沪深300ETF</t>
+        </is>
+      </c>
+      <c r="D22" s="50" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="E22" s="52" t="n">
+        <v>23800</v>
+      </c>
+      <c r="F22" s="53">
+        <f>D22*E22</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F19"/>
+  <autoFilter ref="A1:F20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/500万资产配置组合2026.xlsx
+++ b/500万资产配置组合2026.xlsx
@@ -13,7 +13,7 @@
     <sheet name="日报" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">流水!$A$1:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">流水!$A$1:$F$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="455">
   <si>
     <t>500万资产配置 -- 投资纪律速查（优化版 2026-05-21）</t>
   </si>
@@ -425,932 +425,986 @@
     <t>建仓计划</t>
   </si>
   <si>
+    <t>沪深300ETF</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离+6.9%</t>
+  </si>
+  <si>
+    <t>南方中证500ETF</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离-5.1%</t>
+  </si>
+  <si>
+    <t>科创50ETF</t>
+  </si>
+  <si>
+    <t>⚡预警：浮亏-7.6% &gt;= -5%，暂停新增买入</t>
+  </si>
+  <si>
+    <t>易方达创业板ETF</t>
+  </si>
+  <si>
+    <t>华泰柏瑞红利低波ETF</t>
+  </si>
+  <si>
+    <t>可转债ETF</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离-4.1%</t>
+  </si>
+  <si>
+    <t>国泰上证10年期国债ETF</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离+4.9%</t>
+  </si>
+  <si>
+    <t>国泰上证5年期国债ETF</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离+4.7%</t>
+  </si>
+  <si>
+    <t>海富通中证短融ETF</t>
+  </si>
+  <si>
+    <t>华安黄金ETF</t>
+  </si>
+  <si>
+    <t>银华日利ETF</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离-5.0%</t>
+  </si>
+  <si>
+    <t>华宝添益ETF</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>单价</t>
+  </si>
+  <si>
+    <t>金额</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>511360</t>
+  </si>
+  <si>
+    <t>短融ETF</t>
+  </si>
+  <si>
+    <t>518880</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>511010</t>
+  </si>
+  <si>
+    <t>五年国债ETF</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>511260</t>
+  </si>
+  <si>
+    <t>十年国债ETF</t>
+  </si>
+  <si>
+    <t>510300</t>
+  </si>
+  <si>
+    <t>159915</t>
+  </si>
+  <si>
+    <t>创业板ETF</t>
+  </si>
+  <si>
+    <t>510500</t>
+  </si>
+  <si>
+    <t>中证500ETF</t>
+  </si>
+  <si>
+    <t>588050</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>511380</t>
+  </si>
+  <si>
+    <t>511990</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>品种</t>
+  </si>
+  <si>
+    <t>持仓股数</t>
+  </si>
+  <si>
+    <t>持仓成本</t>
+  </si>
+  <si>
+    <t>今日收盘</t>
+  </si>
+  <si>
+    <t>涨跌幅</t>
+  </si>
+  <si>
+    <t>当前市值</t>
+  </si>
+  <si>
+    <t>浮动盈亏</t>
+  </si>
+  <si>
+    <t>盈亏%</t>
+  </si>
+  <si>
+    <t>实际权重</t>
+  </si>
+  <si>
+    <t>触发信号</t>
+  </si>
+  <si>
+    <t>五年国债</t>
+  </si>
+  <si>
+    <t>511010.SH</t>
+  </si>
+  <si>
+    <t>+0.09%</t>
+  </si>
+  <si>
+    <t>-0.00%</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>2.26%</t>
+  </si>
+  <si>
+    <t>-7.7%</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>短融</t>
+  </si>
+  <si>
+    <t>511360.SH</t>
+  </si>
+  <si>
+    <t>+0.01%</t>
+  </si>
+  <si>
+    <t>0.01%</t>
+  </si>
+  <si>
+    <t>5%</t>
+  </si>
+  <si>
+    <t>4.99%</t>
+  </si>
+  <si>
+    <t>-0.0%</t>
+  </si>
+  <si>
+    <t>黄金</t>
+  </si>
+  <si>
+    <t>518880.SH</t>
+  </si>
+  <si>
+    <t>+0.02%</t>
+  </si>
+  <si>
+    <t>0.18%</t>
+  </si>
+  <si>
+    <t>15%</t>
+  </si>
+  <si>
+    <t>3.01%</t>
+  </si>
+  <si>
+    <t>-12.0%</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>0.05%</t>
+  </si>
+  <si>
+    <t>10.42%</t>
+  </si>
+  <si>
+    <t>+0.4%</t>
+  </si>
+  <si>
+    <t>0.02%</t>
+  </si>
+  <si>
+    <t>5.26%</t>
+  </si>
+  <si>
+    <t>+0.3%</t>
+  </si>
+  <si>
+    <t>-1.56%</t>
+  </si>
+  <si>
+    <t>-1.38%</t>
+  </si>
+  <si>
+    <t>3.12%</t>
+  </si>
+  <si>
+    <t>-11.9%</t>
+  </si>
+  <si>
+    <t>沪深300</t>
+  </si>
+  <si>
+    <t>510300.SH</t>
+  </si>
+  <si>
+    <t>-1.29%</t>
+  </si>
+  <si>
+    <t>-2.16%</t>
+  </si>
+  <si>
+    <t>10.63%</t>
+  </si>
+  <si>
+    <t>-4.4%</t>
+  </si>
+  <si>
+    <t>中证500</t>
+  </si>
+  <si>
+    <t>510500.SH</t>
+  </si>
+  <si>
+    <t>-2.80%</t>
+  </si>
+  <si>
+    <t>-2.22%</t>
+  </si>
+  <si>
+    <t>3.42%</t>
+  </si>
+  <si>
+    <t>-6.6%</t>
+  </si>
+  <si>
+    <t>科创50</t>
+  </si>
+  <si>
+    <t>588050.SH</t>
+  </si>
+  <si>
+    <t>-3.67%</t>
+  </si>
+  <si>
+    <t>-1.47%</t>
+  </si>
+  <si>
+    <t>2.18%</t>
+  </si>
+  <si>
+    <t>-2.8%</t>
+  </si>
+  <si>
+    <t>创业板</t>
+  </si>
+  <si>
+    <t>159915.SZ</t>
+  </si>
+  <si>
+    <t>-2.19%</t>
+  </si>
+  <si>
+    <t>-3.07%</t>
+  </si>
+  <si>
+    <t>4.87%</t>
+  </si>
+  <si>
+    <t>-0.1%</t>
+  </si>
+  <si>
+    <t>十年国债</t>
+  </si>
+  <si>
+    <t>511260.SH</t>
+  </si>
+  <si>
+    <t>-0.09%</t>
+  </si>
+  <si>
+    <t>10.08%</t>
+  </si>
+  <si>
+    <t>+0.1%</t>
+  </si>
+  <si>
+    <t>-0.06%</t>
+  </si>
+  <si>
+    <t>-0.01%</t>
+  </si>
+  <si>
+    <t>9.94%</t>
+  </si>
+  <si>
+    <t>5.02%</t>
+  </si>
+  <si>
+    <t>+0.0%</t>
+  </si>
+  <si>
+    <t>+0.89%</t>
+  </si>
+  <si>
+    <t>-0.51%</t>
+  </si>
+  <si>
+    <t>3.00%</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>+1.12%</t>
+  </si>
+  <si>
+    <t>-1.06%</t>
+  </si>
+  <si>
+    <t>10.72%</t>
+  </si>
+  <si>
+    <t>-4.3%</t>
+  </si>
+  <si>
+    <t>+1.82%</t>
+  </si>
+  <si>
+    <t>-0.44%</t>
+  </si>
+  <si>
+    <t>3.47%</t>
+  </si>
+  <si>
+    <t>-6.5%</t>
+  </si>
+  <si>
+    <t>+1.49%</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
+    <t>2.21%</t>
+  </si>
+  <si>
+    <t>+2.60%</t>
+  </si>
+  <si>
+    <t>-0.55%</t>
+  </si>
+  <si>
+    <t>4.98%</t>
+  </si>
+  <si>
+    <t>-0.03%</t>
+  </si>
+  <si>
+    <t>-0.13%</t>
+  </si>
+  <si>
+    <t>10.04%</t>
+  </si>
+  <si>
+    <t>9.90%</t>
+  </si>
+  <si>
+    <t>0.03%</t>
+  </si>
+  <si>
+    <t>5.00%</t>
+  </si>
+  <si>
+    <t>+0.12%</t>
+  </si>
+  <si>
+    <t>-0.39%</t>
+  </si>
+  <si>
+    <t>+1.54%</t>
+  </si>
+  <si>
+    <t>0.47%</t>
+  </si>
+  <si>
+    <t>10.83%</t>
+  </si>
+  <si>
+    <t>-4.2%</t>
+  </si>
+  <si>
+    <t>+1.48%</t>
+  </si>
+  <si>
+    <t>1.03%</t>
+  </si>
+  <si>
+    <t>3.50%</t>
+  </si>
+  <si>
+    <t>+5.60%</t>
+  </si>
+  <si>
+    <t>5.60%</t>
+  </si>
+  <si>
+    <t>2.32%</t>
+  </si>
+  <si>
+    <t>-2.7%</t>
+  </si>
+  <si>
+    <t>+2.23%</t>
+  </si>
+  <si>
+    <t>1.66%</t>
+  </si>
+  <si>
+    <t>5.07%</t>
+  </si>
+  <si>
+    <t>+0.04%</t>
+  </si>
+  <si>
+    <t>10.00%</t>
+  </si>
+  <si>
+    <t>-0.02%</t>
+  </si>
+  <si>
+    <t>9.85%</t>
+  </si>
+  <si>
+    <t>+0.00%</t>
+  </si>
+  <si>
+    <t>+0.54%</t>
+  </si>
+  <si>
+    <t>0.15%</t>
+  </si>
+  <si>
+    <t>+0.71%</t>
+  </si>
+  <si>
+    <t>1.18%</t>
+  </si>
+  <si>
+    <t>10.90%</t>
+  </si>
+  <si>
+    <t>-4.1%</t>
+  </si>
+  <si>
+    <t>0.64%</t>
+  </si>
+  <si>
+    <t>3.49%</t>
+  </si>
+  <si>
+    <t>-1.24%</t>
+  </si>
+  <si>
+    <t>4.30%</t>
+  </si>
+  <si>
+    <t>2.29%</t>
+  </si>
+  <si>
+    <t>+0.52%</t>
+  </si>
+  <si>
+    <t>2.19%</t>
+  </si>
+  <si>
+    <t>5.09%</t>
+  </si>
+  <si>
+    <t>红利低波</t>
+  </si>
+  <si>
+    <t>512890.SH</t>
+  </si>
+  <si>
+    <t>+0.35%</t>
+  </si>
+  <si>
+    <t>0.52%</t>
+  </si>
+  <si>
+    <t>+0.05%</t>
+  </si>
+  <si>
+    <t>-0.04%</t>
+  </si>
+  <si>
+    <t>0.04%</t>
+  </si>
+  <si>
+    <t>-0.61%</t>
+  </si>
+  <si>
+    <t>-0.31%</t>
+  </si>
+  <si>
+    <t>4.48%</t>
+  </si>
+  <si>
+    <t>-10.5%</t>
+  </si>
+  <si>
+    <t>-0.80%</t>
+  </si>
+  <si>
+    <t>0.37%</t>
+  </si>
+  <si>
+    <t>10.84%</t>
+  </si>
+  <si>
+    <t>-1.58%</t>
+  </si>
+  <si>
+    <t>-0.94%</t>
+  </si>
+  <si>
+    <t>3.44%</t>
+  </si>
+  <si>
+    <t>-2.82%</t>
+  </si>
+  <si>
+    <t>1.36%</t>
+  </si>
+  <si>
+    <t>2.23%</t>
+  </si>
+  <si>
+    <t>2.22%</t>
+  </si>
+  <si>
+    <t>5.11%</t>
+  </si>
+  <si>
+    <t>-0.52%</t>
+  </si>
+  <si>
+    <t>5.01%</t>
+  </si>
+  <si>
+    <t>+0.14%</t>
+  </si>
+  <si>
+    <t>0.10%</t>
+  </si>
+  <si>
+    <t>0.06%</t>
+  </si>
+  <si>
+    <t>9.88%</t>
+  </si>
+  <si>
+    <t>-1.15%</t>
+  </si>
+  <si>
+    <t>-1.20%</t>
+  </si>
+  <si>
+    <t>5.94%</t>
+  </si>
+  <si>
+    <t>-9.1%</t>
+  </si>
+  <si>
+    <t>+0.41%</t>
+  </si>
+  <si>
+    <t>-0.54%</t>
+  </si>
+  <si>
+    <t>3.46%</t>
+  </si>
+  <si>
+    <t>+1.56%</t>
+  </si>
+  <si>
+    <t>2.94%</t>
+  </si>
+  <si>
+    <t>2.27%</t>
+  </si>
+  <si>
+    <t>+2.02%</t>
+  </si>
+  <si>
+    <t>4.28%</t>
+  </si>
+  <si>
+    <t>5.21%</t>
+  </si>
+  <si>
+    <t>+0.2%</t>
+  </si>
+  <si>
+    <t>0.24%</t>
+  </si>
+  <si>
+    <t>10.05%</t>
+  </si>
+  <si>
+    <t>+0.08%</t>
+  </si>
+  <si>
+    <t>9.89%</t>
+  </si>
+  <si>
+    <t>-2.28%</t>
+  </si>
+  <si>
+    <t>7.26%</t>
+  </si>
+  <si>
+    <t>华宝添益</t>
+  </si>
+  <si>
+    <t>511990.SH</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>-0.18%</t>
+  </si>
+  <si>
+    <t>10.82%</t>
+  </si>
+  <si>
+    <t>-2.38%</t>
+  </si>
+  <si>
+    <t>-2.91%</t>
+  </si>
+  <si>
+    <t>3.37%</t>
+  </si>
+  <si>
+    <t>-5.18%</t>
+  </si>
+  <si>
+    <t>-2.39%</t>
+  </si>
+  <si>
+    <t>2.15%</t>
+  </si>
+  <si>
+    <t>-2.05%</t>
+  </si>
+  <si>
+    <t>2.14%</t>
+  </si>
+  <si>
+    <t>5.10%</t>
+  </si>
+  <si>
+    <t>+2.01%</t>
+  </si>
+  <si>
+    <t>1.48%</t>
+  </si>
+  <si>
+    <t>5.08%</t>
+  </si>
+  <si>
+    <t>0.27%</t>
+  </si>
+  <si>
+    <t>+0.06%</t>
+  </si>
+  <si>
+    <t>0.20%</t>
+  </si>
+  <si>
+    <t>+2.90%</t>
+  </si>
+  <si>
+    <t>7.47%</t>
+  </si>
+  <si>
+    <t>-7.5%</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>-1.12%</t>
+  </si>
+  <si>
+    <t>10.74%</t>
+  </si>
+  <si>
+    <t>-0.87%</t>
+  </si>
+  <si>
+    <t>-3.75%</t>
+  </si>
+  <si>
+    <t>3.36%</t>
+  </si>
+  <si>
+    <t>-4.85%</t>
+  </si>
+  <si>
+    <t>-7.13%</t>
+  </si>
+  <si>
+    <t>2.05%</t>
+  </si>
+  <si>
+    <t>-2.9%</t>
+  </si>
+  <si>
+    <t>预警</t>
+  </si>
+  <si>
+    <t>-2.20%</t>
+  </si>
+  <si>
+    <t>-0.10%</t>
+  </si>
+  <si>
+    <t>+1.20%</t>
+  </si>
+  <si>
+    <t>2.70%</t>
+  </si>
+  <si>
+    <t>5.16%</t>
+  </si>
+  <si>
+    <t>0.33%</t>
+  </si>
+  <si>
+    <t>10.10%</t>
+  </si>
+  <si>
+    <t>0.21%</t>
+  </si>
+  <si>
+    <t>9.93%</t>
+  </si>
+  <si>
+    <t>-0.56%</t>
+  </si>
+  <si>
+    <t>7.46%</t>
+  </si>
+  <si>
+    <t>20260601</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离-4.3%</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离-6.6%</t>
+  </si>
+  <si>
+    <t>⚡预警：浮亏-7.1% &gt;= -5%，暂停新增买入</t>
+  </si>
+  <si>
+    <t>红利低波ETF</t>
+  </si>
+  <si>
+    <t>512890</t>
+  </si>
+  <si>
+    <t>10年国债ETF</t>
+  </si>
+  <si>
+    <t>5年国债ETF</t>
+  </si>
+  <si>
+    <t>黄金ETF</t>
+  </si>
+  <si>
+    <t>⚠️权重触发线偏离-7.5%</t>
+  </si>
+  <si>
+    <t>511880</t>
+  </si>
+  <si>
+    <t>20260602</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离-4.2%</t>
+  </si>
+  <si>
+    <t>⚡预警：浮亏-5.7% &gt;= -5%，暂停新增买入</t>
+  </si>
+  <si>
+    <t>20260603</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离-4.7%</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离+3.1%</t>
+  </si>
+  <si>
+    <t>🔴再平衡紧急线：偏离-10.0% &gt;= ±10%</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离+5.7%</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离+5.4%</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离-3.5%</t>
+  </si>
+  <si>
+    <t>20260604</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>权重预警偏离-4.7%</t>
+  </si>
+  <si>
+    <t>权重预警偏离+3.1%</t>
+  </si>
+  <si>
+    <t>再平衡紧急:偏离&gt;=+-10%</t>
+  </si>
+  <si>
+    <t>权重预警偏离+5.8%</t>
+  </si>
+  <si>
+    <t>权重预警偏离+5.5%</t>
+  </si>
+  <si>
+    <t>权重预警偏离-3.4%</t>
+  </si>
+  <si>
+    <t>权重预警偏离-5.0%</t>
+  </si>
+  <si>
+    <t>20260609</t>
+  </si>
+  <si>
+    <t>🟠再平衡触发线：偏离+7.6% &gt;= ±7%，强制调仓</t>
+  </si>
+  <si>
+    <t>⚡预警：浮亏-7.2% &gt;= -5%，暂停新增买入</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离-7.0%</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离+5.3%</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离+5.0%</t>
+  </si>
+  <si>
+    <t>20260610</t>
+  </si>
+  <si>
     <t>华泰柏瑞沪深300ETF</t>
   </si>
   <si>
-    <t>🟠再平衡触发线：偏离+7.6% &gt;= ±7%，强制调仓</t>
-  </si>
-  <si>
-    <t>南方中证500ETF</t>
-  </si>
-  <si>
-    <t>📊权重预警偏离-5.0%</t>
-  </si>
-  <si>
-    <t>科创50ETF</t>
-  </si>
-  <si>
-    <t>⚡预警：浮亏-7.2% &gt;= -5%，暂停新增买入</t>
-  </si>
-  <si>
-    <t>易方达创业板ETF</t>
-  </si>
-  <si>
-    <t>华泰柏瑞红利低波ETF</t>
-  </si>
-  <si>
-    <t>可转债ETF</t>
-  </si>
-  <si>
-    <t>📊权重预警偏离-7.0%</t>
-  </si>
-  <si>
-    <t>国泰上证10年期国债ETF</t>
-  </si>
-  <si>
-    <t>📊权重预警偏离+5.3%</t>
-  </si>
-  <si>
-    <t>国泰上证5年期国债ETF</t>
-  </si>
-  <si>
-    <t>📊权重预警偏离+5.0%</t>
-  </si>
-  <si>
-    <t>海富通中证短融ETF</t>
-  </si>
-  <si>
-    <t>华安黄金ETF</t>
-  </si>
-  <si>
-    <t>银华日利ETF</t>
-  </si>
-  <si>
-    <t>华宝添益ETF</t>
-  </si>
-  <si>
-    <t>日期</t>
-  </si>
-  <si>
-    <t>单价</t>
-  </si>
-  <si>
-    <t>金额</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>511360</t>
-  </si>
-  <si>
-    <t>短融ETF</t>
-  </si>
-  <si>
-    <t>518880</t>
-  </si>
-  <si>
-    <t>2026-05-19</t>
-  </si>
-  <si>
-    <t>511010</t>
-  </si>
-  <si>
-    <t>五年国债ETF</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>511260</t>
-  </si>
-  <si>
-    <t>十年国债ETF</t>
-  </si>
-  <si>
-    <t>510300</t>
-  </si>
-  <si>
-    <t>沪深300ETF</t>
-  </si>
-  <si>
-    <t>159915</t>
-  </si>
-  <si>
-    <t>创业板ETF</t>
-  </si>
-  <si>
-    <t>510500</t>
-  </si>
-  <si>
-    <t>中证500ETF</t>
-  </si>
-  <si>
-    <t>588050</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
-    <t>2026-05-27</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>511380</t>
-  </si>
-  <si>
-    <t>511990</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>国泰沪深300ETF</t>
-  </si>
-  <si>
-    <t>品种</t>
-  </si>
-  <si>
-    <t>持仓股数</t>
-  </si>
-  <si>
-    <t>持仓成本</t>
-  </si>
-  <si>
-    <t>今日收盘</t>
-  </si>
-  <si>
-    <t>涨跌幅</t>
-  </si>
-  <si>
-    <t>当前市值</t>
-  </si>
-  <si>
-    <t>浮动盈亏</t>
-  </si>
-  <si>
-    <t>盈亏%</t>
-  </si>
-  <si>
-    <t>实际权重</t>
-  </si>
-  <si>
-    <t>触发信号</t>
-  </si>
-  <si>
-    <t>五年国债</t>
-  </si>
-  <si>
-    <t>511010.SH</t>
-  </si>
-  <si>
-    <t>+0.09%</t>
-  </si>
-  <si>
-    <t>-0.00%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>2.26%</t>
-  </si>
-  <si>
-    <t>-7.7%</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>短融</t>
-  </si>
-  <si>
-    <t>511360.SH</t>
-  </si>
-  <si>
-    <t>+0.01%</t>
-  </si>
-  <si>
-    <t>0.01%</t>
-  </si>
-  <si>
-    <t>5%</t>
-  </si>
-  <si>
-    <t>4.99%</t>
-  </si>
-  <si>
-    <t>-0.0%</t>
-  </si>
-  <si>
-    <t>黄金</t>
-  </si>
-  <si>
-    <t>518880.SH</t>
-  </si>
-  <si>
-    <t>+0.02%</t>
-  </si>
-  <si>
-    <t>0.18%</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>3.01%</t>
-  </si>
-  <si>
-    <t>-12.0%</t>
-  </si>
-  <si>
-    <t>2026-05-20</t>
-  </si>
-  <si>
-    <t>0.05%</t>
-  </si>
-  <si>
-    <t>10.42%</t>
-  </si>
-  <si>
-    <t>+0.4%</t>
-  </si>
-  <si>
-    <t>0.02%</t>
-  </si>
-  <si>
-    <t>5.26%</t>
-  </si>
-  <si>
-    <t>+0.3%</t>
-  </si>
-  <si>
-    <t>-1.56%</t>
-  </si>
-  <si>
-    <t>-1.38%</t>
-  </si>
-  <si>
-    <t>3.12%</t>
-  </si>
-  <si>
-    <t>-11.9%</t>
-  </si>
-  <si>
-    <t>沪深300</t>
-  </si>
-  <si>
-    <t>510300.SH</t>
-  </si>
-  <si>
-    <t>-1.29%</t>
-  </si>
-  <si>
-    <t>-2.16%</t>
-  </si>
-  <si>
-    <t>10.63%</t>
-  </si>
-  <si>
-    <t>-4.4%</t>
-  </si>
-  <si>
-    <t>中证500</t>
-  </si>
-  <si>
-    <t>510500.SH</t>
-  </si>
-  <si>
-    <t>-2.80%</t>
-  </si>
-  <si>
-    <t>-2.22%</t>
-  </si>
-  <si>
-    <t>3.42%</t>
-  </si>
-  <si>
-    <t>-6.6%</t>
-  </si>
-  <si>
-    <t>科创50</t>
-  </si>
-  <si>
-    <t>588050.SH</t>
-  </si>
-  <si>
-    <t>-3.67%</t>
-  </si>
-  <si>
-    <t>-1.47%</t>
-  </si>
-  <si>
-    <t>2.18%</t>
-  </si>
-  <si>
-    <t>-2.8%</t>
-  </si>
-  <si>
-    <t>创业板</t>
-  </si>
-  <si>
-    <t>159915.SZ</t>
-  </si>
-  <si>
-    <t>-2.19%</t>
-  </si>
-  <si>
-    <t>-3.07%</t>
-  </si>
-  <si>
-    <t>4.87%</t>
-  </si>
-  <si>
-    <t>-0.1%</t>
-  </si>
-  <si>
-    <t>十年国债</t>
-  </si>
-  <si>
-    <t>511260.SH</t>
-  </si>
-  <si>
-    <t>-0.09%</t>
-  </si>
-  <si>
-    <t>10.08%</t>
-  </si>
-  <si>
-    <t>+0.1%</t>
-  </si>
-  <si>
-    <t>-0.06%</t>
-  </si>
-  <si>
-    <t>-0.01%</t>
-  </si>
-  <si>
-    <t>9.94%</t>
-  </si>
-  <si>
-    <t>5.02%</t>
-  </si>
-  <si>
-    <t>+0.0%</t>
-  </si>
-  <si>
-    <t>+0.89%</t>
-  </si>
-  <si>
-    <t>-0.51%</t>
-  </si>
-  <si>
-    <t>3.00%</t>
-  </si>
-  <si>
-    <t>2026-05-22</t>
-  </si>
-  <si>
-    <t>+1.12%</t>
-  </si>
-  <si>
-    <t>-1.06%</t>
-  </si>
-  <si>
-    <t>10.72%</t>
-  </si>
-  <si>
-    <t>-4.3%</t>
-  </si>
-  <si>
-    <t>+1.82%</t>
-  </si>
-  <si>
-    <t>-0.44%</t>
-  </si>
-  <si>
-    <t>3.47%</t>
-  </si>
-  <si>
-    <t>-6.5%</t>
-  </si>
-  <si>
-    <t>+1.49%</t>
-  </si>
-  <si>
-    <t>0.00%</t>
-  </si>
-  <si>
-    <t>2.21%</t>
-  </si>
-  <si>
-    <t>+2.60%</t>
-  </si>
-  <si>
-    <t>-0.55%</t>
-  </si>
-  <si>
-    <t>4.98%</t>
-  </si>
-  <si>
-    <t>-0.03%</t>
-  </si>
-  <si>
-    <t>-0.13%</t>
-  </si>
-  <si>
-    <t>10.04%</t>
-  </si>
-  <si>
-    <t>9.90%</t>
-  </si>
-  <si>
-    <t>0.03%</t>
-  </si>
-  <si>
-    <t>5.00%</t>
-  </si>
-  <si>
-    <t>+0.12%</t>
-  </si>
-  <si>
-    <t>-0.39%</t>
-  </si>
-  <si>
-    <t>+1.54%</t>
-  </si>
-  <si>
-    <t>0.47%</t>
-  </si>
-  <si>
-    <t>10.83%</t>
-  </si>
-  <si>
-    <t>-4.2%</t>
-  </si>
-  <si>
-    <t>+1.48%</t>
-  </si>
-  <si>
-    <t>1.03%</t>
-  </si>
-  <si>
-    <t>3.50%</t>
-  </si>
-  <si>
-    <t>+5.60%</t>
-  </si>
-  <si>
-    <t>5.60%</t>
-  </si>
-  <si>
-    <t>2.32%</t>
-  </si>
-  <si>
-    <t>-2.7%</t>
-  </si>
-  <si>
-    <t>+2.23%</t>
-  </si>
-  <si>
-    <t>1.66%</t>
-  </si>
-  <si>
-    <t>5.07%</t>
-  </si>
-  <si>
-    <t>+0.04%</t>
-  </si>
-  <si>
-    <t>10.00%</t>
-  </si>
-  <si>
-    <t>-0.02%</t>
-  </si>
-  <si>
-    <t>9.85%</t>
-  </si>
-  <si>
-    <t>+0.00%</t>
-  </si>
-  <si>
-    <t>+0.54%</t>
-  </si>
-  <si>
-    <t>0.15%</t>
-  </si>
-  <si>
-    <t>+0.71%</t>
-  </si>
-  <si>
-    <t>1.18%</t>
-  </si>
-  <si>
-    <t>10.90%</t>
-  </si>
-  <si>
-    <t>-4.1%</t>
-  </si>
-  <si>
-    <t>0.64%</t>
-  </si>
-  <si>
-    <t>3.49%</t>
-  </si>
-  <si>
-    <t>-1.24%</t>
-  </si>
-  <si>
-    <t>4.30%</t>
-  </si>
-  <si>
-    <t>2.29%</t>
-  </si>
-  <si>
-    <t>+0.52%</t>
-  </si>
-  <si>
-    <t>2.19%</t>
-  </si>
-  <si>
-    <t>5.09%</t>
-  </si>
-  <si>
-    <t>红利低波</t>
-  </si>
-  <si>
-    <t>512890.SH</t>
-  </si>
-  <si>
-    <t>+0.35%</t>
-  </si>
-  <si>
-    <t>0.52%</t>
-  </si>
-  <si>
-    <t>+0.05%</t>
-  </si>
-  <si>
-    <t>-0.04%</t>
-  </si>
-  <si>
-    <t>0.04%</t>
-  </si>
-  <si>
-    <t>-0.61%</t>
-  </si>
-  <si>
-    <t>-0.31%</t>
-  </si>
-  <si>
-    <t>4.48%</t>
-  </si>
-  <si>
-    <t>-10.5%</t>
-  </si>
-  <si>
-    <t>-0.80%</t>
-  </si>
-  <si>
-    <t>0.37%</t>
-  </si>
-  <si>
-    <t>10.84%</t>
-  </si>
-  <si>
-    <t>-1.58%</t>
-  </si>
-  <si>
-    <t>-0.94%</t>
-  </si>
-  <si>
-    <t>3.44%</t>
-  </si>
-  <si>
-    <t>-2.82%</t>
-  </si>
-  <si>
-    <t>1.36%</t>
-  </si>
-  <si>
-    <t>2.23%</t>
-  </si>
-  <si>
-    <t>2.22%</t>
-  </si>
-  <si>
-    <t>5.11%</t>
-  </si>
-  <si>
-    <t>-0.52%</t>
-  </si>
-  <si>
-    <t>5.01%</t>
-  </si>
-  <si>
-    <t>+0.14%</t>
-  </si>
-  <si>
-    <t>0.10%</t>
-  </si>
-  <si>
-    <t>0.06%</t>
-  </si>
-  <si>
-    <t>9.88%</t>
-  </si>
-  <si>
-    <t>-1.15%</t>
-  </si>
-  <si>
-    <t>-1.20%</t>
-  </si>
-  <si>
-    <t>5.94%</t>
-  </si>
-  <si>
-    <t>-9.1%</t>
-  </si>
-  <si>
-    <t>+0.41%</t>
-  </si>
-  <si>
-    <t>-0.54%</t>
-  </si>
-  <si>
-    <t>3.46%</t>
-  </si>
-  <si>
-    <t>+1.56%</t>
-  </si>
-  <si>
-    <t>2.94%</t>
-  </si>
-  <si>
-    <t>2.27%</t>
-  </si>
-  <si>
-    <t>+2.02%</t>
-  </si>
-  <si>
-    <t>4.28%</t>
-  </si>
-  <si>
-    <t>5.21%</t>
-  </si>
-  <si>
-    <t>+0.2%</t>
-  </si>
-  <si>
-    <t>0.24%</t>
-  </si>
-  <si>
-    <t>10.05%</t>
-  </si>
-  <si>
-    <t>+0.08%</t>
-  </si>
-  <si>
-    <t>9.89%</t>
-  </si>
-  <si>
-    <t>-2.28%</t>
-  </si>
-  <si>
-    <t>7.26%</t>
-  </si>
-  <si>
-    <t>华宝添益</t>
-  </si>
-  <si>
-    <t>511990.SH</t>
-  </si>
-  <si>
-    <t>2026-05-29</t>
-  </si>
-  <si>
-    <t>-0.18%</t>
-  </si>
-  <si>
-    <t>10.82%</t>
-  </si>
-  <si>
-    <t>-2.38%</t>
-  </si>
-  <si>
-    <t>-2.91%</t>
-  </si>
-  <si>
-    <t>3.37%</t>
-  </si>
-  <si>
-    <t>-5.18%</t>
-  </si>
-  <si>
-    <t>-2.39%</t>
-  </si>
-  <si>
-    <t>2.15%</t>
-  </si>
-  <si>
-    <t>-2.05%</t>
-  </si>
-  <si>
-    <t>2.14%</t>
-  </si>
-  <si>
-    <t>5.10%</t>
-  </si>
-  <si>
-    <t>+2.01%</t>
-  </si>
-  <si>
-    <t>1.48%</t>
-  </si>
-  <si>
-    <t>5.08%</t>
-  </si>
-  <si>
-    <t>0.27%</t>
-  </si>
-  <si>
-    <t>+0.06%</t>
-  </si>
-  <si>
-    <t>0.20%</t>
-  </si>
-  <si>
-    <t>+2.90%</t>
-  </si>
-  <si>
-    <t>7.47%</t>
-  </si>
-  <si>
-    <t>-7.5%</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>-1.12%</t>
-  </si>
-  <si>
-    <t>10.74%</t>
-  </si>
-  <si>
-    <t>-0.87%</t>
-  </si>
-  <si>
-    <t>-3.75%</t>
-  </si>
-  <si>
-    <t>3.36%</t>
-  </si>
-  <si>
-    <t>-4.85%</t>
-  </si>
-  <si>
-    <t>-7.13%</t>
-  </si>
-  <si>
-    <t>2.05%</t>
-  </si>
-  <si>
-    <t>-2.9%</t>
-  </si>
-  <si>
-    <t>预警</t>
-  </si>
-  <si>
-    <t>-2.20%</t>
-  </si>
-  <si>
-    <t>-0.10%</t>
-  </si>
-  <si>
-    <t>+1.20%</t>
-  </si>
-  <si>
-    <t>2.70%</t>
-  </si>
-  <si>
-    <t>5.16%</t>
-  </si>
-  <si>
-    <t>0.33%</t>
-  </si>
-  <si>
-    <t>10.10%</t>
-  </si>
-  <si>
-    <t>0.21%</t>
-  </si>
-  <si>
-    <t>9.93%</t>
-  </si>
-  <si>
-    <t>-0.56%</t>
-  </si>
-  <si>
-    <t>7.46%</t>
-  </si>
-  <si>
-    <t>20260601</t>
-  </si>
-  <si>
-    <t>📊权重预警偏离-4.3%</t>
-  </si>
-  <si>
-    <t>📊权重预警偏离-6.6%</t>
-  </si>
-  <si>
-    <t>⚡预警：浮亏-7.1% &gt;= -5%，暂停新增买入</t>
-  </si>
-  <si>
-    <t>红利低波ETF</t>
-  </si>
-  <si>
-    <t>512890</t>
-  </si>
-  <si>
-    <t>10年国债ETF</t>
-  </si>
-  <si>
-    <t>5年国债ETF</t>
-  </si>
-  <si>
-    <t>黄金ETF</t>
-  </si>
-  <si>
-    <t>⚠️权重触发线偏离-7.5%</t>
-  </si>
-  <si>
-    <t>511880</t>
-  </si>
-  <si>
-    <t>20260602</t>
-  </si>
-  <si>
-    <t>📊权重预警偏离-4.2%</t>
-  </si>
-  <si>
-    <t>⚡预警：浮亏-5.7% &gt;= -5%，暂停新增买入</t>
-  </si>
-  <si>
-    <t>20260603</t>
-  </si>
-  <si>
-    <t>📊权重预警偏离-4.7%</t>
-  </si>
-  <si>
-    <t>📊权重预警偏离+3.1%</t>
-  </si>
-  <si>
-    <t>🔴再平衡紧急线：偏离-10.0% &gt;= ±10%</t>
-  </si>
-  <si>
-    <t>📊权重预警偏离+5.7%</t>
-  </si>
-  <si>
-    <t>📊权重预警偏离+5.4%</t>
-  </si>
-  <si>
-    <t>📊权重预警偏离-3.5%</t>
-  </si>
-  <si>
-    <t>20260604</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>权重预警偏离-4.7%</t>
-  </si>
-  <si>
-    <t>权重预警偏离+3.1%</t>
-  </si>
-  <si>
-    <t>再平衡紧急:偏离&gt;=+-10%</t>
-  </si>
-  <si>
-    <t>权重预警偏离+5.8%</t>
-  </si>
-  <si>
-    <t>权重预警偏离+5.5%</t>
-  </si>
-  <si>
-    <t>权重预警偏离-3.4%</t>
-  </si>
-  <si>
-    <t>权重预警偏离-5.0%</t>
-  </si>
-  <si>
-    <t>20260609</t>
+    <t>📊权重预警偏离+6.2%</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离-5.3%</t>
+  </si>
+  <si>
+    <t>-0.41%</t>
+  </si>
+  <si>
+    <t>-2.57%</t>
+  </si>
+  <si>
+    <t>+0.69%</t>
+  </si>
+  <si>
+    <t>-1.13%</t>
+  </si>
+  <si>
+    <t>-0.07%</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离+4.5%</t>
+  </si>
+  <si>
+    <t>-0.05%</t>
+  </si>
+  <si>
+    <t>📊权重预警偏离+4.3%</t>
+  </si>
+  <si>
+    <t>-2.99%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="12">
+  <numFmts count="13">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -1363,6 +1417,7 @@
     <numFmt numFmtId="181" formatCode="0.0000%"/>
     <numFmt numFmtId="182" formatCode="0.000%"/>
     <numFmt numFmtId="183" formatCode="0.0000"/>
+    <numFmt numFmtId="184" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??.00_ ;_ @_ "/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -2055,7 +2110,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2181,6 +2236,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="183" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -2727,476 +2785,476 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="47" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="48" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="48" t="s">
+      <c r="D5" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="48" t="s">
+      <c r="E5" s="49" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="49" t="s">
+      <c r="B6" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="C6" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="49" t="s">
+      <c r="E6" s="50" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="49" t="s">
+      <c r="C7" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="49" t="s">
+      <c r="E7" s="50" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="49" t="s">
+      <c r="D8" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="49" t="s">
+      <c r="E8" s="50" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="51" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="47" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A13" s="48" t="s">
+      <c r="A13" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="48" t="s">
+      <c r="D13" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="48" t="s">
+      <c r="E13" s="49" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="14" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="49" t="s">
+      <c r="B14" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="49" t="s">
+      <c r="E14" s="50" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="15" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="49" t="s">
+      <c r="B15" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="49" t="s">
+      <c r="C15" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="49" t="s">
+      <c r="D15" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="49" t="s">
+      <c r="E15" s="50" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="16" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A16" s="49" t="s">
+      <c r="A16" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="49" t="s">
+      <c r="B16" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="49" t="s">
+      <c r="C16" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="49" t="s">
+      <c r="E16" s="50" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="50" t="s">
+      <c r="A18" s="51" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="47" t="s">
+      <c r="A21" s="48" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="47" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="24" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A24" s="48" t="s">
+      <c r="A24" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="48" t="s">
+      <c r="B24" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="48" t="s">
+      <c r="C24" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="48" t="s">
+      <c r="D24" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="48" t="s">
+      <c r="E24" s="49" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="25" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="49" t="s">
+      <c r="B25" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="49" t="s">
+      <c r="C25" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="49" t="s">
+      <c r="D25" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="49" t="s">
+      <c r="E25" s="50" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="26" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A26" s="49" t="s">
+      <c r="A26" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="49" t="s">
+      <c r="B26" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C26" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="49" t="s">
+      <c r="D26" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="E26" s="49" t="s">
+      <c r="E26" s="50" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="27" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="49" t="s">
+      <c r="B27" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="49" t="s">
+      <c r="C27" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="49" t="s">
+      <c r="D27" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="49" t="s">
+      <c r="E27" s="50" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="50" t="s">
+      <c r="A29" s="51" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="52" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A32" s="46" t="s">
+      <c r="A32" s="47" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="33" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A33" s="48" t="s">
+      <c r="A33" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="48" t="s">
+      <c r="B33" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="48" t="s">
+      <c r="C33" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="D33" s="48" t="s">
+      <c r="D33" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="E33" s="48" t="s">
+      <c r="E33" s="49" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="34" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="B34" s="49" t="s">
+      <c r="B34" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="49" t="s">
+      <c r="C34" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="D34" s="49" t="s">
+      <c r="D34" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="E34" s="49" t="s">
+      <c r="E34" s="50" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="35" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A35" s="49" t="s">
+      <c r="A35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="49" t="s">
+      <c r="B35" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="49" t="s">
+      <c r="C35" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="D35" s="49" t="s">
+      <c r="D35" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="E35" s="49" t="s">
+      <c r="E35" s="50" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="36" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A36" s="49" t="s">
+      <c r="A36" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="49" t="s">
+      <c r="B36" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="49" t="s">
+      <c r="C36" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="D36" s="49" t="s">
+      <c r="D36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="E36" s="49" t="s">
+      <c r="E36" s="50" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="37" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A37" s="49" t="s">
+      <c r="A37" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="49" t="s">
+      <c r="B37" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="49" t="s">
+      <c r="C37" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="49" t="s">
+      <c r="D37" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="E37" s="49" t="s">
+      <c r="E37" s="50" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="51" t="s">
+      <c r="A39" s="52" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="50" t="s">
+      <c r="A40" s="51" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:5">
-      <c r="A42" s="46" t="s">
+      <c r="A42" s="47" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="43" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A43" s="48" t="s">
+      <c r="A43" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="B43" s="48" t="s">
+      <c r="B43" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="48" t="s">
+      <c r="C43" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="D43" s="48" t="s">
+      <c r="D43" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="E43" s="48" t="s">
+      <c r="E43" s="49" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="44" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A44" s="49" t="s">
+      <c r="A44" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="49" t="s">
+      <c r="B44" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="49" t="s">
+      <c r="C44" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="D44" s="49" t="s">
+      <c r="D44" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="49" t="s">
+      <c r="E44" s="50" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="45" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="B45" s="49" t="s">
+      <c r="B45" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="49" t="s">
+      <c r="C45" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="D45" s="49" t="s">
+      <c r="D45" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="E45" s="49" t="s">
+      <c r="E45" s="50" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="46" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A46" s="49" t="s">
+      <c r="A46" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="B46" s="49" t="s">
+      <c r="B46" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C46" s="49" t="s">
+      <c r="C46" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="D46" s="49" t="s">
+      <c r="D46" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="E46" s="49" t="s">
+      <c r="E46" s="50" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="47" ht="14.5" customHeight="1" spans="1:5">
-      <c r="A47" s="49" t="s">
+      <c r="A47" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="B47" s="49" t="s">
+      <c r="B47" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="C47" s="49" t="s">
+      <c r="C47" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="D47" s="49" t="s">
+      <c r="D47" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="E47" s="49" t="s">
+      <c r="E47" s="50" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="51" t="s">
+      <c r="A49" s="52" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" spans="1:1">
-      <c r="A51" s="46" t="s">
+      <c r="A51" s="47" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="52" ht="14.5" customHeight="1" spans="1:1">
-      <c r="A52" s="52" t="s">
+      <c r="A52" s="53" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="54" ht="16.5" customHeight="1" spans="1:1">
-      <c r="A54" s="46" t="s">
+      <c r="A54" s="47" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="55" ht="14.5" customHeight="1" spans="1:1">
-      <c r="A55" s="52" t="s">
+      <c r="A55" s="53" t="s">
         <v>115</v>
       </c>
     </row>
@@ -3231,7 +3289,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultColWidth="8.73148148148148" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.5462962962963" style="1" customWidth="1"/>
@@ -3304,7 +3362,7 @@
       <c r="A2" s="22">
         <v>510300</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="4" t="s">
         <v>130</v>
       </c>
       <c r="C2" s="23">
@@ -3318,10 +3376,10 @@
         <v>0.15</v>
       </c>
       <c r="F2" s="26">
-        <v>0.2255</v>
+        <v>0.2187</v>
       </c>
       <c r="G2" s="26">
-        <v>0.0755</v>
+        <v>0.0687</v>
       </c>
       <c r="H2" s="27">
         <v>4.885</v>
@@ -3330,17 +3388,16 @@
         <v>153800</v>
       </c>
       <c r="J2" s="29">
-        <f t="shared" ref="J2:J13" si="1">H2*I2</f>
-        <v>751313</v>
+        <v>751304</v>
       </c>
       <c r="K2" s="30">
-        <v>4.826</v>
+        <v>4.784</v>
       </c>
       <c r="L2" s="31">
-        <v>-9074.2</v>
+        <v>-15533.8</v>
       </c>
       <c r="M2" s="32">
-        <v>-0.0121</v>
+        <v>-0.0207</v>
       </c>
       <c r="N2" s="33" t="s">
         <v>131</v>
@@ -3370,10 +3427,10 @@
         <v>0.1</v>
       </c>
       <c r="F3" s="40">
-        <v>0.0503</v>
+        <v>0.0486</v>
       </c>
       <c r="G3" s="40">
-        <v>-0.0497</v>
+        <v>-0.0514</v>
       </c>
       <c r="H3" s="41">
         <v>8.696</v>
@@ -3382,17 +3439,17 @@
         <v>20000</v>
       </c>
       <c r="J3" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J2:J13" si="1">H3*I3</f>
         <v>173920</v>
       </c>
       <c r="K3" s="42">
-        <v>8.27</v>
+        <v>8.171</v>
       </c>
       <c r="L3" s="43">
-        <v>-8520</v>
+        <v>-10500</v>
       </c>
       <c r="M3" s="21">
-        <v>-0.049</v>
+        <v>-0.0604</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>133</v>
@@ -3423,10 +3480,10 @@
         <v>0.05</v>
       </c>
       <c r="F4" s="40">
-        <v>0.0311</v>
+        <v>0.0303</v>
       </c>
       <c r="G4" s="40">
-        <v>-0.0189</v>
+        <v>-0.0197</v>
       </c>
       <c r="H4" s="41">
         <v>1.838</v>
@@ -3439,13 +3496,13 @@
         <v>110280</v>
       </c>
       <c r="K4" s="42">
-        <v>1.706</v>
+        <v>1.699</v>
       </c>
       <c r="L4" s="43">
-        <v>-7920</v>
+        <v>-8340</v>
       </c>
       <c r="M4" s="21">
-        <v>-0.0718</v>
+        <v>-0.0756</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>135</v>
@@ -3476,10 +3533,10 @@
         <v>0.05</v>
       </c>
       <c r="F5" s="26">
-        <v>0.076</v>
+        <v>0.0725</v>
       </c>
       <c r="G5" s="26">
-        <v>0.026</v>
+        <v>0.0225</v>
       </c>
       <c r="H5" s="30">
         <v>3.968</v>
@@ -3492,13 +3549,13 @@
         <v>249984</v>
       </c>
       <c r="K5" s="42">
-        <v>3.972</v>
+        <v>3.87</v>
       </c>
       <c r="L5" s="31">
-        <v>252</v>
+        <v>-6174</v>
       </c>
       <c r="M5" s="32">
-        <v>0.001</v>
+        <v>-0.0247</v>
       </c>
       <c r="N5" s="33"/>
       <c r="O5" s="34"/>
@@ -3521,10 +3578,10 @@
         <v>0.05</v>
       </c>
       <c r="F6" s="26">
-        <v>0.0771</v>
+        <v>0.076</v>
       </c>
       <c r="G6" s="26">
-        <v>0.0271</v>
+        <v>0.026</v>
       </c>
       <c r="H6" s="30">
         <v>1.15</v>
@@ -3537,13 +3594,13 @@
         <v>250700</v>
       </c>
       <c r="K6" s="42">
-        <v>1.164</v>
+        <v>1.172</v>
       </c>
       <c r="L6" s="31">
-        <v>3052</v>
+        <v>4796</v>
       </c>
       <c r="M6" s="32">
-        <v>0.0122</v>
+        <v>0.0191</v>
       </c>
       <c r="N6" s="33"/>
       <c r="O6" s="34"/>
@@ -3566,36 +3623,35 @@
         <v>0.1</v>
       </c>
       <c r="F7" s="40">
-        <v>0.0305</v>
+        <v>0.0594</v>
       </c>
       <c r="G7" s="40">
-        <v>-0.0695</v>
+        <v>-0.0406</v>
       </c>
       <c r="H7" s="41">
-        <v>13.95</v>
+        <v>13.8644</v>
       </c>
       <c r="I7" s="7">
-        <v>7200</v>
+        <v>14500</v>
       </c>
       <c r="J7" s="8">
-        <f t="shared" si="1"/>
-        <v>100440</v>
+        <v>201034</v>
       </c>
       <c r="K7" s="41">
-        <v>13.927</v>
+        <v>13.77</v>
       </c>
       <c r="L7" s="43">
-        <v>-165.6</v>
+        <v>-1368.8</v>
       </c>
       <c r="M7" s="21">
-        <v>-0.0016</v>
+        <v>-0.0068</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>139</v>
       </c>
       <c r="O7" s="34">
         <f>D7-J7</f>
-        <v>399560</v>
+        <v>298966</v>
       </c>
     </row>
     <row r="8" s="10" customFormat="1" spans="1:18">
@@ -3616,10 +3672,10 @@
         <v>0.1</v>
       </c>
       <c r="F8" s="26">
-        <v>0.1526</v>
+        <v>0.1492</v>
       </c>
       <c r="G8" s="26">
-        <v>0.0526</v>
+        <v>0.0492</v>
       </c>
       <c r="H8" s="30">
         <v>135.645</v>
@@ -3632,13 +3688,13 @@
         <v>501886.5</v>
       </c>
       <c r="K8" s="42">
-        <v>135.75</v>
+        <v>135.653</v>
       </c>
       <c r="L8" s="31">
-        <v>388.5</v>
+        <v>29.6</v>
       </c>
       <c r="M8" s="32">
-        <v>0.0008</v>
+        <v>0.0001</v>
       </c>
       <c r="N8" s="33" t="s">
         <v>141</v>
@@ -3663,10 +3719,10 @@
         <v>0.1</v>
       </c>
       <c r="F9" s="26">
-        <v>0.1503</v>
+        <v>0.147</v>
       </c>
       <c r="G9" s="26">
-        <v>0.0503</v>
+        <v>0.047</v>
       </c>
       <c r="H9" s="30">
         <v>141.2121</v>
@@ -3675,17 +3731,16 @@
         <v>3500</v>
       </c>
       <c r="J9" s="29">
-        <f t="shared" si="1"/>
-        <v>494242.35</v>
+        <v>494242.4</v>
       </c>
       <c r="K9" s="42">
-        <v>141.345</v>
+        <v>141.278</v>
       </c>
       <c r="L9" s="31">
-        <v>465.15</v>
+        <v>230.65</v>
       </c>
       <c r="M9" s="32">
-        <v>0.0009</v>
+        <v>0.0005</v>
       </c>
       <c r="N9" s="33" t="s">
         <v>143</v>
@@ -3710,10 +3765,10 @@
         <v>0.05</v>
       </c>
       <c r="F10" s="26">
-        <v>0.0759</v>
+        <v>0.0743</v>
       </c>
       <c r="G10" s="26">
-        <v>0.0259</v>
+        <v>0.0243</v>
       </c>
       <c r="H10" s="30">
         <v>113.462</v>
@@ -3726,10 +3781,10 @@
         <v>249616.4</v>
       </c>
       <c r="K10" s="42">
-        <v>113.559</v>
+        <v>113.56</v>
       </c>
       <c r="L10" s="31">
-        <v>213.4</v>
+        <v>215.6</v>
       </c>
       <c r="M10" s="32">
         <v>0.0009</v>
@@ -3755,10 +3810,10 @@
         <v>0.15</v>
       </c>
       <c r="F11" s="40">
-        <v>0.1308</v>
+        <v>0.1241</v>
       </c>
       <c r="G11" s="40">
-        <v>-0.0192</v>
+        <v>-0.0259</v>
       </c>
       <c r="H11" s="44">
         <v>9.3302</v>
@@ -3767,22 +3822,21 @@
         <v>47800</v>
       </c>
       <c r="J11" s="8">
-        <f t="shared" si="1"/>
-        <v>445983.56</v>
+        <v>445988.4</v>
       </c>
       <c r="K11" s="42">
-        <v>9.005</v>
+        <v>8.736</v>
       </c>
       <c r="L11" s="43">
-        <v>-15544.56</v>
+        <v>-28402.76</v>
       </c>
       <c r="M11" s="21">
-        <v>-0.0349</v>
+        <v>-0.0637</v>
       </c>
       <c r="N11" s="4"/>
       <c r="O11" s="34">
         <f>D11-J11</f>
-        <v>304016.44</v>
+        <v>304011.6</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -3815,7 +3869,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="41">
-        <v>100.514</v>
+        <v>100.517</v>
       </c>
       <c r="L12" s="43">
         <v>0</v>
@@ -3824,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="O12" s="34">
         <f>D12-J12</f>
@@ -3836,7 +3890,7 @@
         <v>511990</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C13" s="37">
         <v>5000000</v>
@@ -3861,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="42">
-        <v>100.003</v>
+        <v>100.002</v>
       </c>
       <c r="L13" s="43">
         <v>0</v>
@@ -3870,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="O13" s="34">
         <f>D13-J13</f>
@@ -3904,24 +3958,32 @@
       </c>
       <c r="J14" s="8">
         <f>SUM(J2:J13)</f>
-        <v>3328365.81</v>
+        <v>3428955.7</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="8">
         <f>SUM(L2:L13)</f>
-        <v>-36853.31</v>
+        <v>-65047.51</v>
       </c>
       <c r="M14" s="21">
         <f>L14/J14</f>
-        <v>-0.0110724938614845</v>
+        <v>-0.0189700642676719</v>
       </c>
       <c r="N14" s="4" t="s">
         <v>33</v>
       </c>
       <c r="O14" s="8">
         <f>D14-J14</f>
-        <v>1671634.19</v>
-      </c>
+        <v>1571044.3</v>
+      </c>
+    </row>
+    <row r="17" spans="10:10">
+      <c r="J17" s="45">
+        <v>3428935.7</v>
+      </c>
+    </row>
+    <row r="21" spans="10:10">
+      <c r="J21" s="45"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3932,7 +3994,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="20.8148148148148" style="2" customWidth="1"/>
@@ -3944,7 +4006,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>116</v>
@@ -3953,24 +4015,24 @@
         <v>117</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>124</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D2" s="6">
         <v>113.462</v>
@@ -3985,10 +4047,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>145</v>
@@ -4006,13 +4068,13 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D4" s="6">
         <v>141.253</v>
@@ -4027,13 +4089,13 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D5" s="6">
         <v>135.645</v>
@@ -4048,13 +4110,13 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="D6" s="6">
         <v>4.942</v>
@@ -4069,7 +4131,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>163</v>
@@ -4090,7 +4152,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>165</v>
@@ -4111,7 +4173,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>165</v>
@@ -4132,13 +4194,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="D10" s="6">
         <v>4.865</v>
@@ -4153,7 +4215,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>167</v>
@@ -4174,13 +4236,13 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>157</v>
       </c>
       <c r="D12" s="6">
         <v>141.2</v>
@@ -4284,7 +4346,7 @@
         <v>511990</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D17" s="6">
         <v>99.997</v>
@@ -4325,7 +4387,7 @@
         <v>174</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D19" s="6">
         <v>100.005</v>
@@ -4364,7 +4426,7 @@
         <v>175</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>145</v>
@@ -4385,10 +4447,10 @@
         <v>175</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="D22" s="6">
         <v>4.78</v>
@@ -4401,8 +4463,34 @@
         <v>113764</v>
       </c>
     </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="6">
+        <v>13.78</v>
+      </c>
+      <c r="E23" s="7">
+        <v>7300</v>
+      </c>
+      <c r="F23" s="8">
+        <v>100594</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="F24" s="1">
+        <f>SUM(F2:F23)</f>
+        <v>3428935.7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F22" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F24" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4413,7 +4501,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q151"/>
+  <dimension ref="A1:Q163"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.8148148148148" style="1" customWidth="1"/>
@@ -4432,7 +4520,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B1" t="s">
         <v>177</v>
@@ -4479,7 +4567,7 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B2" t="s">
         <v>187</v>
@@ -4532,7 +4620,7 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B3" t="s">
         <v>195</v>
@@ -4585,7 +4673,7 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B4" t="s">
         <v>202</v>
@@ -4797,7 +4885,7 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B8" t="s">
         <v>220</v>
@@ -4850,7 +4938,7 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B9" t="s">
         <v>226</v>
@@ -4903,7 +4991,7 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
         <v>232</v>
@@ -4956,7 +5044,7 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B11" t="s">
         <v>238</v>
@@ -5009,7 +5097,7 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s">
         <v>244</v>
@@ -5062,7 +5150,7 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s">
         <v>187</v>
@@ -5115,7 +5203,7 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s">
         <v>195</v>
@@ -5168,7 +5256,7 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B15" t="s">
         <v>202</v>
@@ -8616,10 +8704,10 @@
         <v>406</v>
       </c>
       <c r="B80" t="s">
+        <v>130</v>
+      </c>
+      <c r="C80" t="s">
         <v>162</v>
-      </c>
-      <c r="C80" t="s">
-        <v>161</v>
       </c>
       <c r="H80">
         <v>4.868</v>
@@ -8754,7 +8842,7 @@
         <v>412</v>
       </c>
       <c r="C86" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H86">
         <v>136.091</v>
@@ -8777,7 +8865,7 @@
         <v>413</v>
       </c>
       <c r="C87" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H87">
         <v>141.504</v>
@@ -8797,10 +8885,10 @@
         <v>406</v>
       </c>
       <c r="B88" t="s">
+        <v>154</v>
+      </c>
+      <c r="C88" t="s">
         <v>153</v>
-      </c>
-      <c r="C88" t="s">
-        <v>152</v>
       </c>
       <c r="H88">
         <v>113.525</v>
@@ -8823,7 +8911,7 @@
         <v>414</v>
       </c>
       <c r="C89" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H89">
         <v>9.344</v>
@@ -8863,7 +8951,7 @@
         <v>406</v>
       </c>
       <c r="B91" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C91" t="s">
         <v>174</v>
@@ -8886,10 +8974,10 @@
         <v>406</v>
       </c>
       <c r="B92" t="s">
+        <v>130</v>
+      </c>
+      <c r="C92" t="s">
         <v>162</v>
-      </c>
-      <c r="C92" t="s">
-        <v>161</v>
       </c>
       <c r="H92">
         <v>4.868</v>
@@ -9024,7 +9112,7 @@
         <v>412</v>
       </c>
       <c r="C98" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H98">
         <v>136.091</v>
@@ -9047,7 +9135,7 @@
         <v>413</v>
       </c>
       <c r="C99" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H99">
         <v>141.504</v>
@@ -9067,10 +9155,10 @@
         <v>406</v>
       </c>
       <c r="B100" t="s">
+        <v>154</v>
+      </c>
+      <c r="C100" t="s">
         <v>153</v>
-      </c>
-      <c r="C100" t="s">
-        <v>152</v>
       </c>
       <c r="H100">
         <v>113.525</v>
@@ -9093,7 +9181,7 @@
         <v>414</v>
       </c>
       <c r="C101" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H101">
         <v>9.344</v>
@@ -9133,7 +9221,7 @@
         <v>406</v>
       </c>
       <c r="B103" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C103" t="s">
         <v>174</v>
@@ -9156,10 +9244,10 @@
         <v>417</v>
       </c>
       <c r="B104" t="s">
+        <v>130</v>
+      </c>
+      <c r="C104" t="s">
         <v>162</v>
-      </c>
-      <c r="C104" t="s">
-        <v>161</v>
       </c>
       <c r="H104">
         <v>4.936</v>
@@ -9294,7 +9382,7 @@
         <v>412</v>
       </c>
       <c r="C110" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H110">
         <v>136.14</v>
@@ -9317,7 +9405,7 @@
         <v>413</v>
       </c>
       <c r="C111" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H111">
         <v>141.48</v>
@@ -9337,10 +9425,10 @@
         <v>417</v>
       </c>
       <c r="B112" t="s">
+        <v>154</v>
+      </c>
+      <c r="C112" t="s">
         <v>153</v>
-      </c>
-      <c r="C112" t="s">
-        <v>152</v>
       </c>
       <c r="H112">
         <v>113.526</v>
@@ -9363,7 +9451,7 @@
         <v>414</v>
       </c>
       <c r="C113" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H113">
         <v>9.41</v>
@@ -9403,7 +9491,7 @@
         <v>417</v>
       </c>
       <c r="B115" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C115" t="s">
         <v>174</v>
@@ -9426,10 +9514,10 @@
         <v>420</v>
       </c>
       <c r="B116" t="s">
+        <v>130</v>
+      </c>
+      <c r="C116" t="s">
         <v>162</v>
-      </c>
-      <c r="C116" t="s">
-        <v>161</v>
       </c>
       <c r="H116">
         <v>4.965</v>
@@ -9567,7 +9655,7 @@
         <v>412</v>
       </c>
       <c r="C122" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H122">
         <v>136.078</v>
@@ -9590,7 +9678,7 @@
         <v>413</v>
       </c>
       <c r="C123" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H123">
         <v>141.464</v>
@@ -9610,10 +9698,10 @@
         <v>420</v>
       </c>
       <c r="B124" t="s">
+        <v>154</v>
+      </c>
+      <c r="C124" t="s">
         <v>153</v>
-      </c>
-      <c r="C124" t="s">
-        <v>152</v>
       </c>
       <c r="H124">
         <v>113.528</v>
@@ -9636,7 +9724,7 @@
         <v>414</v>
       </c>
       <c r="C125" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H125">
         <v>9.281</v>
@@ -9671,7 +9759,7 @@
         <v>0</v>
       </c>
       <c r="N126" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -9679,7 +9767,7 @@
         <v>420</v>
       </c>
       <c r="B127" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C127" t="s">
         <v>174</v>
@@ -9702,10 +9790,10 @@
         <v>427</v>
       </c>
       <c r="B128" t="s">
+        <v>130</v>
+      </c>
+      <c r="C128" t="s">
         <v>162</v>
-      </c>
-      <c r="C128" t="s">
-        <v>161</v>
       </c>
       <c r="H128">
         <v>4.926</v>
@@ -9843,7 +9931,7 @@
         <v>412</v>
       </c>
       <c r="C134" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H134">
         <v>136.133</v>
@@ -9866,7 +9954,7 @@
         <v>413</v>
       </c>
       <c r="C135" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H135">
         <v>141.504</v>
@@ -9886,10 +9974,10 @@
         <v>427</v>
       </c>
       <c r="B136" t="s">
+        <v>154</v>
+      </c>
+      <c r="C136" t="s">
         <v>153</v>
-      </c>
-      <c r="C136" t="s">
-        <v>152</v>
       </c>
       <c r="H136">
         <v>113.535</v>
@@ -9912,7 +10000,7 @@
         <v>414</v>
       </c>
       <c r="C137" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H137">
         <v>9.29</v>
@@ -9955,7 +10043,7 @@
         <v>427</v>
       </c>
       <c r="B139" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C139" t="s">
         <v>174</v>
@@ -9978,10 +10066,10 @@
         <v>436</v>
       </c>
       <c r="B140" t="s">
+        <v>130</v>
+      </c>
+      <c r="C140" t="s">
         <v>162</v>
-      </c>
-      <c r="C140" t="s">
-        <v>161</v>
       </c>
       <c r="H140">
         <v>4.826</v>
@@ -9993,7 +10081,7 @@
         <v>-0.0121</v>
       </c>
       <c r="N140" t="s">
-        <v>131</v>
+        <v>437</v>
       </c>
     </row>
     <row r="141" spans="1:14">
@@ -10016,7 +10104,7 @@
         <v>-0.049</v>
       </c>
       <c r="N141" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
     </row>
     <row r="142" spans="1:14">
@@ -10039,7 +10127,7 @@
         <v>-0.0718</v>
       </c>
       <c r="N142" t="s">
-        <v>135</v>
+        <v>438</v>
       </c>
     </row>
     <row r="143" spans="1:14">
@@ -10088,7 +10176,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:15">
       <c r="A145" t="s">
         <v>436</v>
       </c>
@@ -10108,10 +10196,10 @@
         <v>-0.0016</v>
       </c>
       <c r="N145" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15">
       <c r="A146" t="s">
         <v>436</v>
       </c>
@@ -10119,7 +10207,7 @@
         <v>412</v>
       </c>
       <c r="C146" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H146">
         <v>135.75</v>
@@ -10131,10 +10219,10 @@
         <v>0.0008</v>
       </c>
       <c r="N146" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="147" spans="1:14">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15">
       <c r="A147" t="s">
         <v>436</v>
       </c>
@@ -10142,7 +10230,7 @@
         <v>413</v>
       </c>
       <c r="C147" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H147">
         <v>141.345</v>
@@ -10154,18 +10242,18 @@
         <v>0.0009</v>
       </c>
       <c r="N147" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="148" spans="1:14">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15">
       <c r="A148" t="s">
         <v>436</v>
       </c>
       <c r="B148" t="s">
+        <v>154</v>
+      </c>
+      <c r="C148" t="s">
         <v>153</v>
-      </c>
-      <c r="C148" t="s">
-        <v>152</v>
       </c>
       <c r="H148">
         <v>113.559</v>
@@ -10180,7 +10268,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:15">
       <c r="A149" t="s">
         <v>436</v>
       </c>
@@ -10188,7 +10276,7 @@
         <v>414</v>
       </c>
       <c r="C149" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H149">
         <v>9.005</v>
@@ -10203,7 +10291,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:15">
       <c r="A150" t="s">
         <v>436</v>
       </c>
@@ -10223,15 +10311,15 @@
         <v>0</v>
       </c>
       <c r="N150" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="151" spans="1:14">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15">
       <c r="A151" t="s">
         <v>436</v>
       </c>
       <c r="B151" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C151" t="s">
         <v>174</v>
@@ -10246,7 +10334,571 @@
         <v>0</v>
       </c>
       <c r="N151" t="s">
-        <v>133</v>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15">
+      <c r="A152" t="s">
+        <v>442</v>
+      </c>
+      <c r="B152" t="s">
+        <v>443</v>
+      </c>
+      <c r="C152" t="s">
+        <v>162</v>
+      </c>
+      <c r="D152">
+        <v>153800</v>
+      </c>
+      <c r="E152">
+        <v>4.885</v>
+      </c>
+      <c r="F152">
+        <v>751313</v>
+      </c>
+      <c r="G152">
+        <v>4.784</v>
+      </c>
+      <c r="H152" t="s">
+        <v>387</v>
+      </c>
+      <c r="I152">
+        <v>735779.2</v>
+      </c>
+      <c r="J152">
+        <v>-15533.8</v>
+      </c>
+      <c r="K152">
+        <v>-0.0207</v>
+      </c>
+      <c r="L152">
+        <v>0.15</v>
+      </c>
+      <c r="M152">
+        <v>0.2124</v>
+      </c>
+      <c r="N152">
+        <v>0.0624</v>
+      </c>
+      <c r="O152" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15">
+      <c r="A153" t="s">
+        <v>442</v>
+      </c>
+      <c r="B153" t="s">
+        <v>132</v>
+      </c>
+      <c r="C153" t="s">
+        <v>165</v>
+      </c>
+      <c r="D153">
+        <v>20000</v>
+      </c>
+      <c r="E153">
+        <v>8.696</v>
+      </c>
+      <c r="F153">
+        <v>173920</v>
+      </c>
+      <c r="G153">
+        <v>8.171</v>
+      </c>
+      <c r="H153" t="s">
+        <v>342</v>
+      </c>
+      <c r="I153">
+        <v>163420</v>
+      </c>
+      <c r="J153">
+        <v>-10500</v>
+      </c>
+      <c r="K153">
+        <v>-0.0604</v>
+      </c>
+      <c r="L153">
+        <v>0.1</v>
+      </c>
+      <c r="M153">
+        <v>0.0472</v>
+      </c>
+      <c r="N153">
+        <v>-0.0528</v>
+      </c>
+      <c r="O153" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15">
+      <c r="A154" t="s">
+        <v>442</v>
+      </c>
+      <c r="B154" t="s">
+        <v>134</v>
+      </c>
+      <c r="C154" t="s">
+        <v>167</v>
+      </c>
+      <c r="D154">
+        <v>60000</v>
+      </c>
+      <c r="E154">
+        <v>1.838</v>
+      </c>
+      <c r="F154">
+        <v>110280</v>
+      </c>
+      <c r="G154">
+        <v>1.699</v>
+      </c>
+      <c r="H154" t="s">
+        <v>446</v>
+      </c>
+      <c r="I154">
+        <v>101940</v>
+      </c>
+      <c r="J154">
+        <v>-8340</v>
+      </c>
+      <c r="K154">
+        <v>-0.0756</v>
+      </c>
+      <c r="L154">
+        <v>0.05</v>
+      </c>
+      <c r="M154">
+        <v>0.0294</v>
+      </c>
+      <c r="N154">
+        <v>-0.0206</v>
+      </c>
+      <c r="O154" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15">
+      <c r="A155" t="s">
+        <v>442</v>
+      </c>
+      <c r="B155" t="s">
+        <v>136</v>
+      </c>
+      <c r="C155" t="s">
+        <v>163</v>
+      </c>
+      <c r="D155">
+        <v>63000</v>
+      </c>
+      <c r="E155">
+        <v>3.968</v>
+      </c>
+      <c r="F155">
+        <v>249984</v>
+      </c>
+      <c r="G155">
+        <v>3.87</v>
+      </c>
+      <c r="H155" t="s">
+        <v>447</v>
+      </c>
+      <c r="I155">
+        <v>243810</v>
+      </c>
+      <c r="J155">
+        <v>-6174</v>
+      </c>
+      <c r="K155">
+        <v>-0.0247</v>
+      </c>
+      <c r="L155">
+        <v>0.05</v>
+      </c>
+      <c r="M155">
+        <v>0.0704</v>
+      </c>
+      <c r="N155">
+        <v>0.0204</v>
+      </c>
+      <c r="O155" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15">
+      <c r="A156" t="s">
+        <v>442</v>
+      </c>
+      <c r="B156" t="s">
+        <v>137</v>
+      </c>
+      <c r="C156" t="s">
+        <v>411</v>
+      </c>
+      <c r="D156">
+        <v>218000</v>
+      </c>
+      <c r="E156">
+        <v>1.15</v>
+      </c>
+      <c r="F156">
+        <v>250700</v>
+      </c>
+      <c r="G156">
+        <v>1.172</v>
+      </c>
+      <c r="H156" t="s">
+        <v>448</v>
+      </c>
+      <c r="I156">
+        <v>255496</v>
+      </c>
+      <c r="J156">
+        <v>4796</v>
+      </c>
+      <c r="K156">
+        <v>0.0191</v>
+      </c>
+      <c r="L156">
+        <v>0.05</v>
+      </c>
+      <c r="M156">
+        <v>0.0737</v>
+      </c>
+      <c r="N156">
+        <v>0.0237</v>
+      </c>
+      <c r="O156" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15">
+      <c r="A157" t="s">
+        <v>442</v>
+      </c>
+      <c r="B157" t="s">
+        <v>138</v>
+      </c>
+      <c r="C157" t="s">
+        <v>173</v>
+      </c>
+      <c r="D157">
+        <v>14500</v>
+      </c>
+      <c r="E157">
+        <v>13.8644</v>
+      </c>
+      <c r="F157">
+        <v>201034</v>
+      </c>
+      <c r="G157">
+        <v>13.77</v>
+      </c>
+      <c r="H157" t="s">
+        <v>449</v>
+      </c>
+      <c r="I157">
+        <v>199665</v>
+      </c>
+      <c r="J157">
+        <v>-1368.8</v>
+      </c>
+      <c r="K157">
+        <v>-0.0068</v>
+      </c>
+      <c r="L157">
+        <v>0.1</v>
+      </c>
+      <c r="M157">
+        <v>0.0594</v>
+      </c>
+      <c r="N157">
+        <v>-0.0406</v>
+      </c>
+      <c r="O157" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15">
+      <c r="A158" t="s">
+        <v>442</v>
+      </c>
+      <c r="B158" t="s">
+        <v>140</v>
+      </c>
+      <c r="C158" t="s">
+        <v>160</v>
+      </c>
+      <c r="D158">
+        <v>3700</v>
+      </c>
+      <c r="E158">
+        <v>135.645</v>
+      </c>
+      <c r="F158">
+        <v>501886.5</v>
+      </c>
+      <c r="G158">
+        <v>135.653</v>
+      </c>
+      <c r="H158" t="s">
+        <v>450</v>
+      </c>
+      <c r="I158">
+        <v>501916.1</v>
+      </c>
+      <c r="J158">
+        <v>29.6</v>
+      </c>
+      <c r="K158">
+        <v>0.0001</v>
+      </c>
+      <c r="L158">
+        <v>0.1</v>
+      </c>
+      <c r="M158">
+        <v>0.1449</v>
+      </c>
+      <c r="N158">
+        <v>0.0449</v>
+      </c>
+      <c r="O158" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15">
+      <c r="A159" t="s">
+        <v>442</v>
+      </c>
+      <c r="B159" t="s">
+        <v>142</v>
+      </c>
+      <c r="C159" t="s">
+        <v>157</v>
+      </c>
+      <c r="D159">
+        <v>3500</v>
+      </c>
+      <c r="E159">
+        <v>141.2121</v>
+      </c>
+      <c r="F159">
+        <v>494242.35</v>
+      </c>
+      <c r="G159">
+        <v>141.278</v>
+      </c>
+      <c r="H159" t="s">
+        <v>452</v>
+      </c>
+      <c r="I159">
+        <v>494473</v>
+      </c>
+      <c r="J159">
+        <v>230.65</v>
+      </c>
+      <c r="K159">
+        <v>0.0005</v>
+      </c>
+      <c r="L159">
+        <v>0.1</v>
+      </c>
+      <c r="M159">
+        <v>0.1427</v>
+      </c>
+      <c r="N159">
+        <v>0.0427</v>
+      </c>
+      <c r="O159" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15">
+      <c r="A160" t="s">
+        <v>442</v>
+      </c>
+      <c r="B160" t="s">
+        <v>144</v>
+      </c>
+      <c r="C160" t="s">
+        <v>153</v>
+      </c>
+      <c r="D160">
+        <v>2200</v>
+      </c>
+      <c r="E160">
+        <v>113.462</v>
+      </c>
+      <c r="F160">
+        <v>249616.4</v>
+      </c>
+      <c r="G160">
+        <v>113.56</v>
+      </c>
+      <c r="H160" t="s">
+        <v>298</v>
+      </c>
+      <c r="I160">
+        <v>249832</v>
+      </c>
+      <c r="J160">
+        <v>215.6</v>
+      </c>
+      <c r="K160">
+        <v>0.0009</v>
+      </c>
+      <c r="L160">
+        <v>0.05</v>
+      </c>
+      <c r="M160">
+        <v>0.0721</v>
+      </c>
+      <c r="N160">
+        <v>0.0221</v>
+      </c>
+      <c r="O160" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15">
+      <c r="A161" t="s">
+        <v>442</v>
+      </c>
+      <c r="B161" t="s">
+        <v>145</v>
+      </c>
+      <c r="C161" t="s">
+        <v>155</v>
+      </c>
+      <c r="D161">
+        <v>47800</v>
+      </c>
+      <c r="E161">
+        <v>9.3302</v>
+      </c>
+      <c r="F161">
+        <v>445983.56</v>
+      </c>
+      <c r="G161">
+        <v>8.736</v>
+      </c>
+      <c r="H161" t="s">
+        <v>454</v>
+      </c>
+      <c r="I161">
+        <v>417580.8</v>
+      </c>
+      <c r="J161">
+        <v>-28402.76</v>
+      </c>
+      <c r="K161">
+        <v>-0.0637</v>
+      </c>
+      <c r="L161">
+        <v>0.15</v>
+      </c>
+      <c r="M161">
+        <v>0.1205</v>
+      </c>
+      <c r="N161">
+        <v>-0.0295</v>
+      </c>
+      <c r="O161" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15">
+      <c r="A162" t="s">
+        <v>442</v>
+      </c>
+      <c r="B162" t="s">
+        <v>146</v>
+      </c>
+      <c r="C162" t="s">
+        <v>416</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="E162">
+        <v>0</v>
+      </c>
+      <c r="F162">
+        <v>0</v>
+      </c>
+      <c r="G162">
+        <v>100.517</v>
+      </c>
+      <c r="H162" t="s">
+        <v>298</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <v>0.05</v>
+      </c>
+      <c r="M162">
+        <v>0</v>
+      </c>
+      <c r="N162">
+        <v>-0.05</v>
+      </c>
+      <c r="O162" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15">
+      <c r="A163" t="s">
+        <v>442</v>
+      </c>
+      <c r="B163" t="s">
+        <v>148</v>
+      </c>
+      <c r="C163" t="s">
+        <v>174</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <v>0</v>
+      </c>
+      <c r="F163">
+        <v>0</v>
+      </c>
+      <c r="G163">
+        <v>100.002</v>
+      </c>
+      <c r="H163" t="s">
+        <v>298</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>0.05</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
+      </c>
+      <c r="N163">
+        <v>-0.05</v>
+      </c>
+      <c r="O163" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/500万资产配置组合2026.xlsx
+++ b/500万资产配置组合2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="9060" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="9060" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="投资纪要" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日报" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'流水'!$A$1:$F$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'流水'!$A$1:$F$25</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1561,7 +1561,7 @@
     <row r="1" ht="20" customHeight="1" s="1">
       <c r="A1" s="46" t="inlineStr">
         <is>
-          <t>500万资产配置 -- 投资纪律速查（优化版 2026-05-21）</t>
+          <t>400万资产配置 -- 投资纪律速查（优化版 2026-05-21）</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
-          <t>适用：510300/510500/588050/159915/512890/511380/518880 | 不适用：债底/现金</t>
+          <t>适用：510300/588050/159915/512890/511380/518880 | 不适用：债底</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
     <row r="10">
       <c r="A10" s="51" t="inlineStr">
         <is>
-          <t>[新增] 止盈资金须2个交易日内再配置，优先补给低仓位资产或买入511880/511990</t>
+          <t>[新增] 止盈资金须2个交易日内再配置，优先补给低仓位资产或买入511360</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
     <row r="21">
       <c r="A21" s="48" t="inlineStr">
         <is>
-          <t>适用：510300/510500/512890/518880/511380  |  清仓后观察40个交易日，站稳20日均线方可重建</t>
+          <t>适用：510300/512890/518880/511380  |  清仓后观察40个交易日，站稳20日均线方可重建</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="30">
       <c r="A30" s="52" t="inlineStr">
         <is>
-          <t>卖出排序：黄金&gt;科创/创业&gt;可转债&gt;中证500&gt;沪深300&gt;红利低波</t>
+          <t>卖出排序：黄金&gt;科创/创业&gt;可转债&gt;沪深300&gt;红利低波</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
     <row r="39">
       <c r="A39" s="52" t="inlineStr">
         <is>
-          <t>黑天鹅卖出顺序：科创50&gt;创业板&gt;黄金(保留底10万)&gt;中证500&gt;可转债 | 恢复：回撤&lt;-10%</t>
+          <t>黑天鹅卖出顺序：科创50&gt;创业板&gt;黄金(保留底10万)&gt;可转债 | 恢复：回撤&lt;-10%</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
     <row r="55" ht="14.5" customHeight="1" s="1">
       <c r="A55" s="53" t="inlineStr">
         <is>
-          <t>511880+511990(50万)：除非系统暴跌补仓，否则不动 | 511360(25万)：T+0战术 | 类现金合计&gt;=75万</t>
+          <t>511360 (25万)：T+0战术灵活配置，作为组合唯一现金管理工具，类现金合计≥25万</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.731481481481479" defaultRowHeight="14.4"/>
   <cols>
     <col width="7.5462962962963" customWidth="1" style="1" min="1" max="1"/>
@@ -2338,7 +2338,7 @@
     <row r="1" ht="115.2" customHeight="1" s="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>更新日期: 2026-06-21 (数据日期: 2026-06-18)</t>
+          <t>更新日期: 2026-06-22 (数据日期: 2026-06-22)</t>
         </is>
       </c>
       <c r="B1" s="16" t="inlineStr">
@@ -2422,14 +2422,14 @@
         </is>
       </c>
       <c r="C2" s="63" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="D2" s="64">
         <f>E2*C2</f>
         <v/>
       </c>
       <c r="E2" s="26" t="n">
-        <v>0.15</v>
+        <v>0.1875</v>
       </c>
       <c r="F2" s="65" t="n">
         <v>0.2177</v>
@@ -2443,8 +2443,9 @@
       <c r="I2" s="67" t="n">
         <v>153800</v>
       </c>
-      <c r="J2" s="68" t="n">
-        <v>751304</v>
+      <c r="J2" s="68">
+        <f>H2*I2</f>
+        <v/>
       </c>
       <c r="K2" s="69" t="n">
         <v>4.984</v>
@@ -2469,600 +2470,450 @@
     </row>
     <row r="3">
       <c r="A3" s="36" t="n">
-        <v>510500</v>
+        <v>588050</v>
       </c>
       <c r="B3" s="36" t="inlineStr">
         <is>
-          <t>南方中证500ETF</t>
+          <t>科创50ETF</t>
         </is>
       </c>
       <c r="C3" s="73" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="D3" s="74">
         <f>E3*C3</f>
         <v/>
       </c>
       <c r="E3" s="39" t="n">
-        <v>0.1</v>
+        <v>0.0625</v>
       </c>
       <c r="F3" s="75" t="n">
-        <v>0.0501</v>
+        <v>0.0334</v>
       </c>
       <c r="G3" s="75" t="n">
-        <v>-0.0499</v>
+        <v>-0.0166</v>
       </c>
       <c r="H3" s="76" t="n">
-        <v>8.696</v>
+        <v>1.838</v>
       </c>
       <c r="I3" s="77" t="n">
-        <v>20000</v>
+        <v>60000</v>
       </c>
       <c r="J3" s="78">
         <f>H3*I3</f>
         <v/>
       </c>
       <c r="K3" s="79" t="n">
-        <v>8.827999999999999</v>
+        <v>1.958</v>
       </c>
       <c r="L3" s="80" t="n">
-        <v>2640</v>
+        <v>7200</v>
       </c>
       <c r="M3" s="62" t="n">
-        <v>0.0152</v>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>📊权重预警偏离-5.0%</t>
-        </is>
-      </c>
+        <v>0.0653</v>
+      </c>
+      <c r="N3" s="4" t="n"/>
       <c r="O3" s="72">
         <f>D3-J3</f>
         <v/>
       </c>
       <c r="R3" s="0" t="n">
-        <v>38700</v>
+        <v>77900</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="n">
-        <v>588050</v>
-      </c>
-      <c r="B4" s="36" t="inlineStr">
-        <is>
-          <t>科创50ETF</t>
-        </is>
-      </c>
-      <c r="C4" s="73" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D4" s="74">
+      <c r="A4" s="22" t="n">
+        <v>159915</v>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="C4" s="63" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="D4" s="64">
         <f>E4*C4</f>
         <v/>
       </c>
-      <c r="E4" s="39" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F4" s="75" t="n">
-        <v>0.0334</v>
-      </c>
-      <c r="G4" s="75" t="n">
-        <v>-0.0166</v>
-      </c>
-      <c r="H4" s="76" t="n">
-        <v>1.838</v>
-      </c>
-      <c r="I4" s="77" t="n">
-        <v>60000</v>
-      </c>
-      <c r="J4" s="78">
+      <c r="E4" s="26" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="F4" s="65" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="G4" s="65" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="H4" s="69" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="I4" s="67" t="n">
+        <v>63000</v>
+      </c>
+      <c r="J4" s="68">
         <f>H4*I4</f>
         <v/>
       </c>
       <c r="K4" s="79" t="n">
-        <v>1.958</v>
-      </c>
-      <c r="L4" s="80" t="n">
-        <v>7200</v>
-      </c>
-      <c r="M4" s="62" t="n">
-        <v>0.0653</v>
-      </c>
-      <c r="N4" s="4" t="n"/>
-      <c r="O4" s="72">
-        <f>D4-J4</f>
-        <v/>
-      </c>
-      <c r="R4" s="0" t="n">
-        <v>77900</v>
-      </c>
+        <v>4.269</v>
+      </c>
+      <c r="L4" s="70" t="n">
+        <v>18963</v>
+      </c>
+      <c r="M4" s="71" t="n">
+        <v>0.0759</v>
+      </c>
+      <c r="N4" s="23" t="inlineStr">
+        <is>
+          <t>🟢止盈第一档：浮盈7.6% &gt;= 7%，减仓20%</t>
+        </is>
+      </c>
+      <c r="O4" s="72" t="n"/>
     </row>
     <row r="5" customFormat="1" s="10">
       <c r="A5" s="22" t="n">
-        <v>159915</v>
+        <v>512890</v>
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>易方达创业板ETF</t>
+          <t>华泰柏瑞红利低波ETF</t>
         </is>
       </c>
       <c r="C5" s="63" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="D5" s="64">
         <f>E5*C5</f>
         <v/>
       </c>
       <c r="E5" s="26" t="n">
-        <v>0.05</v>
+        <v>0.0625</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>0.0764</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G5" s="65" t="n">
-        <v>0.0264</v>
+        <v>0.019</v>
       </c>
       <c r="H5" s="69" t="n">
-        <v>3.968</v>
+        <v>1.15</v>
       </c>
       <c r="I5" s="67" t="n">
-        <v>63000</v>
+        <v>218000</v>
       </c>
       <c r="J5" s="68">
         <f>H5*I5</f>
         <v/>
       </c>
       <c r="K5" s="79" t="n">
-        <v>4.269</v>
+        <v>1.115</v>
       </c>
       <c r="L5" s="70" t="n">
-        <v>18963</v>
+        <v>-7630</v>
       </c>
       <c r="M5" s="71" t="n">
-        <v>0.0759</v>
-      </c>
-      <c r="N5" s="23" t="inlineStr">
-        <is>
-          <t>🟢止盈第一档：浮盈7.6% &gt;= 7%，减仓20%</t>
-        </is>
-      </c>
+        <v>-0.0304</v>
+      </c>
+      <c r="N5" s="23" t="n"/>
       <c r="O5" s="72" t="n"/>
     </row>
     <row r="6" customFormat="1" s="10">
-      <c r="A6" s="22" t="n">
-        <v>512890</v>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>华泰柏瑞红利低波ETF</t>
-        </is>
-      </c>
-      <c r="C6" s="63" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D6" s="64">
+      <c r="A6" s="36" t="n">
+        <v>511380</v>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>可转债ETF</t>
+        </is>
+      </c>
+      <c r="C6" s="73" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="D6" s="74">
         <f>E6*C6</f>
         <v/>
       </c>
-      <c r="E6" s="26" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F6" s="65" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="G6" s="65" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="H6" s="69" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="I6" s="67" t="n">
-        <v>218000</v>
-      </c>
-      <c r="J6" s="68">
+      <c r="E6" s="39" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F6" s="75" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="G6" s="75" t="n">
+        <v>-0.0421</v>
+      </c>
+      <c r="H6" s="76" t="n">
+        <v>13.8644</v>
+      </c>
+      <c r="I6" s="77" t="n">
+        <v>14500</v>
+      </c>
+      <c r="J6" s="78">
         <f>H6*I6</f>
         <v/>
       </c>
-      <c r="K6" s="79" t="n">
-        <v>1.115</v>
-      </c>
-      <c r="L6" s="70" t="n">
-        <v>-7630</v>
-      </c>
-      <c r="M6" s="71" t="n">
-        <v>-0.0304</v>
-      </c>
-      <c r="N6" s="23" t="n"/>
-      <c r="O6" s="72" t="n"/>
+      <c r="K6" s="76" t="n">
+        <v>14.067</v>
+      </c>
+      <c r="L6" s="80" t="n">
+        <v>2937.7</v>
+      </c>
+      <c r="M6" s="62" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>📊权重预警偏离-4.2%</t>
+        </is>
+      </c>
+      <c r="O6" s="72">
+        <f>D6-J6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="n">
-        <v>511380</v>
-      </c>
-      <c r="B7" s="36" t="inlineStr">
-        <is>
-          <t>可转债ETF</t>
-        </is>
-      </c>
-      <c r="C7" s="73" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D7" s="74">
+      <c r="A7" s="22" t="n">
+        <v>511260</v>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>国泰上证10年期国债ETF</t>
+        </is>
+      </c>
+      <c r="C7" s="63" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="D7" s="64">
         <f>E7*C7</f>
         <v/>
       </c>
-      <c r="E7" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F7" s="75" t="n">
-        <v>0.0579</v>
-      </c>
-      <c r="G7" s="75" t="n">
-        <v>-0.0421</v>
-      </c>
-      <c r="H7" s="76" t="n">
-        <v>13.8644</v>
-      </c>
-      <c r="I7" s="77" t="n">
-        <v>14500</v>
-      </c>
-      <c r="J7" s="78" t="n">
-        <v>201034</v>
-      </c>
-      <c r="K7" s="76" t="n">
-        <v>14.067</v>
-      </c>
-      <c r="L7" s="80" t="n">
-        <v>2937.7</v>
-      </c>
-      <c r="M7" s="62" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>📊权重预警偏离-4.2%</t>
-        </is>
-      </c>
-      <c r="O7" s="72">
-        <f>D7-J7</f>
+      <c r="E7" s="26" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F7" s="65" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="G7" s="65" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="H7" s="69" t="n">
+        <v>135.645</v>
+      </c>
+      <c r="I7" s="67" t="n">
+        <v>3700</v>
+      </c>
+      <c r="J7" s="68">
+        <f>H7*I7</f>
         <v/>
       </c>
+      <c r="K7" s="79" t="n">
+        <v>135.984</v>
+      </c>
+      <c r="L7" s="70" t="n">
+        <v>1254.3</v>
+      </c>
+      <c r="M7" s="71" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="N7" s="23" t="inlineStr">
+        <is>
+          <t>📊权重预警偏离+4.3%</t>
+        </is>
+      </c>
+      <c r="O7" s="72" t="n"/>
     </row>
     <row r="8" customFormat="1" s="10">
       <c r="A8" s="22" t="n">
-        <v>511260</v>
+        <v>511010</v>
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>国泰上证10年期国债ETF</t>
+          <t>国泰上证5年期国债ETF</t>
         </is>
       </c>
       <c r="C8" s="63" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="D8" s="64">
         <f>E8*C8</f>
         <v/>
       </c>
       <c r="E8" s="26" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="F8" s="65" t="n">
-        <v>0.1429</v>
+        <v>0.1406</v>
       </c>
       <c r="G8" s="65" t="n">
-        <v>0.0429</v>
+        <v>0.0406</v>
       </c>
       <c r="H8" s="69" t="n">
-        <v>135.645</v>
+        <v>141.2121</v>
       </c>
       <c r="I8" s="67" t="n">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="J8" s="68">
         <f>H8*I8</f>
         <v/>
       </c>
       <c r="K8" s="79" t="n">
-        <v>135.984</v>
+        <v>141.431</v>
       </c>
       <c r="L8" s="70" t="n">
-        <v>1254.3</v>
+        <v>766.15</v>
       </c>
       <c r="M8" s="71" t="n">
-        <v>0.0025</v>
+        <v>0.0016</v>
       </c>
       <c r="N8" s="23" t="inlineStr">
         <is>
-          <t>📊权重预警偏离+4.3%</t>
+          <t>📊权重预警偏离+4.1%</t>
         </is>
       </c>
       <c r="O8" s="72" t="n"/>
     </row>
     <row r="9" customFormat="1" s="10">
       <c r="A9" s="22" t="n">
-        <v>511010</v>
+        <v>511360</v>
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>国泰上证5年期国债ETF</t>
+          <t>海富通中证短融ETF</t>
         </is>
       </c>
       <c r="C9" s="63" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="D9" s="64">
         <f>E9*C9</f>
         <v/>
       </c>
       <c r="E9" s="26" t="n">
-        <v>0.1</v>
+        <v>0.0625</v>
       </c>
       <c r="F9" s="65" t="n">
-        <v>0.1406</v>
+        <v>0.0709</v>
       </c>
       <c r="G9" s="65" t="n">
-        <v>0.0406</v>
+        <v>0.0209</v>
       </c>
       <c r="H9" s="69" t="n">
-        <v>141.2121</v>
+        <v>113.462</v>
       </c>
       <c r="I9" s="67" t="n">
-        <v>3500</v>
-      </c>
-      <c r="J9" s="68" t="n">
-        <v>494242.4</v>
+        <v>2200</v>
+      </c>
+      <c r="J9" s="68">
+        <f>H9*I9</f>
+        <v/>
       </c>
       <c r="K9" s="79" t="n">
-        <v>141.431</v>
+        <v>113.557</v>
       </c>
       <c r="L9" s="70" t="n">
-        <v>766.15</v>
+        <v>209</v>
       </c>
       <c r="M9" s="71" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="N9" s="23" t="inlineStr">
-        <is>
-          <t>📊权重预警偏离+4.1%</t>
-        </is>
-      </c>
+        <v>0.0008</v>
+      </c>
+      <c r="N9" s="23" t="n"/>
       <c r="O9" s="72" t="n"/>
     </row>
     <row r="10" customFormat="1" s="10">
-      <c r="A10" s="22" t="n">
-        <v>511360</v>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>海富通中证短融ETF</t>
-        </is>
-      </c>
-      <c r="C10" s="63" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D10" s="64">
+      <c r="A10" s="36" t="n">
+        <v>518880</v>
+      </c>
+      <c r="B10" s="36" t="inlineStr">
+        <is>
+          <t>华安黄金ETF</t>
+        </is>
+      </c>
+      <c r="C10" s="73" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="D10" s="74">
         <f>E10*C10</f>
         <v/>
       </c>
-      <c r="E10" s="26" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F10" s="65" t="n">
-        <v>0.0709</v>
-      </c>
-      <c r="G10" s="65" t="n">
-        <v>0.0209</v>
-      </c>
-      <c r="H10" s="69" t="n">
-        <v>113.462</v>
-      </c>
-      <c r="I10" s="67" t="n">
-        <v>2200</v>
-      </c>
-      <c r="J10" s="68">
+      <c r="E10" s="39" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="F10" s="75" t="n">
+        <v>0.1411</v>
+      </c>
+      <c r="G10" s="75" t="n">
+        <v>-0.0089</v>
+      </c>
+      <c r="H10" s="81" t="n">
+        <v>9.232699999999999</v>
+      </c>
+      <c r="I10" s="77" t="n">
+        <v>55800</v>
+      </c>
+      <c r="J10" s="78">
         <f>H10*I10</f>
         <v/>
       </c>
       <c r="K10" s="79" t="n">
-        <v>113.557</v>
-      </c>
-      <c r="L10" s="70" t="n">
-        <v>209</v>
-      </c>
-      <c r="M10" s="71" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="N10" s="23" t="n"/>
-      <c r="O10" s="72" t="n"/>
+        <v>8.907999999999999</v>
+      </c>
+      <c r="L10" s="80" t="n">
+        <v>-18118.26</v>
+      </c>
+      <c r="M10" s="62" t="n">
+        <v>-0.0352</v>
+      </c>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="72">
+        <f>D10-J10</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="n">
-        <v>518880</v>
-      </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>华安黄金ETF</t>
-        </is>
-      </c>
-      <c r="C11" s="73" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D11" s="74">
-        <f>E11*C11</f>
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="78">
+        <f>SUM(D2:D10)</f>
         <v/>
       </c>
-      <c r="E11" s="39" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F11" s="75" t="n">
-        <v>0.1411</v>
-      </c>
-      <c r="G11" s="75" t="n">
-        <v>-0.0089</v>
-      </c>
-      <c r="H11" s="81" t="n">
-        <v>9.232699999999999</v>
-      </c>
-      <c r="I11" s="77" t="n">
-        <v>55800</v>
-      </c>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="76" t="inlineStr"/>
+      <c r="I11" s="77" t="inlineStr"/>
       <c r="J11" s="78">
-        <f>H11*I11</f>
+        <f>SUM(J2:J10)</f>
         <v/>
       </c>
-      <c r="K11" s="79" t="n">
-        <v>8.907999999999999</v>
-      </c>
-      <c r="L11" s="80" t="n">
-        <v>-18118.26</v>
-      </c>
-      <c r="M11" s="62" t="n">
-        <v>-0.0352</v>
-      </c>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="72">
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="78">
+        <f>SUM(L2:L10)</f>
+        <v/>
+      </c>
+      <c r="M11" s="62">
+        <f>L11/J11</f>
+        <v/>
+      </c>
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="78">
         <f>D11-J11</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="36" t="n">
-        <v>511880</v>
-      </c>
-      <c r="B12" s="36" t="inlineStr">
-        <is>
-          <t>银华日利ETF</t>
-        </is>
-      </c>
-      <c r="C12" s="73" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D12" s="74">
-        <f>E12*C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="39" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F12" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="75" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="H12" s="76" t="n"/>
-      <c r="I12" s="77" t="n"/>
-      <c r="J12" s="78">
-        <f>H12*I12</f>
-        <v/>
-      </c>
-      <c r="K12" s="76" t="n">
-        <v>100.533</v>
-      </c>
-      <c r="L12" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>📊权重预警偏离-5.0%</t>
-        </is>
-      </c>
-      <c r="O12" s="72">
-        <f>D12-J12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="36" t="n">
-        <v>511990</v>
-      </c>
-      <c r="B13" s="36" t="inlineStr">
-        <is>
-          <t>华宝添益ETF</t>
-        </is>
-      </c>
-      <c r="C13" s="73" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D13" s="74">
-        <f>E13*C13</f>
-        <v/>
-      </c>
-      <c r="E13" s="39" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F13" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="75" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="H13" s="76" t="n"/>
-      <c r="I13" s="77" t="n"/>
-      <c r="J13" s="78">
-        <f>H13*I13</f>
-        <v/>
-      </c>
-      <c r="K13" s="79" t="n">
-        <v>100</v>
-      </c>
-      <c r="L13" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>📊权重预警偏离-5.0%</t>
-        </is>
-      </c>
-      <c r="O13" s="72">
-        <f>D13-J13</f>
-        <v/>
-      </c>
-    </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr"/>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="78">
-        <f>SUM(D2:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="39" t="n"/>
-      <c r="F14" s="39" t="n"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="76" t="inlineStr"/>
-      <c r="I14" s="77" t="inlineStr"/>
-      <c r="J14" s="78">
-        <f>SUM(J2:J13)</f>
-        <v/>
-      </c>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="78">
-        <f>SUM(L2:L13)</f>
-        <v/>
-      </c>
-      <c r="M14" s="62">
-        <f>L14/J14</f>
-        <v/>
-      </c>
-      <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="78">
-        <f>D14-J14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="J17" s="82" t="n"/>
-    </row>
-    <row r="21">
-      <c r="J21" s="82" t="n"/>
+      <c r="J14" s="82" t="n"/>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18">
+      <c r="J18" s="82" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3075,7 +2926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="20.8148148148148" customWidth="1" style="83" min="1" max="1"/>
@@ -3573,7 +3424,7 @@
         <v>-2500</v>
       </c>
       <c r="F19" s="78" t="n">
-        <v>250012.5</v>
+        <v>-250012.5</v>
       </c>
     </row>
     <row r="20">
@@ -3704,8 +3555,33 @@
         <v>69200</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="84" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>510500</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>中证500ETF</t>
+        </is>
+      </c>
+      <c r="D25" s="85" t="n">
+        <v>8.776999999999999</v>
+      </c>
+      <c r="E25" s="77" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="F25" s="78">
+        <f>D25*E25</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F24"/>
+  <autoFilter ref="A1:F25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14072,7 +13948,7 @@
         <v>135.645</v>
       </c>
       <c r="F194" s="0" t="n">
-        <v>501886.5000000001</v>
+        <v>501886.5</v>
       </c>
       <c r="G194" s="0" t="n">
         <v>135.838</v>
@@ -14705,7 +14581,7 @@
         <v>135.645</v>
       </c>
       <c r="F206" s="0" t="n">
-        <v>501886.5000000001</v>
+        <v>501886.5</v>
       </c>
       <c r="G206" s="0" t="n">
         <v>135.971</v>
@@ -14769,7 +14645,7 @@
         <v>0.0003</v>
       </c>
       <c r="I207" s="0" t="n">
-        <v>494718.0000000001</v>
+        <v>494718</v>
       </c>
       <c r="J207" s="0" t="n">
         <v>475.65</v>
@@ -14986,2559 +14862,2559 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
+      <c r="A212" s="0" t="inlineStr">
         <is>
           <t>20260618</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B212" s="0" t="inlineStr">
         <is>
           <t>沪深300ETF</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
+      <c r="C212" s="0" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="D212" t="n">
+      <c r="D212" s="0" t="n">
         <v>153800</v>
       </c>
-      <c r="E212" t="n">
+      <c r="E212" s="0" t="n">
         <v>4.885</v>
       </c>
-      <c r="F212" t="n">
+      <c r="F212" s="0" t="n">
         <v>751313</v>
       </c>
-      <c r="G212" t="n">
+      <c r="G212" s="0" t="n">
         <v>4.984</v>
       </c>
-      <c r="H212" t="n">
+      <c r="H212" s="0" t="n">
         <v>0.0052</v>
       </c>
-      <c r="I212" t="n">
+      <c r="I212" s="0" t="n">
         <v>766539.2</v>
       </c>
-      <c r="J212" t="n">
+      <c r="J212" s="0" t="n">
         <v>15226.2</v>
       </c>
-      <c r="K212" t="n">
+      <c r="K212" s="0" t="n">
         <v>0.0203</v>
       </c>
-      <c r="L212" t="n">
+      <c r="L212" s="0" t="n">
         <v>0.15</v>
       </c>
-      <c r="M212" t="n">
+      <c r="M212" s="0" t="n">
         <v>0.2177</v>
       </c>
-      <c r="N212" t="n">
+      <c r="N212" s="0" t="n">
         <v>0.0677</v>
       </c>
-      <c r="O212" t="inlineStr">
+      <c r="O212" s="0" t="inlineStr">
         <is>
           <t>📊权重预警偏离+6.8%</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
+      <c r="A213" s="0" t="inlineStr">
         <is>
           <t>20260618</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B213" s="0" t="inlineStr">
         <is>
           <t>中证500ETF</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
+      <c r="C213" s="0" t="inlineStr">
         <is>
           <t>510500</t>
         </is>
       </c>
-      <c r="D213" t="n">
+      <c r="D213" s="0" t="n">
         <v>20000</v>
       </c>
-      <c r="E213" t="n">
+      <c r="E213" s="0" t="n">
         <v>8.696</v>
       </c>
-      <c r="F213" t="n">
+      <c r="F213" s="0" t="n">
         <v>173920</v>
       </c>
-      <c r="G213" t="n">
+      <c r="G213" s="0" t="n">
         <v>8.827999999999999</v>
       </c>
-      <c r="H213" t="n">
+      <c r="H213" s="0" t="n">
         <v>0.0074</v>
       </c>
-      <c r="I213" t="n">
+      <c r="I213" s="0" t="n">
         <v>176560</v>
       </c>
-      <c r="J213" t="n">
+      <c r="J213" s="0" t="n">
         <v>2640</v>
       </c>
-      <c r="K213" t="n">
+      <c r="K213" s="0" t="n">
         <v>0.0152</v>
       </c>
-      <c r="L213" t="n">
+      <c r="L213" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M213" t="n">
+      <c r="M213" s="0" t="n">
         <v>0.0501</v>
       </c>
-      <c r="N213" t="n">
+      <c r="N213" s="0" t="n">
         <v>-0.0499</v>
       </c>
-      <c r="O213" t="inlineStr">
+      <c r="O213" s="0" t="inlineStr">
         <is>
           <t>📊权重预警偏离-5.0%</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
+      <c r="A214" s="0" t="inlineStr">
         <is>
           <t>20260618</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B214" s="0" t="inlineStr">
         <is>
           <t>科创50ETF</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
+      <c r="C214" s="0" t="inlineStr">
         <is>
           <t>588050</t>
         </is>
       </c>
-      <c r="D214" t="n">
+      <c r="D214" s="0" t="n">
         <v>60000</v>
       </c>
-      <c r="E214" t="n">
+      <c r="E214" s="0" t="n">
         <v>1.838</v>
       </c>
-      <c r="F214" t="n">
+      <c r="F214" s="0" t="n">
         <v>110280</v>
       </c>
-      <c r="G214" t="n">
+      <c r="G214" s="0" t="n">
         <v>1.958</v>
       </c>
-      <c r="H214" t="n">
+      <c r="H214" s="0" t="n">
         <v>0.0398</v>
       </c>
-      <c r="I214" t="n">
+      <c r="I214" s="0" t="n">
         <v>117480</v>
       </c>
-      <c r="J214" t="n">
+      <c r="J214" s="0" t="n">
         <v>7200</v>
       </c>
-      <c r="K214" t="n">
+      <c r="K214" s="0" t="n">
         <v>0.0653</v>
       </c>
-      <c r="L214" t="n">
+      <c r="L214" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M214" t="n">
+      <c r="M214" s="0" t="n">
         <v>0.0334</v>
       </c>
-      <c r="N214" t="n">
+      <c r="N214" s="0" t="n">
         <v>-0.0166</v>
       </c>
-      <c r="O214" t="inlineStr">
+      <c r="O214" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
+      <c r="A215" s="0" t="inlineStr">
         <is>
           <t>20260618</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B215" s="0" t="inlineStr">
         <is>
           <t>创业板ETF</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
+      <c r="C215" s="0" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="D215" t="n">
+      <c r="D215" s="0" t="n">
         <v>63000</v>
       </c>
-      <c r="E215" t="n">
+      <c r="E215" s="0" t="n">
         <v>3.968</v>
       </c>
-      <c r="F215" t="n">
+      <c r="F215" s="0" t="n">
         <v>249984</v>
       </c>
-      <c r="G215" t="n">
+      <c r="G215" s="0" t="n">
         <v>4.269</v>
       </c>
-      <c r="H215" t="n">
+      <c r="H215" s="0" t="n">
         <v>0.0206</v>
       </c>
-      <c r="I215" t="n">
+      <c r="I215" s="0" t="n">
         <v>268947</v>
       </c>
-      <c r="J215" t="n">
+      <c r="J215" s="0" t="n">
         <v>18963</v>
       </c>
-      <c r="K215" t="n">
+      <c r="K215" s="0" t="n">
         <v>0.0759</v>
       </c>
-      <c r="L215" t="n">
+      <c r="L215" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M215" t="n">
+      <c r="M215" s="0" t="n">
         <v>0.0764</v>
       </c>
-      <c r="N215" t="n">
+      <c r="N215" s="0" t="n">
         <v>0.0264</v>
       </c>
-      <c r="O215" t="inlineStr">
+      <c r="O215" s="0" t="inlineStr">
         <is>
           <t>🟢止盈第一档：浮盈7.6% &gt;= 7%，减仓20%</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
+      <c r="A216" s="0" t="inlineStr">
         <is>
           <t>20260618</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B216" s="0" t="inlineStr">
         <is>
           <t>红利低波ETF</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
+      <c r="C216" s="0" t="inlineStr">
         <is>
           <t>512890</t>
         </is>
       </c>
-      <c r="D216" t="n">
+      <c r="D216" s="0" t="n">
         <v>218000</v>
       </c>
-      <c r="E216" t="n">
+      <c r="E216" s="0" t="n">
         <v>1.15</v>
       </c>
-      <c r="F216" t="n">
+      <c r="F216" s="0" t="n">
         <v>250700</v>
       </c>
-      <c r="G216" t="n">
+      <c r="G216" s="0" t="n">
         <v>1.115</v>
       </c>
-      <c r="H216" t="n">
+      <c r="H216" s="0" t="n">
         <v>-0.0219</v>
       </c>
-      <c r="I216" t="n">
+      <c r="I216" s="0" t="n">
         <v>243070</v>
       </c>
-      <c r="J216" t="n">
+      <c r="J216" s="0" t="n">
         <v>-7630</v>
       </c>
-      <c r="K216" t="n">
+      <c r="K216" s="0" t="n">
         <v>-0.0304</v>
       </c>
-      <c r="L216" t="n">
+      <c r="L216" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M216" t="n">
+      <c r="M216" s="0" t="n">
         <v>0.06900000000000001</v>
       </c>
-      <c r="N216" t="n">
+      <c r="N216" s="0" t="n">
         <v>0.019</v>
       </c>
-      <c r="O216" t="inlineStr">
+      <c r="O216" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
+      <c r="A217" s="0" t="inlineStr">
         <is>
           <t>20260618</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B217" s="0" t="inlineStr">
         <is>
           <t>可转债ETF</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
+      <c r="C217" s="0" t="inlineStr">
         <is>
           <t>511380</t>
         </is>
       </c>
-      <c r="D217" t="n">
+      <c r="D217" s="0" t="n">
         <v>14500</v>
       </c>
-      <c r="E217" t="n">
+      <c r="E217" s="0" t="n">
         <v>13.8644</v>
       </c>
-      <c r="F217" t="n">
+      <c r="F217" s="0" t="n">
         <v>201033.8</v>
       </c>
-      <c r="G217" t="n">
+      <c r="G217" s="0" t="n">
         <v>14.067</v>
       </c>
-      <c r="H217" t="n">
+      <c r="H217" s="0" t="n">
         <v>-0.0064</v>
       </c>
-      <c r="I217" t="n">
+      <c r="I217" s="0" t="n">
         <v>203971.5</v>
       </c>
-      <c r="J217" t="n">
+      <c r="J217" s="0" t="n">
         <v>2937.7</v>
       </c>
-      <c r="K217" t="n">
+      <c r="K217" s="0" t="n">
         <v>0.0146</v>
       </c>
-      <c r="L217" t="n">
+      <c r="L217" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M217" t="n">
+      <c r="M217" s="0" t="n">
         <v>0.0579</v>
       </c>
-      <c r="N217" t="n">
+      <c r="N217" s="0" t="n">
         <v>-0.0421</v>
       </c>
-      <c r="O217" t="inlineStr">
+      <c r="O217" s="0" t="inlineStr">
         <is>
           <t>📊权重预警偏离-4.2%</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="A218" s="0" t="inlineStr">
         <is>
           <t>20260618</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B218" s="0" t="inlineStr">
         <is>
           <t>10年国债ETF</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
+      <c r="C218" s="0" t="inlineStr">
         <is>
           <t>511260</t>
         </is>
       </c>
-      <c r="D218" t="n">
+      <c r="D218" s="0" t="n">
         <v>3700</v>
       </c>
-      <c r="E218" t="n">
+      <c r="E218" s="0" t="n">
         <v>135.645</v>
       </c>
-      <c r="F218" t="n">
+      <c r="F218" s="0" t="n">
         <v>501886.5</v>
       </c>
-      <c r="G218" t="n">
+      <c r="G218" s="0" t="n">
         <v>135.984</v>
       </c>
-      <c r="H218" t="n">
+      <c r="H218" s="0" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I218" t="n">
+      <c r="I218" s="0" t="n">
         <v>503140.8</v>
       </c>
-      <c r="J218" t="n">
+      <c r="J218" s="0" t="n">
         <v>1254.3</v>
       </c>
-      <c r="K218" t="n">
+      <c r="K218" s="0" t="n">
         <v>0.0025</v>
       </c>
-      <c r="L218" t="n">
+      <c r="L218" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M218" t="n">
+      <c r="M218" s="0" t="n">
         <v>0.1429</v>
       </c>
-      <c r="N218" t="n">
+      <c r="N218" s="0" t="n">
         <v>0.0429</v>
       </c>
-      <c r="O218" t="inlineStr">
+      <c r="O218" s="0" t="inlineStr">
         <is>
           <t>📊权重预警偏离+4.3%</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
+      <c r="A219" s="0" t="inlineStr">
         <is>
           <t>20260618</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B219" s="0" t="inlineStr">
         <is>
           <t>5年国债ETF</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="C219" s="0" t="inlineStr">
         <is>
           <t>511010</t>
         </is>
       </c>
-      <c r="D219" t="n">
+      <c r="D219" s="0" t="n">
         <v>3500</v>
       </c>
-      <c r="E219" t="n">
+      <c r="E219" s="0" t="n">
         <v>141.2121</v>
       </c>
-      <c r="F219" t="n">
+      <c r="F219" s="0" t="n">
         <v>494242.35</v>
       </c>
-      <c r="G219" t="n">
+      <c r="G219" s="0" t="n">
         <v>141.431</v>
       </c>
-      <c r="H219" t="n">
+      <c r="H219" s="0" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="I219" t="n">
+      <c r="I219" s="0" t="n">
         <v>495008.5</v>
       </c>
-      <c r="J219" t="n">
+      <c r="J219" s="0" t="n">
         <v>766.15</v>
       </c>
-      <c r="K219" t="n">
+      <c r="K219" s="0" t="n">
         <v>0.0016</v>
       </c>
-      <c r="L219" t="n">
+      <c r="L219" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M219" t="n">
+      <c r="M219" s="0" t="n">
         <v>0.1406</v>
       </c>
-      <c r="N219" t="n">
+      <c r="N219" s="0" t="n">
         <v>0.0406</v>
       </c>
-      <c r="O219" t="inlineStr">
+      <c r="O219" s="0" t="inlineStr">
         <is>
           <t>📊权重预警偏离+4.1%</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
+      <c r="A220" s="0" t="inlineStr">
         <is>
           <t>20260618</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B220" s="0" t="inlineStr">
         <is>
           <t>短融ETF</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="C220" s="0" t="inlineStr">
         <is>
           <t>511360</t>
         </is>
       </c>
-      <c r="D220" t="n">
+      <c r="D220" s="0" t="n">
         <v>2200</v>
       </c>
-      <c r="E220" t="n">
+      <c r="E220" s="0" t="n">
         <v>113.462</v>
       </c>
-      <c r="F220" t="n">
+      <c r="F220" s="0" t="n">
         <v>249616.4</v>
       </c>
-      <c r="G220" t="n">
+      <c r="G220" s="0" t="n">
         <v>113.557</v>
       </c>
-      <c r="H220" t="n">
+      <c r="H220" s="0" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I220" t="n">
+      <c r="I220" s="0" t="n">
         <v>249825.4</v>
       </c>
-      <c r="J220" t="n">
+      <c r="J220" s="0" t="n">
         <v>209</v>
       </c>
-      <c r="K220" t="n">
+      <c r="K220" s="0" t="n">
         <v>0.0008</v>
       </c>
-      <c r="L220" t="n">
+      <c r="L220" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M220" t="n">
+      <c r="M220" s="0" t="n">
         <v>0.0709</v>
       </c>
-      <c r="N220" t="n">
+      <c r="N220" s="0" t="n">
         <v>0.0209</v>
       </c>
-      <c r="O220" t="inlineStr">
+      <c r="O220" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
+      <c r="A221" s="0" t="inlineStr">
         <is>
           <t>20260618</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B221" s="0" t="inlineStr">
         <is>
           <t>黄金ETF</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C221" s="0" t="inlineStr">
         <is>
           <t>518880</t>
         </is>
       </c>
-      <c r="D221" t="n">
+      <c r="D221" s="0" t="n">
         <v>55800</v>
       </c>
-      <c r="E221" t="n">
+      <c r="E221" s="0" t="n">
         <v>9.232699999999999</v>
       </c>
-      <c r="F221" t="n">
+      <c r="F221" s="0" t="n">
         <v>515184.66</v>
       </c>
-      <c r="G221" t="n">
+      <c r="G221" s="0" t="n">
         <v>8.907999999999999</v>
       </c>
-      <c r="H221" t="n">
+      <c r="H221" s="0" t="n">
         <v>-0.0055</v>
       </c>
-      <c r="I221" t="n">
+      <c r="I221" s="0" t="n">
         <v>497066.4</v>
       </c>
-      <c r="J221" t="n">
+      <c r="J221" s="0" t="n">
         <v>-18118.26</v>
       </c>
-      <c r="K221" t="n">
+      <c r="K221" s="0" t="n">
         <v>-0.0352</v>
       </c>
-      <c r="L221" t="n">
+      <c r="L221" s="0" t="n">
         <v>0.15</v>
       </c>
-      <c r="M221" t="n">
+      <c r="M221" s="0" t="n">
         <v>0.1411</v>
       </c>
-      <c r="N221" t="n">
+      <c r="N221" s="0" t="n">
         <v>-0.0089</v>
       </c>
-      <c r="O221" t="inlineStr">
+      <c r="O221" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
+      <c r="A222" s="0" t="inlineStr">
         <is>
           <t>20260618</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B222" s="0" t="inlineStr">
         <is>
           <t>银华日利ETF</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C222" s="0" t="inlineStr">
         <is>
           <t>511880</t>
         </is>
       </c>
-      <c r="G222" t="n">
+      <c r="G222" s="0" t="n">
         <v>100.533</v>
       </c>
-      <c r="H222" t="n">
+      <c r="H222" s="0" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I222" t="n">
+      <c r="I222" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J222" t="n">
+      <c r="J222" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K222" t="n">
+      <c r="K222" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="L222" t="n">
+      <c r="L222" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M222" t="n">
+      <c r="M222" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="N222" t="n">
+      <c r="N222" s="0" t="n">
         <v>-0.05</v>
       </c>
-      <c r="O222" t="inlineStr">
+      <c r="O222" s="0" t="inlineStr">
         <is>
           <t>📊权重预警偏离-5.0%</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
+      <c r="A223" s="0" t="inlineStr">
         <is>
           <t>20260618</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B223" s="0" t="inlineStr">
         <is>
           <t>华宝添益ETF</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C223" s="0" t="inlineStr">
         <is>
           <t>511990</t>
         </is>
       </c>
-      <c r="G223" t="n">
+      <c r="G223" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="I223" t="n">
+      <c r="I223" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J223" t="n">
+      <c r="J223" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K223" t="n">
+      <c r="K223" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="L223" t="n">
+      <c r="L223" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M223" t="n">
+      <c r="M223" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="N223" t="n">
+      <c r="N223" s="0" t="n">
         <v>-0.05</v>
       </c>
-      <c r="O223" t="inlineStr">
+      <c r="O223" s="0" t="inlineStr">
         <is>
           <t>📊权重预警偏离-5.0%</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
+      <c r="A224" s="0" t="inlineStr">
         <is>
           <t>20260605</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B224" s="0" t="inlineStr">
         <is>
           <t>沪深300ETF</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
+      <c r="C224" s="0" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="D224" t="n">
+      <c r="D224" s="0" t="n">
         <v>153800</v>
       </c>
-      <c r="E224" t="n">
+      <c r="E224" s="0" t="n">
         <v>4.885</v>
       </c>
-      <c r="F224" t="n">
+      <c r="F224" s="0" t="n">
         <v>751313</v>
       </c>
-      <c r="G224" t="n">
+      <c r="G224" s="0" t="n">
         <v>4.843</v>
       </c>
-      <c r="H224" t="n">
+      <c r="H224" s="0" t="n">
         <v>-0.0169</v>
       </c>
-      <c r="I224" t="n">
+      <c r="I224" s="0" t="n">
         <v>744853.4</v>
       </c>
-      <c r="J224" t="n">
+      <c r="J224" s="0" t="n">
         <v>-6459.6</v>
       </c>
-      <c r="K224" t="n">
+      <c r="K224" s="0" t="n">
         <v>-0.0086</v>
       </c>
-      <c r="L224" t="n">
+      <c r="L224" s="0" t="n">
         <v>0.15</v>
       </c>
-      <c r="M224" t="n">
+      <c r="M224" s="0" t="n">
         <v>0.2137</v>
       </c>
-      <c r="N224" t="n">
+      <c r="N224" s="0" t="n">
         <v>0.06370000000000001</v>
       </c>
-      <c r="O224" t="inlineStr">
+      <c r="O224" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
+      <c r="A225" s="0" t="inlineStr">
         <is>
           <t>20260605</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B225" s="0" t="inlineStr">
         <is>
           <t>中证500ETF</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
+      <c r="C225" s="0" t="inlineStr">
         <is>
           <t>510500</t>
         </is>
       </c>
-      <c r="D225" t="n">
+      <c r="D225" s="0" t="n">
         <v>20000</v>
       </c>
-      <c r="E225" t="n">
+      <c r="E225" s="0" t="n">
         <v>8.696</v>
       </c>
-      <c r="F225" t="n">
+      <c r="F225" s="0" t="n">
         <v>173920</v>
       </c>
-      <c r="G225" t="n">
+      <c r="G225" s="0" t="n">
         <v>8.339</v>
       </c>
-      <c r="H225" t="n">
+      <c r="H225" s="0" t="n">
         <v>-0.0129</v>
       </c>
-      <c r="I225" t="n">
+      <c r="I225" s="0" t="n">
         <v>166780</v>
       </c>
-      <c r="J225" t="n">
+      <c r="J225" s="0" t="n">
         <v>-7140</v>
       </c>
-      <c r="K225" t="n">
+      <c r="K225" s="0" t="n">
         <v>-0.0411</v>
       </c>
-      <c r="L225" t="n">
+      <c r="L225" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M225" t="n">
+      <c r="M225" s="0" t="n">
         <v>0.0479</v>
       </c>
-      <c r="N225" t="n">
+      <c r="N225" s="0" t="n">
         <v>-0.0521</v>
       </c>
-      <c r="O225" t="inlineStr">
+      <c r="O225" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
+      <c r="A226" s="0" t="inlineStr">
         <is>
           <t>20260605</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B226" s="0" t="inlineStr">
         <is>
           <t>科创50ETF</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="C226" s="0" t="inlineStr">
         <is>
           <t>588050</t>
         </is>
       </c>
-      <c r="D226" t="n">
+      <c r="D226" s="0" t="n">
         <v>60000</v>
       </c>
-      <c r="E226" t="n">
+      <c r="E226" s="0" t="n">
         <v>1.838</v>
       </c>
-      <c r="F226" t="n">
+      <c r="F226" s="0" t="n">
         <v>110280</v>
       </c>
-      <c r="G226" t="n">
+      <c r="G226" s="0" t="n">
         <v>1.714</v>
       </c>
-      <c r="H226" t="n">
+      <c r="H226" s="0" t="n">
         <v>-0.0387</v>
       </c>
-      <c r="I226" t="n">
+      <c r="I226" s="0" t="n">
         <v>102840</v>
       </c>
-      <c r="J226" t="n">
+      <c r="J226" s="0" t="n">
         <v>-7440</v>
       </c>
-      <c r="K226" t="n">
+      <c r="K226" s="0" t="n">
         <v>-0.0675</v>
       </c>
-      <c r="L226" t="n">
+      <c r="L226" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M226" t="n">
+      <c r="M226" s="0" t="n">
         <v>0.0295</v>
       </c>
-      <c r="N226" t="n">
+      <c r="N226" s="0" t="n">
         <v>-0.0205</v>
       </c>
-      <c r="O226" t="inlineStr">
+      <c r="O226" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
+      <c r="A227" s="0" t="inlineStr">
         <is>
           <t>20260605</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B227" s="0" t="inlineStr">
         <is>
           <t>创业板ETF</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C227" s="0" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="D227" t="n">
+      <c r="D227" s="0" t="n">
         <v>63000</v>
       </c>
-      <c r="E227" t="n">
+      <c r="E227" s="0" t="n">
         <v>3.968</v>
       </c>
-      <c r="F227" t="n">
+      <c r="F227" s="0" t="n">
         <v>249984</v>
       </c>
-      <c r="G227" t="n">
+      <c r="G227" s="0" t="n">
         <v>3.977</v>
       </c>
-      <c r="H227" t="n">
+      <c r="H227" s="0" t="n">
         <v>-0.03</v>
       </c>
-      <c r="I227" t="n">
+      <c r="I227" s="0" t="n">
         <v>250551</v>
       </c>
-      <c r="J227" t="n">
+      <c r="J227" s="0" t="n">
         <v>567</v>
       </c>
-      <c r="K227" t="n">
+      <c r="K227" s="0" t="n">
         <v>0.0023</v>
       </c>
-      <c r="L227" t="n">
+      <c r="L227" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M227" t="n">
+      <c r="M227" s="0" t="n">
         <v>0.07190000000000001</v>
       </c>
-      <c r="N227" t="n">
+      <c r="N227" s="0" t="n">
         <v>0.0219</v>
       </c>
-      <c r="O227" t="inlineStr">
+      <c r="O227" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
+      <c r="A228" s="0" t="inlineStr">
         <is>
           <t>20260605</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B228" s="0" t="inlineStr">
         <is>
           <t>红利低波ETF</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
+      <c r="C228" s="0" t="inlineStr">
         <is>
           <t>512890</t>
         </is>
       </c>
-      <c r="D228" t="n">
+      <c r="D228" s="0" t="n">
         <v>218000</v>
       </c>
-      <c r="E228" t="n">
+      <c r="E228" s="0" t="n">
         <v>1.15</v>
       </c>
-      <c r="F228" t="n">
+      <c r="F228" s="0" t="n">
         <v>250700</v>
       </c>
-      <c r="G228" t="n">
+      <c r="G228" s="0" t="n">
         <v>1.159</v>
       </c>
-      <c r="H228" t="n">
+      <c r="H228" s="0" t="n">
         <v>0.0009</v>
       </c>
-      <c r="I228" t="n">
+      <c r="I228" s="0" t="n">
         <v>252662</v>
       </c>
-      <c r="J228" t="n">
+      <c r="J228" s="0" t="n">
         <v>1962</v>
       </c>
-      <c r="K228" t="n">
+      <c r="K228" s="0" t="n">
         <v>0.0078</v>
       </c>
-      <c r="L228" t="n">
+      <c r="L228" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M228" t="n">
+      <c r="M228" s="0" t="n">
         <v>0.0725</v>
       </c>
-      <c r="N228" t="n">
+      <c r="N228" s="0" t="n">
         <v>0.0225</v>
       </c>
-      <c r="O228" t="inlineStr">
+      <c r="O228" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
+      <c r="A229" s="0" t="inlineStr">
         <is>
           <t>20260605</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B229" s="0" t="inlineStr">
         <is>
           <t>可转债ETF</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
+      <c r="C229" s="0" t="inlineStr">
         <is>
           <t>511380</t>
         </is>
       </c>
-      <c r="D229" t="n">
+      <c r="D229" s="0" t="n">
         <v>14500</v>
       </c>
-      <c r="E229" t="n">
+      <c r="E229" s="0" t="n">
         <v>13.8644</v>
       </c>
-      <c r="F229" t="n">
+      <c r="F229" s="0" t="n">
         <v>201033.8</v>
       </c>
-      <c r="G229" t="n">
+      <c r="G229" s="0" t="n">
         <v>13.948</v>
       </c>
-      <c r="H229" t="n">
+      <c r="H229" s="0" t="n">
         <v>-0.0036</v>
       </c>
-      <c r="I229" t="n">
+      <c r="I229" s="0" t="n">
         <v>202246</v>
       </c>
-      <c r="J229" t="n">
+      <c r="J229" s="0" t="n">
         <v>1212.2</v>
       </c>
-      <c r="K229" t="n">
+      <c r="K229" s="0" t="n">
         <v>0.006</v>
       </c>
-      <c r="L229" t="n">
+      <c r="L229" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M229" t="n">
+      <c r="M229" s="0" t="n">
         <v>0.058</v>
       </c>
-      <c r="N229" t="n">
+      <c r="N229" s="0" t="n">
         <v>-0.042</v>
       </c>
-      <c r="O229" t="inlineStr">
+      <c r="O229" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
+      <c r="A230" s="0" t="inlineStr">
         <is>
           <t>20260605</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B230" s="0" t="inlineStr">
         <is>
           <t>10年国债ETF</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
+      <c r="C230" s="0" t="inlineStr">
         <is>
           <t>511260</t>
         </is>
       </c>
-      <c r="D230" t="n">
+      <c r="D230" s="0" t="n">
         <v>3700</v>
       </c>
-      <c r="E230" t="n">
+      <c r="E230" s="0" t="n">
         <v>135.645</v>
       </c>
-      <c r="F230" t="n">
-        <v>501886.5000000001</v>
-      </c>
-      <c r="G230" t="n">
+      <c r="F230" s="0" t="n">
+        <v>501886.5</v>
+      </c>
+      <c r="G230" s="0" t="n">
         <v>136.071</v>
       </c>
-      <c r="H230" t="n">
+      <c r="H230" s="0" t="n">
         <v>-0.0005</v>
       </c>
-      <c r="I230" t="n">
+      <c r="I230" s="0" t="n">
         <v>503462.7</v>
       </c>
-      <c r="J230" t="n">
+      <c r="J230" s="0" t="n">
         <v>1576.2</v>
       </c>
-      <c r="K230" t="n">
+      <c r="K230" s="0" t="n">
         <v>0.0031</v>
       </c>
-      <c r="L230" t="n">
+      <c r="L230" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M230" t="n">
+      <c r="M230" s="0" t="n">
         <v>0.1445</v>
       </c>
-      <c r="N230" t="n">
+      <c r="N230" s="0" t="n">
         <v>0.0445</v>
       </c>
-      <c r="O230" t="inlineStr">
+      <c r="O230" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
+      <c r="A231" s="0" t="inlineStr">
         <is>
           <t>20260605</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B231" s="0" t="inlineStr">
         <is>
           <t>5年国债ETF</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
+      <c r="C231" s="0" t="inlineStr">
         <is>
           <t>511010</t>
         </is>
       </c>
-      <c r="D231" t="n">
+      <c r="D231" s="0" t="n">
         <v>3500</v>
       </c>
-      <c r="E231" t="n">
+      <c r="E231" s="0" t="n">
         <v>141.2121</v>
       </c>
-      <c r="F231" t="n">
+      <c r="F231" s="0" t="n">
         <v>494242.35</v>
       </c>
-      <c r="G231" t="n">
+      <c r="G231" s="0" t="n">
         <v>141.5</v>
       </c>
-      <c r="I231" t="n">
+      <c r="I231" s="0" t="n">
         <v>495250</v>
       </c>
-      <c r="J231" t="n">
+      <c r="J231" s="0" t="n">
         <v>1007.65</v>
       </c>
-      <c r="K231" t="n">
+      <c r="K231" s="0" t="n">
         <v>0.002</v>
       </c>
-      <c r="L231" t="n">
+      <c r="L231" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M231" t="n">
+      <c r="M231" s="0" t="n">
         <v>0.1421</v>
       </c>
-      <c r="N231" t="n">
+      <c r="N231" s="0" t="n">
         <v>0.0421</v>
       </c>
-      <c r="O231" t="inlineStr">
+      <c r="O231" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
+      <c r="A232" s="0" t="inlineStr">
         <is>
           <t>20260605</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B232" s="0" t="inlineStr">
         <is>
           <t>短融ETF</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
+      <c r="C232" s="0" t="inlineStr">
         <is>
           <t>511360</t>
         </is>
       </c>
-      <c r="D232" t="n">
+      <c r="D232" s="0" t="n">
         <v>2200</v>
       </c>
-      <c r="E232" t="n">
+      <c r="E232" s="0" t="n">
         <v>113.462</v>
       </c>
-      <c r="F232" t="n">
+      <c r="F232" s="0" t="n">
         <v>249616.4</v>
       </c>
-      <c r="G232" t="n">
+      <c r="G232" s="0" t="n">
         <v>113.551</v>
       </c>
-      <c r="H232" t="n">
+      <c r="H232" s="0" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I232" t="n">
+      <c r="I232" s="0" t="n">
         <v>249812.2</v>
       </c>
-      <c r="J232" t="n">
+      <c r="J232" s="0" t="n">
         <v>195.8</v>
       </c>
-      <c r="K232" t="n">
+      <c r="K232" s="0" t="n">
         <v>0.0008</v>
       </c>
-      <c r="L232" t="n">
+      <c r="L232" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M232" t="n">
+      <c r="M232" s="0" t="n">
         <v>0.0717</v>
       </c>
-      <c r="N232" t="n">
+      <c r="N232" s="0" t="n">
         <v>0.0217</v>
       </c>
-      <c r="O232" t="inlineStr">
+      <c r="O232" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
+      <c r="A233" s="0" t="inlineStr">
         <is>
           <t>20260605</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B233" s="0" t="inlineStr">
         <is>
           <t>黄金ETF</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
+      <c r="C233" s="0" t="inlineStr">
         <is>
           <t>518880</t>
         </is>
       </c>
-      <c r="D233" t="n">
+      <c r="D233" s="0" t="n">
         <v>55800</v>
       </c>
-      <c r="E233" t="n">
+      <c r="E233" s="0" t="n">
         <v>9.232699999999999</v>
       </c>
-      <c r="F233" t="n">
+      <c r="F233" s="0" t="n">
         <v>515184.66</v>
       </c>
-      <c r="G233" t="n">
+      <c r="G233" s="0" t="n">
         <v>9.252000000000001</v>
       </c>
-      <c r="H233" t="n">
+      <c r="H233" s="0" t="n">
         <v>-0.0041</v>
       </c>
-      <c r="I233" t="n">
+      <c r="I233" s="0" t="n">
         <v>516261.6</v>
       </c>
-      <c r="J233" t="n">
+      <c r="J233" s="0" t="n">
         <v>1076.94</v>
       </c>
-      <c r="K233" t="n">
+      <c r="K233" s="0" t="n">
         <v>0.0021</v>
       </c>
-      <c r="L233" t="n">
+      <c r="L233" s="0" t="n">
         <v>0.15</v>
       </c>
-      <c r="M233" t="n">
+      <c r="M233" s="0" t="n">
         <v>0.1482</v>
       </c>
-      <c r="N233" t="n">
+      <c r="N233" s="0" t="n">
         <v>-0.0018</v>
       </c>
-      <c r="O233" t="inlineStr">
+      <c r="O233" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
+      <c r="A234" s="0" t="inlineStr">
         <is>
           <t>20260605</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B234" s="0" t="inlineStr">
         <is>
           <t>银华日利ETF</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
+      <c r="C234" s="0" t="inlineStr">
         <is>
           <t>511880</t>
         </is>
       </c>
-      <c r="G234" t="n">
+      <c r="G234" s="0" t="n">
         <v>100.523</v>
       </c>
-      <c r="H234" t="n">
+      <c r="H234" s="0" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I234" t="n">
+      <c r="I234" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J234" t="n">
+      <c r="J234" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K234" t="n">
+      <c r="K234" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="L234" t="n">
+      <c r="L234" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M234" t="n">
+      <c r="M234" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="N234" t="n">
+      <c r="N234" s="0" t="n">
         <v>-0.05</v>
       </c>
-      <c r="O234" t="inlineStr">
+      <c r="O234" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
+      <c r="A235" s="0" t="inlineStr">
         <is>
           <t>20260605</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B235" s="0" t="inlineStr">
         <is>
           <t>华宝添益ETF</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="C235" s="0" t="inlineStr">
         <is>
           <t>511990</t>
         </is>
       </c>
-      <c r="G235" t="n">
+      <c r="G235" s="0" t="n">
         <v>100.007</v>
       </c>
-      <c r="H235" t="n">
+      <c r="H235" s="0" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I235" t="n">
+      <c r="I235" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J235" t="n">
+      <c r="J235" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K235" t="n">
+      <c r="K235" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="L235" t="n">
+      <c r="L235" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M235" t="n">
+      <c r="M235" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="N235" t="n">
+      <c r="N235" s="0" t="n">
         <v>-0.05</v>
       </c>
-      <c r="O235" t="inlineStr">
+      <c r="O235" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
+      <c r="A236" s="0" t="inlineStr">
         <is>
           <t>20260608</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B236" s="0" t="inlineStr">
         <is>
           <t>沪深300ETF</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
+      <c r="C236" s="0" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="D236" t="n">
+      <c r="D236" s="0" t="n">
         <v>153800</v>
       </c>
-      <c r="E236" t="n">
+      <c r="E236" s="0" t="n">
         <v>4.885</v>
       </c>
-      <c r="F236" t="n">
+      <c r="F236" s="0" t="n">
         <v>751313</v>
       </c>
-      <c r="G236" t="n">
+      <c r="G236" s="0" t="n">
         <v>4.739</v>
       </c>
-      <c r="H236" t="n">
+      <c r="H236" s="0" t="n">
         <v>-0.0215</v>
       </c>
-      <c r="I236" t="n">
+      <c r="I236" s="0" t="n">
         <v>728858.2</v>
       </c>
-      <c r="J236" t="n">
+      <c r="J236" s="0" t="n">
         <v>-22454.8</v>
       </c>
-      <c r="K236" t="n">
+      <c r="K236" s="0" t="n">
         <v>-0.0299</v>
       </c>
-      <c r="L236" t="n">
+      <c r="L236" s="0" t="n">
         <v>0.15</v>
       </c>
-      <c r="M236" t="n">
+      <c r="M236" s="0" t="n">
         <v>0.2124</v>
       </c>
-      <c r="N236" t="n">
+      <c r="N236" s="0" t="n">
         <v>0.0624</v>
       </c>
-      <c r="O236" t="inlineStr">
+      <c r="O236" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
+      <c r="A237" s="0" t="inlineStr">
         <is>
           <t>20260608</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B237" s="0" t="inlineStr">
         <is>
           <t>中证500ETF</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
+      <c r="C237" s="0" t="inlineStr">
         <is>
           <t>510500</t>
         </is>
       </c>
-      <c r="D237" t="n">
+      <c r="D237" s="0" t="n">
         <v>20000</v>
       </c>
-      <c r="E237" t="n">
+      <c r="E237" s="0" t="n">
         <v>8.696</v>
       </c>
-      <c r="F237" t="n">
+      <c r="F237" s="0" t="n">
         <v>173920</v>
       </c>
-      <c r="G237" t="n">
+      <c r="G237" s="0" t="n">
         <v>8.068</v>
       </c>
-      <c r="H237" t="n">
+      <c r="H237" s="0" t="n">
         <v>-0.0325</v>
       </c>
-      <c r="I237" t="n">
+      <c r="I237" s="0" t="n">
         <v>161360</v>
       </c>
-      <c r="J237" t="n">
+      <c r="J237" s="0" t="n">
         <v>-12560</v>
       </c>
-      <c r="K237" t="n">
+      <c r="K237" s="0" t="n">
         <v>-0.0722</v>
       </c>
-      <c r="L237" t="n">
+      <c r="L237" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M237" t="n">
+      <c r="M237" s="0" t="n">
         <v>0.047</v>
       </c>
-      <c r="N237" t="n">
+      <c r="N237" s="0" t="n">
         <v>-0.053</v>
       </c>
-      <c r="O237" t="inlineStr">
+      <c r="O237" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
+      <c r="A238" s="0" t="inlineStr">
         <is>
           <t>20260608</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B238" s="0" t="inlineStr">
         <is>
           <t>科创50ETF</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
+      <c r="C238" s="0" t="inlineStr">
         <is>
           <t>588050</t>
         </is>
       </c>
-      <c r="D238" t="n">
+      <c r="D238" s="0" t="n">
         <v>60000</v>
       </c>
-      <c r="E238" t="n">
+      <c r="E238" s="0" t="n">
         <v>1.838</v>
       </c>
-      <c r="F238" t="n">
+      <c r="F238" s="0" t="n">
         <v>110280</v>
       </c>
-      <c r="G238" t="n">
+      <c r="G238" s="0" t="n">
         <v>1.641</v>
       </c>
-      <c r="H238" t="n">
+      <c r="H238" s="0" t="n">
         <v>-0.0426</v>
       </c>
-      <c r="I238" t="n">
+      <c r="I238" s="0" t="n">
         <v>98460</v>
       </c>
-      <c r="J238" t="n">
+      <c r="J238" s="0" t="n">
         <v>-11820</v>
       </c>
-      <c r="K238" t="n">
+      <c r="K238" s="0" t="n">
         <v>-0.1072</v>
       </c>
-      <c r="L238" t="n">
+      <c r="L238" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M238" t="n">
+      <c r="M238" s="0" t="n">
         <v>0.0287</v>
       </c>
-      <c r="N238" t="n">
+      <c r="N238" s="0" t="n">
         <v>-0.0213</v>
       </c>
-      <c r="O238" t="inlineStr">
+      <c r="O238" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
+      <c r="A239" s="0" t="inlineStr">
         <is>
           <t>20260608</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B239" s="0" t="inlineStr">
         <is>
           <t>创业板ETF</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
+      <c r="C239" s="0" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="D239" t="n">
+      <c r="D239" s="0" t="n">
         <v>63000</v>
       </c>
-      <c r="E239" t="n">
+      <c r="E239" s="0" t="n">
         <v>3.968</v>
       </c>
-      <c r="F239" t="n">
+      <c r="F239" s="0" t="n">
         <v>249984</v>
       </c>
-      <c r="G239" t="n">
+      <c r="G239" s="0" t="n">
         <v>3.827</v>
       </c>
-      <c r="H239" t="n">
+      <c r="H239" s="0" t="n">
         <v>-0.0377</v>
       </c>
-      <c r="I239" t="n">
+      <c r="I239" s="0" t="n">
         <v>241101</v>
       </c>
-      <c r="J239" t="n">
+      <c r="J239" s="0" t="n">
         <v>-8883</v>
       </c>
-      <c r="K239" t="n">
+      <c r="K239" s="0" t="n">
         <v>-0.0355</v>
       </c>
-      <c r="L239" t="n">
+      <c r="L239" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M239" t="n">
+      <c r="M239" s="0" t="n">
         <v>0.0703</v>
       </c>
-      <c r="N239" t="n">
+      <c r="N239" s="0" t="n">
         <v>0.0203</v>
       </c>
-      <c r="O239" t="inlineStr">
+      <c r="O239" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
+      <c r="A240" s="0" t="inlineStr">
         <is>
           <t>20260608</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B240" s="0" t="inlineStr">
         <is>
           <t>红利低波ETF</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
+      <c r="C240" s="0" t="inlineStr">
         <is>
           <t>512890</t>
         </is>
       </c>
-      <c r="D240" t="n">
+      <c r="D240" s="0" t="n">
         <v>218000</v>
       </c>
-      <c r="E240" t="n">
+      <c r="E240" s="0" t="n">
         <v>1.15</v>
       </c>
-      <c r="F240" t="n">
+      <c r="F240" s="0" t="n">
         <v>250700</v>
       </c>
-      <c r="G240" t="n">
+      <c r="G240" s="0" t="n">
         <v>1.165</v>
       </c>
-      <c r="H240" t="n">
+      <c r="H240" s="0" t="n">
         <v>0.0052</v>
       </c>
-      <c r="I240" t="n">
+      <c r="I240" s="0" t="n">
         <v>253970</v>
       </c>
-      <c r="J240" t="n">
+      <c r="J240" s="0" t="n">
         <v>3270</v>
       </c>
-      <c r="K240" t="n">
+      <c r="K240" s="0" t="n">
         <v>0.013</v>
       </c>
-      <c r="L240" t="n">
+      <c r="L240" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M240" t="n">
+      <c r="M240" s="0" t="n">
         <v>0.074</v>
       </c>
-      <c r="N240" t="n">
+      <c r="N240" s="0" t="n">
         <v>0.024</v>
       </c>
-      <c r="O240" t="inlineStr">
+      <c r="O240" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
+      <c r="A241" s="0" t="inlineStr">
         <is>
           <t>20260608</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B241" s="0" t="inlineStr">
         <is>
           <t>可转债ETF</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="C241" s="0" t="inlineStr">
         <is>
           <t>511380</t>
         </is>
       </c>
-      <c r="D241" t="n">
+      <c r="D241" s="0" t="n">
         <v>14500</v>
       </c>
-      <c r="E241" t="n">
+      <c r="E241" s="0" t="n">
         <v>13.8644</v>
       </c>
-      <c r="F241" t="n">
+      <c r="F241" s="0" t="n">
         <v>201033.8</v>
       </c>
-      <c r="G241" t="n">
+      <c r="G241" s="0" t="n">
         <v>13.824</v>
       </c>
-      <c r="H241" t="n">
+      <c r="H241" s="0" t="n">
         <v>-0.0089</v>
       </c>
-      <c r="I241" t="n">
+      <c r="I241" s="0" t="n">
         <v>200448</v>
       </c>
-      <c r="J241" t="n">
+      <c r="J241" s="0" t="n">
         <v>-585.8</v>
       </c>
-      <c r="K241" t="n">
+      <c r="K241" s="0" t="n">
         <v>-0.0029</v>
       </c>
-      <c r="L241" t="n">
+      <c r="L241" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M241" t="n">
+      <c r="M241" s="0" t="n">
         <v>0.0584</v>
       </c>
-      <c r="N241" t="n">
+      <c r="N241" s="0" t="n">
         <v>-0.0416</v>
       </c>
-      <c r="O241" t="inlineStr">
+      <c r="O241" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
+      <c r="A242" s="0" t="inlineStr">
         <is>
           <t>20260608</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B242" s="0" t="inlineStr">
         <is>
           <t>10年国债ETF</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
+      <c r="C242" s="0" t="inlineStr">
         <is>
           <t>511260</t>
         </is>
       </c>
-      <c r="D242" t="n">
+      <c r="D242" s="0" t="n">
         <v>3700</v>
       </c>
-      <c r="E242" t="n">
+      <c r="E242" s="0" t="n">
         <v>135.645</v>
       </c>
-      <c r="F242" t="n">
-        <v>501886.5000000001</v>
-      </c>
-      <c r="G242" t="n">
+      <c r="F242" s="0" t="n">
+        <v>501886.5</v>
+      </c>
+      <c r="G242" s="0" t="n">
         <v>135.899</v>
       </c>
-      <c r="H242" t="n">
+      <c r="H242" s="0" t="n">
         <v>-0.0013</v>
       </c>
-      <c r="I242" t="n">
+      <c r="I242" s="0" t="n">
         <v>502826.3</v>
       </c>
-      <c r="J242" t="n">
+      <c r="J242" s="0" t="n">
         <v>939.8</v>
       </c>
-      <c r="K242" t="n">
+      <c r="K242" s="0" t="n">
         <v>0.0019</v>
       </c>
-      <c r="L242" t="n">
+      <c r="L242" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M242" t="n">
+      <c r="M242" s="0" t="n">
         <v>0.1465</v>
       </c>
-      <c r="N242" t="n">
+      <c r="N242" s="0" t="n">
         <v>0.0465</v>
       </c>
-      <c r="O242" t="inlineStr">
+      <c r="O242" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
+      <c r="A243" s="0" t="inlineStr">
         <is>
           <t>20260608</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B243" s="0" t="inlineStr">
         <is>
           <t>5年国债ETF</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
+      <c r="C243" s="0" t="inlineStr">
         <is>
           <t>511010</t>
         </is>
       </c>
-      <c r="D243" t="n">
+      <c r="D243" s="0" t="n">
         <v>3500</v>
       </c>
-      <c r="E243" t="n">
+      <c r="E243" s="0" t="n">
         <v>141.2121</v>
       </c>
-      <c r="F243" t="n">
+      <c r="F243" s="0" t="n">
         <v>494242.35</v>
       </c>
-      <c r="G243" t="n">
+      <c r="G243" s="0" t="n">
         <v>141.409</v>
       </c>
-      <c r="H243" t="n">
+      <c r="H243" s="0" t="n">
         <v>-0.0005999999999999999</v>
       </c>
-      <c r="I243" t="n">
+      <c r="I243" s="0" t="n">
         <v>494931.5</v>
       </c>
-      <c r="J243" t="n">
+      <c r="J243" s="0" t="n">
         <v>689.15</v>
       </c>
-      <c r="K243" t="n">
+      <c r="K243" s="0" t="n">
         <v>0.0014</v>
       </c>
-      <c r="L243" t="n">
+      <c r="L243" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M243" t="n">
+      <c r="M243" s="0" t="n">
         <v>0.1442</v>
       </c>
-      <c r="N243" t="n">
+      <c r="N243" s="0" t="n">
         <v>0.0442</v>
       </c>
-      <c r="O243" t="inlineStr">
+      <c r="O243" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="A244" s="0" t="inlineStr">
         <is>
           <t>20260608</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B244" s="0" t="inlineStr">
         <is>
           <t>短融ETF</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
+      <c r="C244" s="0" t="inlineStr">
         <is>
           <t>511360</t>
         </is>
       </c>
-      <c r="D244" t="n">
+      <c r="D244" s="0" t="n">
         <v>2200</v>
       </c>
-      <c r="E244" t="n">
+      <c r="E244" s="0" t="n">
         <v>113.462</v>
       </c>
-      <c r="F244" t="n">
+      <c r="F244" s="0" t="n">
         <v>249616.4</v>
       </c>
-      <c r="G244" t="n">
+      <c r="G244" s="0" t="n">
         <v>113.558</v>
       </c>
-      <c r="H244" t="n">
+      <c r="H244" s="0" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I244" t="n">
+      <c r="I244" s="0" t="n">
         <v>249827.6</v>
       </c>
-      <c r="J244" t="n">
+      <c r="J244" s="0" t="n">
         <v>211.2</v>
       </c>
-      <c r="K244" t="n">
+      <c r="K244" s="0" t="n">
         <v>0.0008</v>
       </c>
-      <c r="L244" t="n">
+      <c r="L244" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M244" t="n">
+      <c r="M244" s="0" t="n">
         <v>0.0728</v>
       </c>
-      <c r="N244" t="n">
+      <c r="N244" s="0" t="n">
         <v>0.0228</v>
       </c>
-      <c r="O244" t="inlineStr">
+      <c r="O244" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
+      <c r="A245" s="0" t="inlineStr">
         <is>
           <t>20260608</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B245" s="0" t="inlineStr">
         <is>
           <t>黄金ETF</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="C245" s="0" t="inlineStr">
         <is>
           <t>518880</t>
         </is>
       </c>
-      <c r="D245" t="n">
+      <c r="D245" s="0" t="n">
         <v>55800</v>
       </c>
-      <c r="E245" t="n">
+      <c r="E245" s="0" t="n">
         <v>9.232699999999999</v>
       </c>
-      <c r="F245" t="n">
+      <c r="F245" s="0" t="n">
         <v>515184.66</v>
       </c>
-      <c r="G245" t="n">
+      <c r="G245" s="0" t="n">
         <v>8.952999999999999</v>
       </c>
-      <c r="H245" t="n">
+      <c r="H245" s="0" t="n">
         <v>-0.0323</v>
       </c>
-      <c r="I245" t="n">
+      <c r="I245" s="0" t="n">
         <v>499577.4</v>
       </c>
-      <c r="J245" t="n">
+      <c r="J245" s="0" t="n">
         <v>-15607.26</v>
       </c>
-      <c r="K245" t="n">
+      <c r="K245" s="0" t="n">
         <v>-0.0303</v>
       </c>
-      <c r="L245" t="n">
+      <c r="L245" s="0" t="n">
         <v>0.15</v>
       </c>
-      <c r="M245" t="n">
+      <c r="M245" s="0" t="n">
         <v>0.1456</v>
       </c>
-      <c r="N245" t="n">
+      <c r="N245" s="0" t="n">
         <v>-0.0044</v>
       </c>
-      <c r="O245" t="inlineStr">
+      <c r="O245" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
+      <c r="A246" s="0" t="inlineStr">
         <is>
           <t>20260608</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B246" s="0" t="inlineStr">
         <is>
           <t>银华日利ETF</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
+      <c r="C246" s="0" t="inlineStr">
         <is>
           <t>511880</t>
         </is>
       </c>
-      <c r="G246" t="n">
+      <c r="G246" s="0" t="n">
         <v>100.516</v>
       </c>
-      <c r="H246" t="n">
+      <c r="H246" s="0" t="n">
         <v>-0.0001</v>
       </c>
-      <c r="I246" t="n">
+      <c r="I246" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J246" t="n">
+      <c r="J246" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K246" t="n">
+      <c r="K246" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="L246" t="n">
+      <c r="L246" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M246" t="n">
+      <c r="M246" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="N246" t="n">
+      <c r="N246" s="0" t="n">
         <v>-0.05</v>
       </c>
-      <c r="O246" t="inlineStr">
+      <c r="O246" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
+      <c r="A247" s="0" t="inlineStr">
         <is>
           <t>20260608</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B247" s="0" t="inlineStr">
         <is>
           <t>华宝添益ETF</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="C247" s="0" t="inlineStr">
         <is>
           <t>511990</t>
         </is>
       </c>
-      <c r="G247" t="n">
+      <c r="G247" s="0" t="n">
         <v>100.002</v>
       </c>
-      <c r="H247" t="n">
+      <c r="H247" s="0" t="n">
         <v>-0.0001</v>
       </c>
-      <c r="I247" t="n">
+      <c r="I247" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J247" t="n">
+      <c r="J247" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K247" t="n">
+      <c r="K247" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="L247" t="n">
+      <c r="L247" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M247" t="n">
+      <c r="M247" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="N247" t="n">
+      <c r="N247" s="0" t="n">
         <v>-0.05</v>
       </c>
-      <c r="O247" t="inlineStr">
+      <c r="O247" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
+      <c r="A248" s="0" t="inlineStr">
         <is>
           <t>20260612</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B248" s="0" t="inlineStr">
         <is>
           <t>沪深300ETF</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
+      <c r="C248" s="0" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="D248" t="n">
+      <c r="D248" s="0" t="n">
         <v>153800</v>
       </c>
-      <c r="E248" t="n">
+      <c r="E248" s="0" t="n">
         <v>4.885</v>
       </c>
-      <c r="F248" t="n">
+      <c r="F248" s="0" t="n">
         <v>751313</v>
       </c>
-      <c r="G248" t="n">
+      <c r="G248" s="0" t="n">
         <v>4.818</v>
       </c>
-      <c r="H248" t="n">
+      <c r="H248" s="0" t="n">
         <v>0.0141</v>
       </c>
-      <c r="I248" t="n">
-        <v>741008.3999999999</v>
-      </c>
-      <c r="J248" t="n">
+      <c r="I248" s="0" t="n">
+        <v>741008.4</v>
+      </c>
+      <c r="J248" s="0" t="n">
         <v>-10304.6</v>
       </c>
-      <c r="K248" t="n">
+      <c r="K248" s="0" t="n">
         <v>-0.0137</v>
       </c>
-      <c r="L248" t="n">
+      <c r="L248" s="0" t="n">
         <v>0.15</v>
       </c>
-      <c r="M248" t="n">
+      <c r="M248" s="0" t="n">
         <v>0.2156</v>
       </c>
-      <c r="N248" t="n">
+      <c r="N248" s="0" t="n">
         <v>0.06560000000000001</v>
       </c>
-      <c r="O248" t="inlineStr">
+      <c r="O248" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
+      <c r="A249" s="0" t="inlineStr">
         <is>
           <t>20260612</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B249" s="0" t="inlineStr">
         <is>
           <t>中证500ETF</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="C249" s="0" t="inlineStr">
         <is>
           <t>510500</t>
         </is>
       </c>
-      <c r="D249" t="n">
+      <c r="D249" s="0" t="n">
         <v>20000</v>
       </c>
-      <c r="E249" t="n">
+      <c r="E249" s="0" t="n">
         <v>8.696</v>
       </c>
-      <c r="F249" t="n">
+      <c r="F249" s="0" t="n">
         <v>173920</v>
       </c>
-      <c r="G249" t="n">
+      <c r="G249" s="0" t="n">
         <v>8.242000000000001</v>
       </c>
-      <c r="H249" t="n">
+      <c r="H249" s="0" t="n">
         <v>0.0134</v>
       </c>
-      <c r="I249" t="n">
+      <c r="I249" s="0" t="n">
         <v>164840</v>
       </c>
-      <c r="J249" t="n">
+      <c r="J249" s="0" t="n">
         <v>-9080</v>
       </c>
-      <c r="K249" t="n">
+      <c r="K249" s="0" t="n">
         <v>-0.0522</v>
       </c>
-      <c r="L249" t="n">
+      <c r="L249" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M249" t="n">
+      <c r="M249" s="0" t="n">
         <v>0.048</v>
       </c>
-      <c r="N249" t="n">
+      <c r="N249" s="0" t="n">
         <v>-0.052</v>
       </c>
-      <c r="O249" t="inlineStr">
+      <c r="O249" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
+      <c r="A250" s="0" t="inlineStr">
         <is>
           <t>20260612</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B250" s="0" t="inlineStr">
         <is>
           <t>科创50ETF</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="C250" s="0" t="inlineStr">
         <is>
           <t>588050</t>
         </is>
       </c>
-      <c r="D250" t="n">
+      <c r="D250" s="0" t="n">
         <v>60000</v>
       </c>
-      <c r="E250" t="n">
+      <c r="E250" s="0" t="n">
         <v>1.838</v>
       </c>
-      <c r="F250" t="n">
+      <c r="F250" s="0" t="n">
         <v>110280</v>
       </c>
-      <c r="G250" t="n">
+      <c r="G250" s="0" t="n">
         <v>1.709</v>
       </c>
-      <c r="H250" t="n">
+      <c r="H250" s="0" t="n">
         <v>-0.0005999999999999999</v>
       </c>
-      <c r="I250" t="n">
+      <c r="I250" s="0" t="n">
         <v>102540</v>
       </c>
-      <c r="J250" t="n">
+      <c r="J250" s="0" t="n">
         <v>-7740</v>
       </c>
-      <c r="K250" t="n">
+      <c r="K250" s="0" t="n">
         <v>-0.0702</v>
       </c>
-      <c r="L250" t="n">
+      <c r="L250" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M250" t="n">
+      <c r="M250" s="0" t="n">
         <v>0.0298</v>
       </c>
-      <c r="N250" t="n">
+      <c r="N250" s="0" t="n">
         <v>-0.0202</v>
       </c>
-      <c r="O250" t="inlineStr">
+      <c r="O250" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
+      <c r="A251" s="0" t="inlineStr">
         <is>
           <t>20260612</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B251" s="0" t="inlineStr">
         <is>
           <t>创业板ETF</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
+      <c r="C251" s="0" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="D251" t="n">
+      <c r="D251" s="0" t="n">
         <v>63000</v>
       </c>
-      <c r="E251" t="n">
+      <c r="E251" s="0" t="n">
         <v>3.968</v>
       </c>
-      <c r="F251" t="n">
+      <c r="F251" s="0" t="n">
         <v>249984</v>
       </c>
-      <c r="G251" t="n">
+      <c r="G251" s="0" t="n">
         <v>3.846</v>
       </c>
-      <c r="H251" t="n">
+      <c r="H251" s="0" t="n">
         <v>0.0042</v>
       </c>
-      <c r="I251" t="n">
+      <c r="I251" s="0" t="n">
         <v>242298</v>
       </c>
-      <c r="J251" t="n">
+      <c r="J251" s="0" t="n">
         <v>-7686</v>
       </c>
-      <c r="K251" t="n">
+      <c r="K251" s="0" t="n">
         <v>-0.0307</v>
       </c>
-      <c r="L251" t="n">
+      <c r="L251" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M251" t="n">
+      <c r="M251" s="0" t="n">
         <v>0.07049999999999999</v>
       </c>
-      <c r="N251" t="n">
+      <c r="N251" s="0" t="n">
         <v>0.0205</v>
       </c>
-      <c r="O251" t="inlineStr">
+      <c r="O251" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
+      <c r="A252" s="0" t="inlineStr">
         <is>
           <t>20260612</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B252" s="0" t="inlineStr">
         <is>
           <t>红利低波ETF</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
+      <c r="C252" s="0" t="inlineStr">
         <is>
           <t>512890</t>
         </is>
       </c>
-      <c r="D252" t="n">
+      <c r="D252" s="0" t="n">
         <v>218000</v>
       </c>
-      <c r="E252" t="n">
+      <c r="E252" s="0" t="n">
         <v>1.15</v>
       </c>
-      <c r="F252" t="n">
+      <c r="F252" s="0" t="n">
         <v>250700</v>
       </c>
-      <c r="G252" t="n">
+      <c r="G252" s="0" t="n">
         <v>1.172</v>
       </c>
-      <c r="H252" t="n">
+      <c r="H252" s="0" t="n">
         <v>0.0086</v>
       </c>
-      <c r="I252" t="n">
+      <c r="I252" s="0" t="n">
         <v>255496</v>
       </c>
-      <c r="J252" t="n">
+      <c r="J252" s="0" t="n">
         <v>4796</v>
       </c>
-      <c r="K252" t="n">
+      <c r="K252" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="L252" t="n">
+      <c r="L252" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M252" t="n">
+      <c r="M252" s="0" t="n">
         <v>0.0743</v>
       </c>
-      <c r="N252" t="n">
+      <c r="N252" s="0" t="n">
         <v>0.0243</v>
       </c>
-      <c r="O252" t="inlineStr">
+      <c r="O252" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
+      <c r="A253" s="0" t="inlineStr">
         <is>
           <t>20260612</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B253" s="0" t="inlineStr">
         <is>
           <t>可转债ETF</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
+      <c r="C253" s="0" t="inlineStr">
         <is>
           <t>511380</t>
         </is>
       </c>
-      <c r="D253" t="n">
+      <c r="D253" s="0" t="n">
         <v>14500</v>
       </c>
-      <c r="E253" t="n">
+      <c r="E253" s="0" t="n">
         <v>13.8644</v>
       </c>
-      <c r="F253" t="n">
+      <c r="F253" s="0" t="n">
         <v>201033.8</v>
       </c>
-      <c r="G253" t="n">
+      <c r="G253" s="0" t="n">
         <v>13.929</v>
       </c>
-      <c r="H253" t="n">
+      <c r="H253" s="0" t="n">
         <v>0.0083</v>
       </c>
-      <c r="I253" t="n">
+      <c r="I253" s="0" t="n">
         <v>201970.5</v>
       </c>
-      <c r="J253" t="n">
+      <c r="J253" s="0" t="n">
         <v>936.7</v>
       </c>
-      <c r="K253" t="n">
+      <c r="K253" s="0" t="n">
         <v>0.0047</v>
       </c>
-      <c r="L253" t="n">
+      <c r="L253" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M253" t="n">
+      <c r="M253" s="0" t="n">
         <v>0.0588</v>
       </c>
-      <c r="N253" t="n">
+      <c r="N253" s="0" t="n">
         <v>-0.0412</v>
       </c>
-      <c r="O253" t="inlineStr">
+      <c r="O253" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
+      <c r="A254" s="0" t="inlineStr">
         <is>
           <t>20260612</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B254" s="0" t="inlineStr">
         <is>
           <t>10年国债ETF</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
+      <c r="C254" s="0" t="inlineStr">
         <is>
           <t>511260</t>
         </is>
       </c>
-      <c r="D254" t="n">
+      <c r="D254" s="0" t="n">
         <v>3700</v>
       </c>
-      <c r="E254" t="n">
+      <c r="E254" s="0" t="n">
         <v>135.645</v>
       </c>
-      <c r="F254" t="n">
-        <v>501886.5000000001</v>
-      </c>
-      <c r="G254" t="n">
+      <c r="F254" s="0" t="n">
+        <v>501886.5</v>
+      </c>
+      <c r="G254" s="0" t="n">
         <v>135.582</v>
       </c>
-      <c r="H254" t="n">
+      <c r="H254" s="0" t="n">
         <v>0.0005</v>
       </c>
-      <c r="I254" t="n">
+      <c r="I254" s="0" t="n">
         <v>501653.4</v>
       </c>
-      <c r="J254" t="n">
+      <c r="J254" s="0" t="n">
         <v>-233.1</v>
       </c>
-      <c r="K254" t="n">
+      <c r="K254" s="0" t="n">
         <v>-0.0005</v>
       </c>
-      <c r="L254" t="n">
+      <c r="L254" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M254" t="n">
+      <c r="M254" s="0" t="n">
         <v>0.146</v>
       </c>
-      <c r="N254" t="n">
+      <c r="N254" s="0" t="n">
         <v>0.046</v>
       </c>
-      <c r="O254" t="inlineStr">
+      <c r="O254" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
+      <c r="A255" s="0" t="inlineStr">
         <is>
           <t>20260612</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B255" s="0" t="inlineStr">
         <is>
           <t>5年国债ETF</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
+      <c r="C255" s="0" t="inlineStr">
         <is>
           <t>511010</t>
         </is>
       </c>
-      <c r="D255" t="n">
+      <c r="D255" s="0" t="n">
         <v>3500</v>
       </c>
-      <c r="E255" t="n">
+      <c r="E255" s="0" t="n">
         <v>141.2121</v>
       </c>
-      <c r="F255" t="n">
+      <c r="F255" s="0" t="n">
         <v>494242.35</v>
       </c>
-      <c r="G255" t="n">
+      <c r="G255" s="0" t="n">
         <v>141.163</v>
       </c>
-      <c r="H255" t="n">
+      <c r="H255" s="0" t="n">
         <v>0.0002</v>
       </c>
-      <c r="I255" t="n">
-        <v>494070.5000000001</v>
-      </c>
-      <c r="J255" t="n">
+      <c r="I255" s="0" t="n">
+        <v>494070.5</v>
+      </c>
+      <c r="J255" s="0" t="n">
         <v>-171.85</v>
       </c>
-      <c r="K255" t="n">
+      <c r="K255" s="0" t="n">
         <v>-0.0003</v>
       </c>
-      <c r="L255" t="n">
+      <c r="L255" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M255" t="n">
+      <c r="M255" s="0" t="n">
         <v>0.1438</v>
       </c>
-      <c r="N255" t="n">
+      <c r="N255" s="0" t="n">
         <v>0.0438</v>
       </c>
-      <c r="O255" t="inlineStr">
+      <c r="O255" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
+      <c r="A256" s="0" t="inlineStr">
         <is>
           <t>20260612</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B256" s="0" t="inlineStr">
         <is>
           <t>短融ETF</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
+      <c r="C256" s="0" t="inlineStr">
         <is>
           <t>511360</t>
         </is>
       </c>
-      <c r="D256" t="n">
+      <c r="D256" s="0" t="n">
         <v>2200</v>
       </c>
-      <c r="E256" t="n">
+      <c r="E256" s="0" t="n">
         <v>113.462</v>
       </c>
-      <c r="F256" t="n">
+      <c r="F256" s="0" t="n">
         <v>249616.4</v>
       </c>
-      <c r="G256" t="n">
+      <c r="G256" s="0" t="n">
         <v>113.538</v>
       </c>
-      <c r="H256" t="n">
+      <c r="H256" s="0" t="n">
         <v>-0.0001</v>
       </c>
-      <c r="I256" t="n">
+      <c r="I256" s="0" t="n">
         <v>249783.6</v>
       </c>
-      <c r="J256" t="n">
+      <c r="J256" s="0" t="n">
         <v>167.2</v>
       </c>
-      <c r="K256" t="n">
+      <c r="K256" s="0" t="n">
         <v>0.0007</v>
       </c>
-      <c r="L256" t="n">
+      <c r="L256" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M256" t="n">
+      <c r="M256" s="0" t="n">
         <v>0.0727</v>
       </c>
-      <c r="N256" t="n">
+      <c r="N256" s="0" t="n">
         <v>0.0227</v>
       </c>
-      <c r="O256" t="inlineStr">
+      <c r="O256" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
+      <c r="A257" s="0" t="inlineStr">
         <is>
           <t>20260612</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B257" s="0" t="inlineStr">
         <is>
           <t>黄金ETF</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C257" s="0" t="inlineStr">
         <is>
           <t>518880</t>
         </is>
       </c>
-      <c r="D257" t="n">
+      <c r="D257" s="0" t="n">
         <v>55800</v>
       </c>
-      <c r="E257" t="n">
+      <c r="E257" s="0" t="n">
         <v>9.232699999999999</v>
       </c>
-      <c r="F257" t="n">
+      <c r="F257" s="0" t="n">
         <v>515184.66</v>
       </c>
-      <c r="G257" t="n">
+      <c r="G257" s="0" t="n">
         <v>8.659000000000001</v>
       </c>
-      <c r="H257" t="n">
+      <c r="H257" s="0" t="n">
         <v>0.018</v>
       </c>
-      <c r="I257" t="n">
+      <c r="I257" s="0" t="n">
         <v>483172.2</v>
       </c>
-      <c r="J257" t="n">
+      <c r="J257" s="0" t="n">
         <v>-32012.46</v>
       </c>
-      <c r="K257" t="n">
+      <c r="K257" s="0" t="n">
         <v>-0.0621</v>
       </c>
-      <c r="L257" t="n">
+      <c r="L257" s="0" t="n">
         <v>0.15</v>
       </c>
-      <c r="M257" t="n">
+      <c r="M257" s="0" t="n">
         <v>0.1406</v>
       </c>
-      <c r="N257" t="n">
+      <c r="N257" s="0" t="n">
         <v>-0.0094</v>
       </c>
-      <c r="O257" t="inlineStr">
+      <c r="O257" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
+      <c r="A258" s="0" t="inlineStr">
         <is>
           <t>20260612</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B258" s="0" t="inlineStr">
         <is>
           <t>银华日利ETF</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C258" s="0" t="inlineStr">
         <is>
           <t>511880</t>
         </is>
       </c>
-      <c r="G258" t="n">
+      <c r="G258" s="0" t="n">
         <v>100.517</v>
       </c>
-      <c r="H258" t="n">
+      <c r="H258" s="0" t="n">
         <v>-0.0001</v>
       </c>
-      <c r="I258" t="n">
+      <c r="I258" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J258" t="n">
+      <c r="J258" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K258" t="n">
+      <c r="K258" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="L258" t="n">
+      <c r="L258" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M258" t="n">
+      <c r="M258" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="N258" t="n">
+      <c r="N258" s="0" t="n">
         <v>-0.05</v>
       </c>
-      <c r="O258" t="inlineStr">
+      <c r="O258" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
+      <c r="A259" s="0" t="inlineStr">
         <is>
           <t>20260612</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B259" s="0" t="inlineStr">
         <is>
           <t>华宝添益ETF</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
+      <c r="C259" s="0" t="inlineStr">
         <is>
           <t>511990</t>
         </is>
       </c>
-      <c r="G259" t="n">
+      <c r="G259" s="0" t="n">
         <v>100.003</v>
       </c>
-      <c r="I259" t="n">
+      <c r="I259" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J259" t="n">
+      <c r="J259" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K259" t="n">
+      <c r="K259" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="L259" t="n">
+      <c r="L259" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="M259" t="n">
+      <c r="M259" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="N259" t="n">
+      <c r="N259" s="0" t="n">
         <v>-0.05</v>
       </c>
-      <c r="O259" t="inlineStr">
+      <c r="O259" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
